--- a/research/traditional_assets/database/data/denmark/denmark_air_transport.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_air_transport.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="cpse_kbhl" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,115 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.212</v>
+        <v>-0.0581</v>
+      </c>
+      <c r="E2">
+        <v>-0.283</v>
       </c>
       <c r="G2">
-        <v>-0.09156976744186046</v>
+        <v>0.05022935779816513</v>
       </c>
       <c r="H2">
-        <v>-0.09156976744186046</v>
+        <v>0.05022935779816513</v>
       </c>
       <c r="I2">
-        <v>-1.009205426356589</v>
+        <v>0.06605504587155964</v>
       </c>
       <c r="J2">
-        <v>-1.009205426356589</v>
+        <v>0.05243214611098163</v>
       </c>
       <c r="K2">
-        <v>-139.6</v>
+        <v>31.8</v>
       </c>
       <c r="L2">
-        <v>-0.6763565891472868</v>
+        <v>0.07293577981651377</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.0006859608660069935</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0.1449685534591195</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.0006859608660069935</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0.1449685534591195</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>33.4</v>
+        <v>30.4</v>
       </c>
       <c r="V2">
-        <v>0.004768771684347292</v>
+        <v>0.004523472955881258</v>
       </c>
       <c r="W2">
-        <v>-0.3005382131324004</v>
+        <v>0.08383865014500395</v>
       </c>
       <c r="X2">
-        <v>0.05964082823748792</v>
+        <v>0.09141134052793817</v>
       </c>
       <c r="Y2">
-        <v>-0.3601790413698883</v>
+        <v>-0.007572690382934219</v>
       </c>
       <c r="Z2">
-        <v>0.106669422982506</v>
+        <v>0.2188974796666332</v>
       </c>
       <c r="AA2">
-        <v>-0.1076513605002713</v>
+        <v>0.01147726463720654</v>
       </c>
       <c r="AB2">
-        <v>0.05175728722788405</v>
+        <v>0.08220992522269466</v>
       </c>
       <c r="AC2">
-        <v>-0.1594086477281554</v>
+        <v>-0.07073266058548812</v>
       </c>
       <c r="AD2">
-        <v>1645.9</v>
+        <v>1364.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1645.9</v>
+        <v>1364.6</v>
       </c>
       <c r="AG2">
-        <v>1612.5</v>
+        <v>1334.2</v>
       </c>
       <c r="AH2">
-        <v>0.1902818562278897</v>
+        <v>0.1687796069312686</v>
       </c>
       <c r="AI2">
-        <v>0.7723603941811357</v>
+        <v>0.7573117265109052</v>
       </c>
       <c r="AJ2">
-        <v>0.1871431224177151</v>
+        <v>0.1656424199535675</v>
       </c>
       <c r="AK2">
-        <v>0.7687356979405034</v>
+        <v>0.7531470505221564</v>
       </c>
       <c r="AL2">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="AM2">
-        <v>17.461</v>
+        <v>20.1</v>
       </c>
       <c r="AN2">
-        <v>-25.39969135802469</v>
+        <v>9.469812630117973</v>
       </c>
       <c r="AO2">
-        <v>-11.50828729281768</v>
+        <v>1.432835820895522</v>
       </c>
       <c r="AP2">
-        <v>-24.88425925925926</v>
+        <v>9.2588480222068</v>
       </c>
       <c r="AQ2">
-        <v>-11.92944275814673</v>
+        <v>1.432835820895522</v>
       </c>
     </row>
     <row r="3">
@@ -716,115 +724,8833 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.212</v>
+        <v>-0.0581</v>
+      </c>
+      <c r="E3">
+        <v>-0.283</v>
       </c>
       <c r="G3">
-        <v>-0.09156976744186046</v>
+        <v>0.05022935779816513</v>
       </c>
       <c r="H3">
-        <v>-0.09156976744186046</v>
+        <v>0.05022935779816513</v>
       </c>
       <c r="I3">
-        <v>-1.009205426356589</v>
+        <v>0.06605504587155964</v>
       </c>
       <c r="J3">
-        <v>-1.009205426356589</v>
+        <v>0.05243214611098163</v>
       </c>
       <c r="K3">
-        <v>-139.6</v>
+        <v>31.8</v>
       </c>
       <c r="L3">
-        <v>-0.6763565891472868</v>
+        <v>0.07293577981651377</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>4.61</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0006859608660069935</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.1449685534591195</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>4.61</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.0006859608660069935</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.1449685534591195</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>33.4</v>
+        <v>30.4</v>
       </c>
       <c r="V3">
-        <v>0.004768771684347292</v>
+        <v>0.004523472955881258</v>
       </c>
       <c r="W3">
-        <v>-0.3005382131324004</v>
+        <v>0.08383865014500395</v>
       </c>
       <c r="X3">
-        <v>0.05964082823748792</v>
+        <v>0.09141134052793817</v>
       </c>
       <c r="Y3">
-        <v>-0.3601790413698883</v>
+        <v>-0.007572690382934219</v>
       </c>
       <c r="Z3">
-        <v>0.106669422982506</v>
+        <v>0.2188974796666332</v>
       </c>
       <c r="AA3">
-        <v>-0.1076513605002713</v>
+        <v>0.01147726463720654</v>
       </c>
       <c r="AB3">
-        <v>0.05175728722788405</v>
+        <v>0.08220992522269466</v>
       </c>
       <c r="AC3">
-        <v>-0.1594086477281554</v>
+        <v>-0.07073266058548812</v>
       </c>
       <c r="AD3">
-        <v>1645.9</v>
+        <v>1364.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1645.9</v>
+        <v>1364.6</v>
       </c>
       <c r="AG3">
-        <v>1612.5</v>
+        <v>1334.2</v>
       </c>
       <c r="AH3">
-        <v>0.1902818562278897</v>
+        <v>0.1687796069312686</v>
       </c>
       <c r="AI3">
-        <v>0.7723603941811357</v>
+        <v>0.7573117265109052</v>
       </c>
       <c r="AJ3">
-        <v>0.1871431224177151</v>
+        <v>0.1656424199535675</v>
       </c>
       <c r="AK3">
-        <v>0.7687356979405034</v>
+        <v>0.7531470505221564</v>
       </c>
       <c r="AL3">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="AM3">
-        <v>17.461</v>
+        <v>20.1</v>
       </c>
       <c r="AN3">
-        <v>-25.39969135802469</v>
+        <v>9.469812630117973</v>
       </c>
       <c r="AO3">
-        <v>-11.50828729281768</v>
+        <v>1.432835820895522</v>
       </c>
       <c r="AP3">
-        <v>-24.88425925925926</v>
+        <v>9.2588480222068</v>
       </c>
       <c r="AQ3">
-        <v>-11.92944275814673</v>
+        <v>1.432835820895522</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Københavns Lufthavne A/S (CPSE:KBHL)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CPSE:KBHL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Air Transport</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.168779606931269</v>
+      </c>
+      <c r="F2">
+        <v>0.01</v>
+      </c>
+      <c r="G2">
+        <v>6720.5</v>
+      </c>
+      <c r="H2">
+        <v>7658.11487954351</v>
+      </c>
+      <c r="I2">
+        <v>8054.7</v>
+      </c>
+      <c r="J2">
+        <v>7708.56587954351</v>
+      </c>
+      <c r="K2">
+        <v>1364.6</v>
+      </c>
+      <c r="L2">
+        <v>80.851</v>
+      </c>
+      <c r="M2">
+        <v>0.0822099252226947</v>
+      </c>
+      <c r="N2">
+        <v>0.0841591407474544</v>
+      </c>
+      <c r="O2">
+        <v>0.036894</v>
+      </c>
+      <c r="P2">
+        <v>0.0429</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.0914113405279382</v>
+      </c>
+      <c r="T2">
+        <v>0.0845758997449035</v>
+      </c>
+      <c r="U2">
+        <v>0.889570557874532</v>
+      </c>
+      <c r="V2">
+        <v>0.773994584906241</v>
+      </c>
+      <c r="W2">
+        <v>3.598088964998465</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>6720.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.0591424031092525</v>
+      </c>
+      <c r="AC2">
+        <v>0.0473</v>
+      </c>
+      <c r="AD2">
+        <v>0.22</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>144.1</v>
+      </c>
+      <c r="AH2">
+        <v>128.1</v>
+      </c>
+      <c r="AI2">
+        <v>96.7</v>
+      </c>
+      <c r="AJ2">
+        <v>1364.6</v>
+      </c>
+      <c r="AK2">
+        <v>1364.6</v>
+      </c>
+      <c r="AL2">
+        <v>20.1</v>
+      </c>
+      <c r="AM2">
+        <v>1364.6</v>
+      </c>
+      <c r="AN2">
+        <v>30.4</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08421806048051154</v>
+      </c>
+      <c r="C2">
+        <v>7728.96574657722</v>
+      </c>
+      <c r="D2">
+        <v>7698.56574657722</v>
+      </c>
+      <c r="E2">
+        <v>-1364.6</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>30.4</v>
+      </c>
+      <c r="H2">
+        <v>6720.5</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>144.1</v>
+      </c>
+      <c r="K2">
+        <v>128.1</v>
+      </c>
+      <c r="L2">
+        <v>16</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>16</v>
+      </c>
+      <c r="O2">
+        <v>3.52</v>
+      </c>
+      <c r="P2">
+        <v>12.48</v>
+      </c>
+      <c r="Q2">
+        <v>140.58</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08421806048051154</v>
+      </c>
+      <c r="T2">
+        <v>0.7679441161126261</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.22</v>
+      </c>
+      <c r="W2">
+        <v>0.035646</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08415914074745441</v>
+      </c>
+      <c r="C3">
+        <v>7658.114879543508</v>
+      </c>
+      <c r="D3">
+        <v>7708.565879543508</v>
+      </c>
+      <c r="E3">
+        <v>-1283.749</v>
+      </c>
+      <c r="F3">
+        <v>80.851</v>
+      </c>
+      <c r="G3">
+        <v>30.4</v>
+      </c>
+      <c r="H3">
+        <v>6720.5</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>144.1</v>
+      </c>
+      <c r="K3">
+        <v>128.1</v>
+      </c>
+      <c r="L3">
+        <v>16</v>
+      </c>
+      <c r="M3">
+        <v>4.446805</v>
+      </c>
+      <c r="N3">
+        <v>11.553195</v>
+      </c>
+      <c r="O3">
+        <v>2.541702899999999</v>
+      </c>
+      <c r="P3">
+        <v>9.0114921</v>
+      </c>
+      <c r="Q3">
+        <v>137.1114921</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08457589974490345</v>
+      </c>
+      <c r="T3">
+        <v>0.7739945849062407</v>
+      </c>
+      <c r="U3">
+        <v>0.055</v>
+      </c>
+      <c r="V3">
+        <v>0.22</v>
+      </c>
+      <c r="W3">
+        <v>0.0429</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>3.598088964998465</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08719020525695621</v>
+      </c>
+      <c r="C4">
+        <v>7094.41491594499</v>
+      </c>
+      <c r="D4">
+        <v>7225.71691594499</v>
+      </c>
+      <c r="E4">
+        <v>-1202.898</v>
+      </c>
+      <c r="F4">
+        <v>161.702</v>
+      </c>
+      <c r="G4">
+        <v>30.4</v>
+      </c>
+      <c r="H4">
+        <v>6720.5</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>144.1</v>
+      </c>
+      <c r="K4">
+        <v>128.1</v>
+      </c>
+      <c r="L4">
+        <v>16</v>
+      </c>
+      <c r="M4">
+        <v>34.5718876</v>
+      </c>
+      <c r="N4">
+        <v>-18.5718876</v>
+      </c>
+      <c r="O4">
+        <v>-4.085815271999999</v>
+      </c>
+      <c r="P4">
+        <v>-14.486072328</v>
+      </c>
+      <c r="Q4">
+        <v>113.613927672</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.08505058573645002</v>
+      </c>
+      <c r="T4">
+        <v>0.7820207381666975</v>
+      </c>
+      <c r="U4">
+        <v>0.2138</v>
+      </c>
+      <c r="V4">
+        <v>0.1018168299262896</v>
+      </c>
+      <c r="W4">
+        <v>0.1920315617617593</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>0.4628037723922255</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08894020525695621</v>
+      </c>
+      <c r="C5">
+        <v>6761.370999340416</v>
+      </c>
+      <c r="D5">
+        <v>6973.523999340417</v>
+      </c>
+      <c r="E5">
+        <v>-1122.047</v>
+      </c>
+      <c r="F5">
+        <v>242.553</v>
+      </c>
+      <c r="G5">
+        <v>30.4</v>
+      </c>
+      <c r="H5">
+        <v>6720.5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>144.1</v>
+      </c>
+      <c r="K5">
+        <v>128.1</v>
+      </c>
+      <c r="L5">
+        <v>16</v>
+      </c>
+      <c r="M5">
+        <v>51.85783139999999</v>
+      </c>
+      <c r="N5">
+        <v>-35.85783139999999</v>
+      </c>
+      <c r="O5">
+        <v>-7.888722907999998</v>
+      </c>
+      <c r="P5">
+        <v>-27.969108492</v>
+      </c>
+      <c r="Q5">
+        <v>100.130891508</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.08552739589868147</v>
+      </c>
+      <c r="T5">
+        <v>0.7900828076323334</v>
+      </c>
+      <c r="U5">
+        <v>0.2138</v>
+      </c>
+      <c r="V5">
+        <v>0.06787788661752639</v>
+      </c>
+      <c r="W5">
+        <v>0.1992877078411729</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>0.3085358482614836</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.0906902052569562</v>
+      </c>
+      <c r="C6">
+        <v>6445.337522446867</v>
+      </c>
+      <c r="D6">
+        <v>6738.341522446867</v>
+      </c>
+      <c r="E6">
+        <v>-1041.196</v>
+      </c>
+      <c r="F6">
+        <v>323.404</v>
+      </c>
+      <c r="G6">
+        <v>30.4</v>
+      </c>
+      <c r="H6">
+        <v>6720.5</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>144.1</v>
+      </c>
+      <c r="K6">
+        <v>128.1</v>
+      </c>
+      <c r="L6">
+        <v>16</v>
+      </c>
+      <c r="M6">
+        <v>69.14377519999999</v>
+      </c>
+      <c r="N6">
+        <v>-53.14377519999999</v>
+      </c>
+      <c r="O6">
+        <v>-11.691630544</v>
+      </c>
+      <c r="P6">
+        <v>-41.45214465599999</v>
+      </c>
+      <c r="Q6">
+        <v>86.64785534399999</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.08601413960595938</v>
+      </c>
+      <c r="T6">
+        <v>0.7983128368785035</v>
+      </c>
+      <c r="U6">
+        <v>0.2138</v>
+      </c>
+      <c r="V6">
+        <v>0.0509084149631448</v>
+      </c>
+      <c r="W6">
+        <v>0.2029157808808796</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>0.2314018861961127</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.09369988767517129</v>
+      </c>
+      <c r="C7">
+        <v>5995.08197779588</v>
+      </c>
+      <c r="D7">
+        <v>6368.93697779588</v>
+      </c>
+      <c r="E7">
+        <v>-960.3449999999998</v>
+      </c>
+      <c r="F7">
+        <v>404.2550000000001</v>
+      </c>
+      <c r="G7">
+        <v>30.4</v>
+      </c>
+      <c r="H7">
+        <v>6720.5</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>144.1</v>
+      </c>
+      <c r="K7">
+        <v>128.1</v>
+      </c>
+      <c r="L7">
+        <v>16</v>
+      </c>
+      <c r="M7">
+        <v>96.53609400000002</v>
+      </c>
+      <c r="N7">
+        <v>-80.53609400000002</v>
+      </c>
+      <c r="O7">
+        <v>-17.71794068</v>
+      </c>
+      <c r="P7">
+        <v>-62.81815332000002</v>
+      </c>
+      <c r="Q7">
+        <v>65.28184667999997</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.08652132256835379</v>
+      </c>
+      <c r="T7">
+        <v>0.8068884600478479</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>0.03646304562519382</v>
+      </c>
+      <c r="W7">
+        <v>0.2300926247047037</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>0.1657411164781537</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09569988767517129</v>
+      </c>
+      <c r="C8">
+        <v>5690.366318724679</v>
+      </c>
+      <c r="D8">
+        <v>6145.072318724679</v>
+      </c>
+      <c r="E8">
+        <v>-879.4939999999999</v>
+      </c>
+      <c r="F8">
+        <v>485.106</v>
+      </c>
+      <c r="G8">
+        <v>30.4</v>
+      </c>
+      <c r="H8">
+        <v>6720.5</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>144.1</v>
+      </c>
+      <c r="K8">
+        <v>128.1</v>
+      </c>
+      <c r="L8">
+        <v>16</v>
+      </c>
+      <c r="M8">
+        <v>115.8433128</v>
+      </c>
+      <c r="N8">
+        <v>-99.84331280000001</v>
+      </c>
+      <c r="O8">
+        <v>-21.965528816</v>
+      </c>
+      <c r="P8">
+        <v>-77.877783984</v>
+      </c>
+      <c r="Q8">
+        <v>50.22221601599999</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.08702899621269798</v>
+      </c>
+      <c r="T8">
+        <v>0.8154723798355908</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>0.03038587135432819</v>
+      </c>
+      <c r="W8">
+        <v>0.2315438539205865</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>0.1381175970651282</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09769988767517129</v>
+      </c>
+      <c r="C9">
+        <v>5400.853721520476</v>
+      </c>
+      <c r="D9">
+        <v>5936.410721520477</v>
+      </c>
+      <c r="E9">
+        <v>-798.6429999999998</v>
+      </c>
+      <c r="F9">
+        <v>565.9570000000001</v>
+      </c>
+      <c r="G9">
+        <v>30.4</v>
+      </c>
+      <c r="H9">
+        <v>6720.5</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>144.1</v>
+      </c>
+      <c r="K9">
+        <v>128.1</v>
+      </c>
+      <c r="L9">
+        <v>16</v>
+      </c>
+      <c r="M9">
+        <v>135.1505316</v>
+      </c>
+      <c r="N9">
+        <v>-119.1505316</v>
+      </c>
+      <c r="O9">
+        <v>-26.213116952</v>
+      </c>
+      <c r="P9">
+        <v>-92.93741464800001</v>
+      </c>
+      <c r="Q9">
+        <v>35.16258535199998</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.08754758756982378</v>
+      </c>
+      <c r="T9">
+        <v>0.824240900048877</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>0.02604503258942415</v>
+      </c>
+      <c r="W9">
+        <v>0.2325804462176455</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>0.1183865117701098</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09969988767517129</v>
+      </c>
+      <c r="C10">
+        <v>5125.046344813045</v>
+      </c>
+      <c r="D10">
+        <v>5741.454344813045</v>
+      </c>
+      <c r="E10">
+        <v>-717.7919999999999</v>
+      </c>
+      <c r="F10">
+        <v>646.808</v>
+      </c>
+      <c r="G10">
+        <v>30.4</v>
+      </c>
+      <c r="H10">
+        <v>6720.5</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>144.1</v>
+      </c>
+      <c r="K10">
+        <v>128.1</v>
+      </c>
+      <c r="L10">
+        <v>16</v>
+      </c>
+      <c r="M10">
+        <v>154.4577504</v>
+      </c>
+      <c r="N10">
+        <v>-138.4577504</v>
+      </c>
+      <c r="O10">
+        <v>-30.460705088</v>
+      </c>
+      <c r="P10">
+        <v>-107.997045312</v>
+      </c>
+      <c r="Q10">
+        <v>20.10295468799998</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.08807745265210447</v>
+      </c>
+      <c r="T10">
+        <v>0.8332000402667994</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>0.02278940351574614</v>
+      </c>
+      <c r="W10">
+        <v>0.2333578904404398</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>0.1035881977988461</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1016998876751713</v>
+      </c>
+      <c r="C11">
+        <v>4861.636852039158</v>
+      </c>
+      <c r="D11">
+        <v>5558.895852039158</v>
+      </c>
+      <c r="E11">
+        <v>-636.9409999999999</v>
+      </c>
+      <c r="F11">
+        <v>727.659</v>
+      </c>
+      <c r="G11">
+        <v>30.4</v>
+      </c>
+      <c r="H11">
+        <v>6720.5</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>144.1</v>
+      </c>
+      <c r="K11">
+        <v>128.1</v>
+      </c>
+      <c r="L11">
+        <v>16</v>
+      </c>
+      <c r="M11">
+        <v>173.7649692</v>
+      </c>
+      <c r="N11">
+        <v>-157.7649692</v>
+      </c>
+      <c r="O11">
+        <v>-34.70829322399999</v>
+      </c>
+      <c r="P11">
+        <v>-123.056675976</v>
+      </c>
+      <c r="Q11">
+        <v>5.043324023999986</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.08861896312080891</v>
+      </c>
+      <c r="T11">
+        <v>0.8423560846653357</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>0.02025724756955212</v>
+      </c>
+      <c r="W11">
+        <v>0.233962569280391</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>0.09207839804341877</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1036998876751713</v>
+      </c>
+      <c r="C12">
+        <v>4609.479057800566</v>
+      </c>
+      <c r="D12">
+        <v>5387.589057800566</v>
+      </c>
+      <c r="E12">
+        <v>-556.0899999999998</v>
+      </c>
+      <c r="F12">
+        <v>808.5100000000001</v>
+      </c>
+      <c r="G12">
+        <v>30.4</v>
+      </c>
+      <c r="H12">
+        <v>6720.5</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>144.1</v>
+      </c>
+      <c r="K12">
+        <v>128.1</v>
+      </c>
+      <c r="L12">
+        <v>16</v>
+      </c>
+      <c r="M12">
+        <v>193.072188</v>
+      </c>
+      <c r="N12">
+        <v>-177.072188</v>
+      </c>
+      <c r="O12">
+        <v>-38.95588136000001</v>
+      </c>
+      <c r="P12">
+        <v>-138.11630664</v>
+      </c>
+      <c r="Q12">
+        <v>-10.01630664000004</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.08917250715548455</v>
+      </c>
+      <c r="T12">
+        <v>0.8517155967171727</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>0.01823152281259691</v>
+      </c>
+      <c r="W12">
+        <v>0.2344463123523519</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>0.08287055823907685</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1056998876751713</v>
+      </c>
+      <c r="C13">
+        <v>4367.563839458086</v>
+      </c>
+      <c r="D13">
+        <v>5226.524839458087</v>
+      </c>
+      <c r="E13">
+        <v>-475.2389999999999</v>
+      </c>
+      <c r="F13">
+        <v>889.361</v>
+      </c>
+      <c r="G13">
+        <v>30.4</v>
+      </c>
+      <c r="H13">
+        <v>6720.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>144.1</v>
+      </c>
+      <c r="K13">
+        <v>128.1</v>
+      </c>
+      <c r="L13">
+        <v>16</v>
+      </c>
+      <c r="M13">
+        <v>212.3794068</v>
+      </c>
+      <c r="N13">
+        <v>-196.3794068</v>
+      </c>
+      <c r="O13">
+        <v>-43.203469496</v>
+      </c>
+      <c r="P13">
+        <v>-153.175937304</v>
+      </c>
+      <c r="Q13">
+        <v>-25.07593730400001</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.08973849038195068</v>
+      </c>
+      <c r="T13">
+        <v>0.8612854348825342</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>0.01657411164781537</v>
+      </c>
+      <c r="W13">
+        <v>0.2348421021385017</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>0.0753368711264335</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1076998876751713</v>
+      </c>
+      <c r="C14">
+        <v>4134.99924410076</v>
+      </c>
+      <c r="D14">
+        <v>5074.811244100761</v>
+      </c>
+      <c r="E14">
+        <v>-394.3879999999999</v>
+      </c>
+      <c r="F14">
+        <v>970.212</v>
+      </c>
+      <c r="G14">
+        <v>30.4</v>
+      </c>
+      <c r="H14">
+        <v>6720.5</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>144.1</v>
+      </c>
+      <c r="K14">
+        <v>128.1</v>
+      </c>
+      <c r="L14">
+        <v>16</v>
+      </c>
+      <c r="M14">
+        <v>231.6866256</v>
+      </c>
+      <c r="N14">
+        <v>-215.6866256</v>
+      </c>
+      <c r="O14">
+        <v>-47.45105763199999</v>
+      </c>
+      <c r="P14">
+        <v>-168.235567968</v>
+      </c>
+      <c r="Q14">
+        <v>-40.13556796800003</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.09031733686356375</v>
+      </c>
+      <c r="T14">
+        <v>0.8710727693698357</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>0.01519293567716409</v>
+      </c>
+      <c r="W14">
+        <v>0.2351719269602932</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.06905879853256403</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1096998876751713</v>
+      </c>
+      <c r="C15">
+        <v>3910.993962464911</v>
+      </c>
+      <c r="D15">
+        <v>4931.656962464912</v>
+      </c>
+      <c r="E15">
+        <v>-313.5369999999998</v>
+      </c>
+      <c r="F15">
+        <v>1051.063</v>
+      </c>
+      <c r="G15">
+        <v>30.4</v>
+      </c>
+      <c r="H15">
+        <v>6720.5</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>144.1</v>
+      </c>
+      <c r="K15">
+        <v>128.1</v>
+      </c>
+      <c r="L15">
+        <v>16</v>
+      </c>
+      <c r="M15">
+        <v>250.9938444</v>
+      </c>
+      <c r="N15">
+        <v>-234.9938444</v>
+      </c>
+      <c r="O15">
+        <v>-51.698645768</v>
+      </c>
+      <c r="P15">
+        <v>-183.295198632</v>
+      </c>
+      <c r="Q15">
+        <v>-55.19519863200003</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.0909094901608461</v>
+      </c>
+      <c r="T15">
+        <v>0.8810851000522477</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>0.01402424831738224</v>
+      </c>
+      <c r="W15">
+        <v>0.2354510095018091</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.06374658326082838</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1116998876751713</v>
+      </c>
+      <c r="C16">
+        <v>3694.843523199942</v>
+      </c>
+      <c r="D16">
+        <v>4796.357523199943</v>
+      </c>
+      <c r="E16">
+        <v>-232.6859999999997</v>
+      </c>
+      <c r="F16">
+        <v>1131.914</v>
+      </c>
+      <c r="G16">
+        <v>30.4</v>
+      </c>
+      <c r="H16">
+        <v>6720.5</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>144.1</v>
+      </c>
+      <c r="K16">
+        <v>128.1</v>
+      </c>
+      <c r="L16">
+        <v>16</v>
+      </c>
+      <c r="M16">
+        <v>270.3010632</v>
+      </c>
+      <c r="N16">
+        <v>-254.3010632</v>
+      </c>
+      <c r="O16">
+        <v>-55.946233904</v>
+      </c>
+      <c r="P16">
+        <v>-198.354829296</v>
+      </c>
+      <c r="Q16">
+        <v>-70.25482929600005</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.09151541446504199</v>
+      </c>
+      <c r="T16">
+        <v>0.8913302756342505</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>0.01302251629471208</v>
+      </c>
+      <c r="W16">
+        <v>0.2356902231088228</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.05919325588505486</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1136998876751713</v>
+      </c>
+      <c r="C17">
+        <v>3485.918699004077</v>
+      </c>
+      <c r="D17">
+        <v>4668.283699004078</v>
+      </c>
+      <c r="E17">
+        <v>-151.8349999999998</v>
+      </c>
+      <c r="F17">
+        <v>1212.765</v>
+      </c>
+      <c r="G17">
+        <v>30.4</v>
+      </c>
+      <c r="H17">
+        <v>6720.5</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>144.1</v>
+      </c>
+      <c r="K17">
+        <v>128.1</v>
+      </c>
+      <c r="L17">
+        <v>16</v>
+      </c>
+      <c r="M17">
+        <v>289.608282</v>
+      </c>
+      <c r="N17">
+        <v>-273.608282</v>
+      </c>
+      <c r="O17">
+        <v>-60.19382204</v>
+      </c>
+      <c r="P17">
+        <v>-213.41445996</v>
+      </c>
+      <c r="Q17">
+        <v>-85.31445996000005</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09213559581168955</v>
+      </c>
+      <c r="T17">
+        <v>0.9018165141711242</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>0.01215434854173127</v>
+      </c>
+      <c r="W17">
+        <v>0.2358975415682346</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.0552470388260512</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1156998876751713</v>
+      </c>
+      <c r="C18">
+        <v>3283.655721948322</v>
+      </c>
+      <c r="D18">
+        <v>4546.871721948322</v>
+      </c>
+      <c r="E18">
+        <v>-70.98399999999992</v>
+      </c>
+      <c r="F18">
+        <v>1293.616</v>
+      </c>
+      <c r="G18">
+        <v>30.4</v>
+      </c>
+      <c r="H18">
+        <v>6720.5</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>144.1</v>
+      </c>
+      <c r="K18">
+        <v>128.1</v>
+      </c>
+      <c r="L18">
+        <v>16</v>
+      </c>
+      <c r="M18">
+        <v>308.9155008</v>
+      </c>
+      <c r="N18">
+        <v>-292.9155008</v>
+      </c>
+      <c r="O18">
+        <v>-64.44141017599999</v>
+      </c>
+      <c r="P18">
+        <v>-228.474090624</v>
+      </c>
+      <c r="Q18">
+        <v>-100.374090624</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09277054338087631</v>
+      </c>
+      <c r="T18">
+        <v>0.9125524250541136</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>0.01139470175787307</v>
+      </c>
+      <c r="W18">
+        <v>0.2360789452202199</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.05179409889942299</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1176998876751713</v>
+      </c>
+      <c r="C19">
+        <v>3087.547986966196</v>
+      </c>
+      <c r="D19">
+        <v>4431.614986966197</v>
+      </c>
+      <c r="E19">
+        <v>9.867000000000189</v>
+      </c>
+      <c r="F19">
+        <v>1374.467</v>
+      </c>
+      <c r="G19">
+        <v>30.4</v>
+      </c>
+      <c r="H19">
+        <v>6720.5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>144.1</v>
+      </c>
+      <c r="K19">
+        <v>128.1</v>
+      </c>
+      <c r="L19">
+        <v>16</v>
+      </c>
+      <c r="M19">
+        <v>328.2227196000001</v>
+      </c>
+      <c r="N19">
+        <v>-312.2227196000001</v>
+      </c>
+      <c r="O19">
+        <v>-68.68899831200001</v>
+      </c>
+      <c r="P19">
+        <v>-243.533721288</v>
+      </c>
+      <c r="Q19">
+        <v>-115.433721288</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09342079089148929</v>
+      </c>
+      <c r="T19">
+        <v>0.9235470325848861</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>0.01072442518388053</v>
+      </c>
+      <c r="W19">
+        <v>0.2362390072660893</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.04874738719945693</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1196998876751713</v>
+      </c>
+      <c r="C20">
+        <v>2897.138985977123</v>
+      </c>
+      <c r="D20">
+        <v>4322.056985977124</v>
+      </c>
+      <c r="E20">
+        <v>90.71800000000007</v>
+      </c>
+      <c r="F20">
+        <v>1455.318</v>
+      </c>
+      <c r="G20">
+        <v>30.4</v>
+      </c>
+      <c r="H20">
+        <v>6720.5</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>144.1</v>
+      </c>
+      <c r="K20">
+        <v>128.1</v>
+      </c>
+      <c r="L20">
+        <v>16</v>
+      </c>
+      <c r="M20">
+        <v>347.5299384</v>
+      </c>
+      <c r="N20">
+        <v>-331.5299384</v>
+      </c>
+      <c r="O20">
+        <v>-72.93658644799999</v>
+      </c>
+      <c r="P20">
+        <v>-258.593351952</v>
+      </c>
+      <c r="Q20">
+        <v>-130.493351952</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09408689809748305</v>
+      </c>
+      <c r="T20">
+        <v>0.9348098012749456</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>0.01012862378477606</v>
+      </c>
+      <c r="W20">
+        <v>0.2363812846401955</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.04603919902170939</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1216998876751713</v>
+      </c>
+      <c r="C21">
+        <v>2712.016264815995</v>
+      </c>
+      <c r="D21">
+        <v>4217.785264815995</v>
+      </c>
+      <c r="E21">
+        <v>171.5690000000002</v>
+      </c>
+      <c r="F21">
+        <v>1536.169</v>
+      </c>
+      <c r="G21">
+        <v>30.4</v>
+      </c>
+      <c r="H21">
+        <v>6720.5</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>144.1</v>
+      </c>
+      <c r="K21">
+        <v>128.1</v>
+      </c>
+      <c r="L21">
+        <v>16</v>
+      </c>
+      <c r="M21">
+        <v>366.8371572</v>
+      </c>
+      <c r="N21">
+        <v>-350.8371572</v>
+      </c>
+      <c r="O21">
+        <v>-77.184174584</v>
+      </c>
+      <c r="P21">
+        <v>-273.652982616</v>
+      </c>
+      <c r="Q21">
+        <v>-145.552982616</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09476945239498286</v>
+      </c>
+      <c r="T21">
+        <v>0.9463506630190808</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.009595538322419425</v>
+      </c>
+      <c r="W21">
+        <v>0.2365085854486063</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.04361608328372468</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1236998876751713</v>
+      </c>
+      <c r="C22">
+        <v>2531.806234308126</v>
+      </c>
+      <c r="D22">
+        <v>4118.426234308127</v>
+      </c>
+      <c r="E22">
+        <v>252.4200000000003</v>
+      </c>
+      <c r="F22">
+        <v>1617.02</v>
+      </c>
+      <c r="G22">
+        <v>30.4</v>
+      </c>
+      <c r="H22">
+        <v>6720.5</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>144.1</v>
+      </c>
+      <c r="K22">
+        <v>128.1</v>
+      </c>
+      <c r="L22">
+        <v>16</v>
+      </c>
+      <c r="M22">
+        <v>386.1443760000001</v>
+      </c>
+      <c r="N22">
+        <v>-370.1443760000001</v>
+      </c>
+      <c r="O22">
+        <v>-81.43176272000001</v>
+      </c>
+      <c r="P22">
+        <v>-288.7126132800001</v>
+      </c>
+      <c r="Q22">
+        <v>-160.6126132800001</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.09546907054992013</v>
+      </c>
+      <c r="T22">
+        <v>0.9581800463068193</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.009115761406298455</v>
+      </c>
+      <c r="W22">
+        <v>0.2366231561761759</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.04143527911953848</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1256998876751713</v>
+      </c>
+      <c r="C23">
+        <v>2356.169697882519</v>
+      </c>
+      <c r="D23">
+        <v>4023.640697882519</v>
+      </c>
+      <c r="E23">
+        <v>333.2710000000002</v>
+      </c>
+      <c r="F23">
+        <v>1697.871</v>
+      </c>
+      <c r="G23">
+        <v>30.4</v>
+      </c>
+      <c r="H23">
+        <v>6720.5</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>144.1</v>
+      </c>
+      <c r="K23">
+        <v>128.1</v>
+      </c>
+      <c r="L23">
+        <v>16</v>
+      </c>
+      <c r="M23">
+        <v>405.4515948000001</v>
+      </c>
+      <c r="N23">
+        <v>-389.4515948000001</v>
+      </c>
+      <c r="O23">
+        <v>-85.679350856</v>
+      </c>
+      <c r="P23">
+        <v>-303.7722439440001</v>
+      </c>
+      <c r="Q23">
+        <v>-175.6722439440001</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.09618640055688114</v>
+      </c>
+      <c r="T23">
+        <v>0.9703089076524751</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.00868167752980805</v>
+      </c>
+      <c r="W23">
+        <v>0.2367268154058818</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.03946217059003665</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1276998876751713</v>
+      </c>
+      <c r="C24">
+        <v>2184.797982882644</v>
+      </c>
+      <c r="D24">
+        <v>3933.119982882644</v>
+      </c>
+      <c r="E24">
+        <v>414.1220000000001</v>
+      </c>
+      <c r="F24">
+        <v>1778.722</v>
+      </c>
+      <c r="G24">
+        <v>30.4</v>
+      </c>
+      <c r="H24">
+        <v>6720.5</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>144.1</v>
+      </c>
+      <c r="K24">
+        <v>128.1</v>
+      </c>
+      <c r="L24">
+        <v>16</v>
+      </c>
+      <c r="M24">
+        <v>424.7588136</v>
+      </c>
+      <c r="N24">
+        <v>-408.7588136</v>
+      </c>
+      <c r="O24">
+        <v>-89.92693899199999</v>
+      </c>
+      <c r="P24">
+        <v>-318.831874608</v>
+      </c>
+      <c r="Q24">
+        <v>-190.731874608</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.09692212364094373</v>
+      </c>
+      <c r="T24">
+        <v>0.9827487654428916</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.008287055823907687</v>
+      </c>
+      <c r="W24">
+        <v>0.2368210510692509</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.03766843556321675</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1296998876751713</v>
+      </c>
+      <c r="C25">
+        <v>2017.40958259591</v>
+      </c>
+      <c r="D25">
+        <v>3846.58258259591</v>
+      </c>
+      <c r="E25">
+        <v>494.9730000000002</v>
+      </c>
+      <c r="F25">
+        <v>1859.573</v>
+      </c>
+      <c r="G25">
+        <v>30.4</v>
+      </c>
+      <c r="H25">
+        <v>6720.5</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>144.1</v>
+      </c>
+      <c r="K25">
+        <v>128.1</v>
+      </c>
+      <c r="L25">
+        <v>16</v>
+      </c>
+      <c r="M25">
+        <v>444.0660324</v>
+      </c>
+      <c r="N25">
+        <v>-428.0660324</v>
+      </c>
+      <c r="O25">
+        <v>-94.17452712799999</v>
+      </c>
+      <c r="P25">
+        <v>-333.891505272</v>
+      </c>
+      <c r="Q25">
+        <v>-205.791505272</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.09767695641550145</v>
+      </c>
+      <c r="T25">
+        <v>0.9955117364226694</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.007926749048955179</v>
+      </c>
+      <c r="W25">
+        <v>0.2369070923271095</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.0360306774952508</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1316998876751713</v>
+      </c>
+      <c r="C26">
+        <v>1853.747232036573</v>
+      </c>
+      <c r="D26">
+        <v>3763.771232036573</v>
+      </c>
+      <c r="E26">
+        <v>575.8240000000001</v>
+      </c>
+      <c r="F26">
+        <v>1940.424</v>
+      </c>
+      <c r="G26">
+        <v>30.4</v>
+      </c>
+      <c r="H26">
+        <v>6720.5</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>144.1</v>
+      </c>
+      <c r="K26">
+        <v>128.1</v>
+      </c>
+      <c r="L26">
+        <v>16</v>
+      </c>
+      <c r="M26">
+        <v>463.3732512</v>
+      </c>
+      <c r="N26">
+        <v>-447.3732512</v>
+      </c>
+      <c r="O26">
+        <v>-98.422115264</v>
+      </c>
+      <c r="P26">
+        <v>-348.951135936</v>
+      </c>
+      <c r="Q26">
+        <v>-220.851135936</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.09845165321044225</v>
+      </c>
+      <c r="T26">
+        <v>1.00861057505981</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.007596467838582047</v>
+      </c>
+      <c r="W26">
+        <v>0.2369859634801466</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.03452939926628207</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1336998876751713</v>
+      </c>
+      <c r="C27">
+        <v>1693.575353493082</v>
+      </c>
+      <c r="D27">
+        <v>3684.450353493082</v>
+      </c>
+      <c r="E27">
+        <v>656.6750000000002</v>
+      </c>
+      <c r="F27">
+        <v>2021.275</v>
+      </c>
+      <c r="G27">
+        <v>30.4</v>
+      </c>
+      <c r="H27">
+        <v>6720.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>144.1</v>
+      </c>
+      <c r="K27">
+        <v>128.1</v>
+      </c>
+      <c r="L27">
+        <v>16</v>
+      </c>
+      <c r="M27">
+        <v>482.6804700000001</v>
+      </c>
+      <c r="N27">
+        <v>-466.6804700000001</v>
+      </c>
+      <c r="O27">
+        <v>-102.6697034</v>
+      </c>
+      <c r="P27">
+        <v>-364.0107666000001</v>
+      </c>
+      <c r="Q27">
+        <v>-235.9107666000001</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.09924700858658148</v>
+      </c>
+      <c r="T27">
+        <v>1.022058716060607</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.007292609125038763</v>
+      </c>
+      <c r="W27">
+        <v>0.2370585249409407</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.03314822329563072</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1356998876751713</v>
+      </c>
+      <c r="C28">
+        <v>1536.677818416712</v>
+      </c>
+      <c r="D28">
+        <v>3608.403818416712</v>
+      </c>
+      <c r="E28">
+        <v>737.5260000000003</v>
+      </c>
+      <c r="F28">
+        <v>2102.126</v>
+      </c>
+      <c r="G28">
+        <v>30.4</v>
+      </c>
+      <c r="H28">
+        <v>6720.5</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>144.1</v>
+      </c>
+      <c r="K28">
+        <v>128.1</v>
+      </c>
+      <c r="L28">
+        <v>16</v>
+      </c>
+      <c r="M28">
+        <v>501.9876888000001</v>
+      </c>
+      <c r="N28">
+        <v>-485.9876888000001</v>
+      </c>
+      <c r="O28">
+        <v>-106.917291536</v>
+      </c>
+      <c r="P28">
+        <v>-379.0703972640001</v>
+      </c>
+      <c r="Q28">
+        <v>-250.9703972640001</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1000638600539677</v>
+      </c>
+      <c r="T28">
+        <v>1.035870320331697</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.007012124158691118</v>
+      </c>
+      <c r="W28">
+        <v>0.2371255047509046</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.03187329163041419</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1376998876751713</v>
+      </c>
+      <c r="C29">
+        <v>1382.855980871008</v>
+      </c>
+      <c r="D29">
+        <v>3535.432980871008</v>
+      </c>
+      <c r="E29">
+        <v>818.3770000000004</v>
+      </c>
+      <c r="F29">
+        <v>2182.977</v>
+      </c>
+      <c r="G29">
+        <v>30.4</v>
+      </c>
+      <c r="H29">
+        <v>6720.5</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>144.1</v>
+      </c>
+      <c r="K29">
+        <v>128.1</v>
+      </c>
+      <c r="L29">
+        <v>16</v>
+      </c>
+      <c r="M29">
+        <v>521.2949076000001</v>
+      </c>
+      <c r="N29">
+        <v>-505.2949076000001</v>
+      </c>
+      <c r="O29">
+        <v>-111.164879672</v>
+      </c>
+      <c r="P29">
+        <v>-394.1300279280001</v>
+      </c>
+      <c r="Q29">
+        <v>-266.0300279280001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1009030910136111</v>
+      </c>
+      <c r="T29">
+        <v>1.050060324719802</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.006752415856517373</v>
+      </c>
+      <c r="W29">
+        <v>0.2371875230934637</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.03069279934780622</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1396998876751713</v>
+      </c>
+      <c r="C30">
+        <v>1231.92694486263</v>
+      </c>
+      <c r="D30">
+        <v>3465.35494486263</v>
+      </c>
+      <c r="E30">
+        <v>899.2280000000005</v>
+      </c>
+      <c r="F30">
+        <v>2263.828</v>
+      </c>
+      <c r="G30">
+        <v>30.4</v>
+      </c>
+      <c r="H30">
+        <v>6720.5</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>144.1</v>
+      </c>
+      <c r="K30">
+        <v>128.1</v>
+      </c>
+      <c r="L30">
+        <v>16</v>
+      </c>
+      <c r="M30">
+        <v>540.6021264000001</v>
+      </c>
+      <c r="N30">
+        <v>-524.6021264000001</v>
+      </c>
+      <c r="O30">
+        <v>-115.412467808</v>
+      </c>
+      <c r="P30">
+        <v>-409.1896585920001</v>
+      </c>
+      <c r="Q30">
+        <v>-281.0896585920001</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1017656339443557</v>
+      </c>
+      <c r="T30">
+        <v>1.064644495896466</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.006511258147356039</v>
+      </c>
+      <c r="W30">
+        <v>0.2372451115544114</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.02959662794252749</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1416998876751713</v>
+      </c>
+      <c r="C31">
+        <v>1083.722033732971</v>
+      </c>
+      <c r="D31">
+        <v>3398.001033732971</v>
+      </c>
+      <c r="E31">
+        <v>980.0790000000002</v>
+      </c>
+      <c r="F31">
+        <v>2344.679</v>
+      </c>
+      <c r="G31">
+        <v>30.4</v>
+      </c>
+      <c r="H31">
+        <v>6720.5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>144.1</v>
+      </c>
+      <c r="K31">
+        <v>128.1</v>
+      </c>
+      <c r="L31">
+        <v>16</v>
+      </c>
+      <c r="M31">
+        <v>559.9093452000001</v>
+      </c>
+      <c r="N31">
+        <v>-543.9093452000001</v>
+      </c>
+      <c r="O31">
+        <v>-119.660055944</v>
+      </c>
+      <c r="P31">
+        <v>-424.2492892560001</v>
+      </c>
+      <c r="Q31">
+        <v>-296.1492892560001</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.102652473859065</v>
+      </c>
+      <c r="T31">
+        <v>1.079639488796416</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.006286732004343761</v>
+      </c>
+      <c r="W31">
+        <v>0.2372987283973627</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.02857605456519896</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1436998876751713</v>
+      </c>
+      <c r="C32">
+        <v>938.0854346433875</v>
+      </c>
+      <c r="D32">
+        <v>3333.215434643388</v>
+      </c>
+      <c r="E32">
+        <v>1060.93</v>
+      </c>
+      <c r="F32">
+        <v>2425.53</v>
+      </c>
+      <c r="G32">
+        <v>30.4</v>
+      </c>
+      <c r="H32">
+        <v>6720.5</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>144.1</v>
+      </c>
+      <c r="K32">
+        <v>128.1</v>
+      </c>
+      <c r="L32">
+        <v>16</v>
+      </c>
+      <c r="M32">
+        <v>579.2165640000001</v>
+      </c>
+      <c r="N32">
+        <v>-563.2165640000001</v>
+      </c>
+      <c r="O32">
+        <v>-123.90764408</v>
+      </c>
+      <c r="P32">
+        <v>-439.3089199200001</v>
+      </c>
+      <c r="Q32">
+        <v>-311.2089199200001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1035646520570516</v>
+      </c>
+      <c r="T32">
+        <v>1.095062910064937</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.006077174270865637</v>
+      </c>
+      <c r="W32">
+        <v>0.2373487707841173</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.02762351941302565</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1456998876751713</v>
+      </c>
+      <c r="C33">
+        <v>794.8729952231374</v>
+      </c>
+      <c r="D33">
+        <v>3270.853995223138</v>
+      </c>
+      <c r="E33">
+        <v>1141.781</v>
+      </c>
+      <c r="F33">
+        <v>2506.381</v>
+      </c>
+      <c r="G33">
+        <v>30.4</v>
+      </c>
+      <c r="H33">
+        <v>6720.5</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>144.1</v>
+      </c>
+      <c r="K33">
+        <v>128.1</v>
+      </c>
+      <c r="L33">
+        <v>16</v>
+      </c>
+      <c r="M33">
+        <v>598.5237828</v>
+      </c>
+      <c r="N33">
+        <v>-582.5237828</v>
+      </c>
+      <c r="O33">
+        <v>-128.155232216</v>
+      </c>
+      <c r="P33">
+        <v>-454.368550584</v>
+      </c>
+      <c r="Q33">
+        <v>-326.2685505840001</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1045032702028059</v>
+      </c>
+      <c r="T33">
+        <v>1.110933387022399</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.005881136391160293</v>
+      </c>
+      <c r="W33">
+        <v>0.2373955846297909</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.02673243814163773</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1476998876751713</v>
+      </c>
+      <c r="C34">
+        <v>653.9511528182402</v>
+      </c>
+      <c r="D34">
+        <v>3210.78315281824</v>
+      </c>
+      <c r="E34">
+        <v>1222.632</v>
+      </c>
+      <c r="F34">
+        <v>2587.232</v>
+      </c>
+      <c r="G34">
+        <v>30.4</v>
+      </c>
+      <c r="H34">
+        <v>6720.5</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>144.1</v>
+      </c>
+      <c r="K34">
+        <v>128.1</v>
+      </c>
+      <c r="L34">
+        <v>16</v>
+      </c>
+      <c r="M34">
+        <v>617.8310016</v>
+      </c>
+      <c r="N34">
+        <v>-601.8310016</v>
+      </c>
+      <c r="O34">
+        <v>-132.402820352</v>
+      </c>
+      <c r="P34">
+        <v>-469.428181248</v>
+      </c>
+      <c r="Q34">
+        <v>-341.3281812480001</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1054694947646119</v>
+      </c>
+      <c r="T34">
+        <v>1.127270642713905</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.005697350878936534</v>
+      </c>
+      <c r="W34">
+        <v>0.23743947261011</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.0258970494497115</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1496998876751713</v>
+      </c>
+      <c r="C35">
+        <v>515.195979601714</v>
+      </c>
+      <c r="D35">
+        <v>3152.878979601714</v>
+      </c>
+      <c r="E35">
+        <v>1303.483</v>
+      </c>
+      <c r="F35">
+        <v>2668.083</v>
+      </c>
+      <c r="G35">
+        <v>30.4</v>
+      </c>
+      <c r="H35">
+        <v>6720.5</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>144.1</v>
+      </c>
+      <c r="K35">
+        <v>128.1</v>
+      </c>
+      <c r="L35">
+        <v>16</v>
+      </c>
+      <c r="M35">
+        <v>637.1382204</v>
+      </c>
+      <c r="N35">
+        <v>-621.1382204</v>
+      </c>
+      <c r="O35">
+        <v>-136.650408488</v>
+      </c>
+      <c r="P35">
+        <v>-484.487811912</v>
+      </c>
+      <c r="Q35">
+        <v>-356.3878119120001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1064645618506509</v>
+      </c>
+      <c r="T35">
+        <v>1.144095577679784</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.005524703882605125</v>
+      </c>
+      <c r="W35">
+        <v>0.2374807007128339</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.0251122903754778</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1516998876751713</v>
+      </c>
+      <c r="C36">
+        <v>378.492329177951</v>
+      </c>
+      <c r="D36">
+        <v>3097.026329177951</v>
+      </c>
+      <c r="E36">
+        <v>1384.334</v>
+      </c>
+      <c r="F36">
+        <v>2748.934</v>
+      </c>
+      <c r="G36">
+        <v>30.4</v>
+      </c>
+      <c r="H36">
+        <v>6720.5</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>144.1</v>
+      </c>
+      <c r="K36">
+        <v>128.1</v>
+      </c>
+      <c r="L36">
+        <v>16</v>
+      </c>
+      <c r="M36">
+        <v>656.4454392000001</v>
+      </c>
+      <c r="N36">
+        <v>-640.4454392000001</v>
+      </c>
+      <c r="O36">
+        <v>-140.897996624</v>
+      </c>
+      <c r="P36">
+        <v>-499.5474425760001</v>
+      </c>
+      <c r="Q36">
+        <v>-371.4474425760001</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1074897824847517</v>
+      </c>
+      <c r="T36">
+        <v>1.161430359159781</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.005362212591940267</v>
+      </c>
+      <c r="W36">
+        <v>0.2375195036330447</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.02437369359972852</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1536998876751713</v>
+      </c>
+      <c r="C37">
+        <v>243.7330723146638</v>
+      </c>
+      <c r="D37">
+        <v>3043.118072314664</v>
+      </c>
+      <c r="E37">
+        <v>1465.185</v>
+      </c>
+      <c r="F37">
+        <v>2829.785</v>
+      </c>
+      <c r="G37">
+        <v>30.4</v>
+      </c>
+      <c r="H37">
+        <v>6720.5</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>144.1</v>
+      </c>
+      <c r="K37">
+        <v>128.1</v>
+      </c>
+      <c r="L37">
+        <v>16</v>
+      </c>
+      <c r="M37">
+        <v>675.7526580000001</v>
+      </c>
+      <c r="N37">
+        <v>-659.7526580000001</v>
+      </c>
+      <c r="O37">
+        <v>-145.14558476</v>
+      </c>
+      <c r="P37">
+        <v>-514.6070732400001</v>
+      </c>
+      <c r="Q37">
+        <v>-386.5070732400001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1085465483691325</v>
+      </c>
+      <c r="T37">
+        <v>1.17929851853147</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.005209006517884831</v>
+      </c>
+      <c r="W37">
+        <v>0.2375560892435291</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.02367730235402199</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1556998876751713</v>
+      </c>
+      <c r="C38">
+        <v>110.8184111284272</v>
+      </c>
+      <c r="D38">
+        <v>2991.054411128427</v>
+      </c>
+      <c r="E38">
+        <v>1546.036</v>
+      </c>
+      <c r="F38">
+        <v>2910.636</v>
+      </c>
+      <c r="G38">
+        <v>30.4</v>
+      </c>
+      <c r="H38">
+        <v>6720.5</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>144.1</v>
+      </c>
+      <c r="K38">
+        <v>128.1</v>
+      </c>
+      <c r="L38">
+        <v>16</v>
+      </c>
+      <c r="M38">
+        <v>695.0598768</v>
+      </c>
+      <c r="N38">
+        <v>-679.0598768</v>
+      </c>
+      <c r="O38">
+        <v>-149.393172896</v>
+      </c>
+      <c r="P38">
+        <v>-529.666703904</v>
+      </c>
+      <c r="Q38">
+        <v>-401.566703904</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1096363381874002</v>
+      </c>
+      <c r="T38">
+        <v>1.197725057883524</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.005064311892388031</v>
+      </c>
+      <c r="W38">
+        <v>0.2375906423200978</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.02301959951085464</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1576998876751713</v>
+      </c>
+      <c r="C39">
+        <v>-20.34473751379664</v>
+      </c>
+      <c r="D39">
+        <v>2940.742262486203</v>
+      </c>
+      <c r="E39">
+        <v>1626.887</v>
+      </c>
+      <c r="F39">
+        <v>2991.487</v>
+      </c>
+      <c r="G39">
+        <v>30.4</v>
+      </c>
+      <c r="H39">
+        <v>6720.5</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>144.1</v>
+      </c>
+      <c r="K39">
+        <v>128.1</v>
+      </c>
+      <c r="L39">
+        <v>16</v>
+      </c>
+      <c r="M39">
+        <v>714.3670956000001</v>
+      </c>
+      <c r="N39">
+        <v>-698.3670956000001</v>
+      </c>
+      <c r="O39">
+        <v>-153.640761032</v>
+      </c>
+      <c r="P39">
+        <v>-544.7263345680001</v>
+      </c>
+      <c r="Q39">
+        <v>-416.6263345680001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1107607245078351</v>
+      </c>
+      <c r="T39">
+        <v>1.216736566738818</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.004927438597999164</v>
+      </c>
+      <c r="W39">
+        <v>0.2376233276627978</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.02239744817272349</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1596998876751713</v>
+      </c>
+      <c r="C40">
+        <v>-149.843297392219</v>
+      </c>
+      <c r="D40">
+        <v>2892.094702607781</v>
+      </c>
+      <c r="E40">
+        <v>1707.738</v>
+      </c>
+      <c r="F40">
+        <v>3072.338</v>
+      </c>
+      <c r="G40">
+        <v>30.4</v>
+      </c>
+      <c r="H40">
+        <v>6720.5</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>144.1</v>
+      </c>
+      <c r="K40">
+        <v>128.1</v>
+      </c>
+      <c r="L40">
+        <v>16</v>
+      </c>
+      <c r="M40">
+        <v>733.6743144000001</v>
+      </c>
+      <c r="N40">
+        <v>-717.6743144000001</v>
+      </c>
+      <c r="O40">
+        <v>-157.888349168</v>
+      </c>
+      <c r="P40">
+        <v>-559.7859652320001</v>
+      </c>
+      <c r="Q40">
+        <v>-431.6859652320001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1119213813547357</v>
+      </c>
+      <c r="T40">
+        <v>1.236361350073315</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.004797769161209713</v>
+      </c>
+      <c r="W40">
+        <v>0.2376542927243031</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.02180804164186234</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1616998876751713</v>
+      </c>
+      <c r="C41">
+        <v>-277.7585341025351</v>
+      </c>
+      <c r="D41">
+        <v>2845.030465897465</v>
+      </c>
+      <c r="E41">
+        <v>1788.589</v>
+      </c>
+      <c r="F41">
+        <v>3153.189</v>
+      </c>
+      <c r="G41">
+        <v>30.4</v>
+      </c>
+      <c r="H41">
+        <v>6720.5</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>144.1</v>
+      </c>
+      <c r="K41">
+        <v>128.1</v>
+      </c>
+      <c r="L41">
+        <v>16</v>
+      </c>
+      <c r="M41">
+        <v>752.9815332000001</v>
+      </c>
+      <c r="N41">
+        <v>-736.9815332000001</v>
+      </c>
+      <c r="O41">
+        <v>-162.135937304</v>
+      </c>
+      <c r="P41">
+        <v>-574.8455958960001</v>
+      </c>
+      <c r="Q41">
+        <v>-446.7455958960001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1131200925244854</v>
+      </c>
+      <c r="T41">
+        <v>1.256629568926976</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.004674749439127413</v>
+      </c>
+      <c r="W41">
+        <v>0.2376836698339364</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.02124886108694279</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1636998876751713</v>
+      </c>
+      <c r="C42">
+        <v>-404.1665080735061</v>
+      </c>
+      <c r="D42">
+        <v>2799.473491926494</v>
+      </c>
+      <c r="E42">
+        <v>1869.440000000001</v>
+      </c>
+      <c r="F42">
+        <v>3234.04</v>
+      </c>
+      <c r="G42">
+        <v>30.4</v>
+      </c>
+      <c r="H42">
+        <v>6720.5</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>144.1</v>
+      </c>
+      <c r="K42">
+        <v>128.1</v>
+      </c>
+      <c r="L42">
+        <v>16</v>
+      </c>
+      <c r="M42">
+        <v>772.2887520000002</v>
+      </c>
+      <c r="N42">
+        <v>-756.2887520000002</v>
+      </c>
+      <c r="O42">
+        <v>-166.38352544</v>
+      </c>
+      <c r="P42">
+        <v>-589.9052265600001</v>
+      </c>
+      <c r="Q42">
+        <v>-461.8052265600001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1143587607332268</v>
+      </c>
+      <c r="T42">
+        <v>1.277573395075759</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.004557880703149227</v>
+      </c>
+      <c r="W42">
+        <v>0.237711578088088</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.02071763955976924</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1656998876751713</v>
+      </c>
+      <c r="C43">
+        <v>-529.1384847459585</v>
+      </c>
+      <c r="D43">
+        <v>2755.352515254042</v>
+      </c>
+      <c r="E43">
+        <v>1950.291000000001</v>
+      </c>
+      <c r="F43">
+        <v>3314.891000000001</v>
+      </c>
+      <c r="G43">
+        <v>30.4</v>
+      </c>
+      <c r="H43">
+        <v>6720.5</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>144.1</v>
+      </c>
+      <c r="K43">
+        <v>128.1</v>
+      </c>
+      <c r="L43">
+        <v>16</v>
+      </c>
+      <c r="M43">
+        <v>791.5959708000001</v>
+      </c>
+      <c r="N43">
+        <v>-775.5959708000001</v>
+      </c>
+      <c r="O43">
+        <v>-170.631113576</v>
+      </c>
+      <c r="P43">
+        <v>-604.9648572240001</v>
+      </c>
+      <c r="Q43">
+        <v>-476.864857224</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.115639417694807</v>
+      </c>
+      <c r="T43">
+        <v>1.299227181432975</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.004446712881121197</v>
+      </c>
+      <c r="W43">
+        <v>0.2377381249639883</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.02021233127782363</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1676998876751713</v>
+      </c>
+      <c r="C44">
+        <v>-652.7413065659666</v>
+      </c>
+      <c r="D44">
+        <v>2712.600693434033</v>
+      </c>
+      <c r="E44">
+        <v>2031.142</v>
+      </c>
+      <c r="F44">
+        <v>3395.742</v>
+      </c>
+      <c r="G44">
+        <v>30.4</v>
+      </c>
+      <c r="H44">
+        <v>6720.5</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>144.1</v>
+      </c>
+      <c r="K44">
+        <v>128.1</v>
+      </c>
+      <c r="L44">
+        <v>16</v>
+      </c>
+      <c r="M44">
+        <v>810.9031896000001</v>
+      </c>
+      <c r="N44">
+        <v>-794.9031896000001</v>
+      </c>
+      <c r="O44">
+        <v>-174.878701712</v>
+      </c>
+      <c r="P44">
+        <v>-620.0244878880001</v>
+      </c>
+      <c r="Q44">
+        <v>-491.924487888</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1169642352412692</v>
+      </c>
+      <c r="T44">
+        <v>1.321627650078371</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.004340838764904025</v>
+      </c>
+      <c r="W44">
+        <v>0.2377634077029409</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.01973108529501832</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1696998876751713</v>
+      </c>
+      <c r="C45">
+        <v>-775.0377308762663</v>
+      </c>
+      <c r="D45">
+        <v>2671.155269123734</v>
+      </c>
+      <c r="E45">
+        <v>2111.993</v>
+      </c>
+      <c r="F45">
+        <v>3476.593</v>
+      </c>
+      <c r="G45">
+        <v>30.4</v>
+      </c>
+      <c r="H45">
+        <v>6720.5</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>144.1</v>
+      </c>
+      <c r="K45">
+        <v>128.1</v>
+      </c>
+      <c r="L45">
+        <v>16</v>
+      </c>
+      <c r="M45">
+        <v>830.2104084000001</v>
+      </c>
+      <c r="N45">
+        <v>-814.2104084000001</v>
+      </c>
+      <c r="O45">
+        <v>-179.126289848</v>
+      </c>
+      <c r="P45">
+        <v>-635.0841185520001</v>
+      </c>
+      <c r="Q45">
+        <v>-506.984118552</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.118335537613923</v>
+      </c>
+      <c r="T45">
+        <v>1.344814100079746</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.004239889026185328</v>
+      </c>
+      <c r="W45">
+        <v>0.2377875145005469</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.01927222284629693</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1716998876751713</v>
+      </c>
+      <c r="C46">
+        <v>-896.0867372982502</v>
+      </c>
+      <c r="D46">
+        <v>2630.95726270175</v>
+      </c>
+      <c r="E46">
+        <v>2192.844</v>
+      </c>
+      <c r="F46">
+        <v>3557.444</v>
+      </c>
+      <c r="G46">
+        <v>30.4</v>
+      </c>
+      <c r="H46">
+        <v>6720.5</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>144.1</v>
+      </c>
+      <c r="K46">
+        <v>128.1</v>
+      </c>
+      <c r="L46">
+        <v>16</v>
+      </c>
+      <c r="M46">
+        <v>849.5176272</v>
+      </c>
+      <c r="N46">
+        <v>-833.5176272</v>
+      </c>
+      <c r="O46">
+        <v>-183.373877984</v>
+      </c>
+      <c r="P46">
+        <v>-650.1437492160001</v>
+      </c>
+      <c r="Q46">
+        <v>-522.043749216</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1197558150713145</v>
+      </c>
+      <c r="T46">
+        <v>1.36882863758117</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.004143527911953843</v>
+      </c>
+      <c r="W46">
+        <v>0.2378105255346254</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.01883421778160843</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1736998876751713</v>
+      </c>
+      <c r="C47">
+        <v>-1015.943807770851</v>
+      </c>
+      <c r="D47">
+        <v>2591.951192229149</v>
+      </c>
+      <c r="E47">
+        <v>2273.695</v>
+      </c>
+      <c r="F47">
+        <v>3638.295</v>
+      </c>
+      <c r="G47">
+        <v>30.4</v>
+      </c>
+      <c r="H47">
+        <v>6720.5</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>144.1</v>
+      </c>
+      <c r="K47">
+        <v>128.1</v>
+      </c>
+      <c r="L47">
+        <v>16</v>
+      </c>
+      <c r="M47">
+        <v>868.8248460000001</v>
+      </c>
+      <c r="N47">
+        <v>-852.8248460000001</v>
+      </c>
+      <c r="O47">
+        <v>-187.62146612</v>
+      </c>
+      <c r="P47">
+        <v>-665.2033798800001</v>
+      </c>
+      <c r="Q47">
+        <v>-537.10337988</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.121227738981702</v>
+      </c>
+      <c r="T47">
+        <v>1.393716430991737</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.004051449513910424</v>
+      </c>
+      <c r="W47">
+        <v>0.2378325138560782</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.01841567960868373</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1756998876751713</v>
+      </c>
+      <c r="C48">
+        <v>-1134.661182042526</v>
+      </c>
+      <c r="D48">
+        <v>2554.084817957475</v>
+      </c>
+      <c r="E48">
+        <v>2354.546</v>
+      </c>
+      <c r="F48">
+        <v>3719.146</v>
+      </c>
+      <c r="G48">
+        <v>30.4</v>
+      </c>
+      <c r="H48">
+        <v>6720.5</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>144.1</v>
+      </c>
+      <c r="K48">
+        <v>128.1</v>
+      </c>
+      <c r="L48">
+        <v>16</v>
+      </c>
+      <c r="M48">
+        <v>888.1320648000001</v>
+      </c>
+      <c r="N48">
+        <v>-872.1320648000001</v>
+      </c>
+      <c r="O48">
+        <v>-191.869054256</v>
+      </c>
+      <c r="P48">
+        <v>-680.2630105440001</v>
+      </c>
+      <c r="Q48">
+        <v>-552.163010544</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1227541785924743</v>
+      </c>
+      <c r="T48">
+        <v>1.419525994528621</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.003963374524477589</v>
+      </c>
+      <c r="W48">
+        <v>0.2378535461635548</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.0180153387476254</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1776998876751713</v>
+      </c>
+      <c r="C49">
+        <v>-1252.288091090492</v>
+      </c>
+      <c r="D49">
+        <v>2517.308908909508</v>
+      </c>
+      <c r="E49">
+        <v>2435.397</v>
+      </c>
+      <c r="F49">
+        <v>3799.997</v>
+      </c>
+      <c r="G49">
+        <v>30.4</v>
+      </c>
+      <c r="H49">
+        <v>6720.5</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>144.1</v>
+      </c>
+      <c r="K49">
+        <v>128.1</v>
+      </c>
+      <c r="L49">
+        <v>16</v>
+      </c>
+      <c r="M49">
+        <v>907.4392836000001</v>
+      </c>
+      <c r="N49">
+        <v>-891.4392836000001</v>
+      </c>
+      <c r="O49">
+        <v>-196.116642392</v>
+      </c>
+      <c r="P49">
+        <v>-695.3226412080001</v>
+      </c>
+      <c r="Q49">
+        <v>-567.222641208</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1243382196979926</v>
+      </c>
+      <c r="T49">
+        <v>1.44630950385935</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.003879047406935513</v>
+      </c>
+      <c r="W49">
+        <v>0.2378736834792238</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.01763203366788868</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1796998876751713</v>
+      </c>
+      <c r="C50">
+        <v>-1368.870970660373</v>
+      </c>
+      <c r="D50">
+        <v>2481.577029339627</v>
+      </c>
+      <c r="E50">
+        <v>2516.248</v>
+      </c>
+      <c r="F50">
+        <v>3880.848</v>
+      </c>
+      <c r="G50">
+        <v>30.4</v>
+      </c>
+      <c r="H50">
+        <v>6720.5</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>144.1</v>
+      </c>
+      <c r="K50">
+        <v>128.1</v>
+      </c>
+      <c r="L50">
+        <v>16</v>
+      </c>
+      <c r="M50">
+        <v>926.7465024000001</v>
+      </c>
+      <c r="N50">
+        <v>-910.7465024000001</v>
+      </c>
+      <c r="O50">
+        <v>-200.364230528</v>
+      </c>
+      <c r="P50">
+        <v>-710.382271872</v>
+      </c>
+      <c r="Q50">
+        <v>-582.282271872</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1259831854614156</v>
+      </c>
+      <c r="T50">
+        <v>1.474123148164337</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.003798233919291023</v>
+      </c>
+      <c r="W50">
+        <v>0.2378929817400733</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.01726469963314103</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1816998876751713</v>
+      </c>
+      <c r="C51">
+        <v>-1484.453656873879</v>
+      </c>
+      <c r="D51">
+        <v>2446.845343126121</v>
+      </c>
+      <c r="E51">
+        <v>2597.099</v>
+      </c>
+      <c r="F51">
+        <v>3961.699</v>
+      </c>
+      <c r="G51">
+        <v>30.4</v>
+      </c>
+      <c r="H51">
+        <v>6720.5</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>144.1</v>
+      </c>
+      <c r="K51">
+        <v>128.1</v>
+      </c>
+      <c r="L51">
+        <v>16</v>
+      </c>
+      <c r="M51">
+        <v>946.0537212</v>
+      </c>
+      <c r="N51">
+        <v>-930.0537212</v>
+      </c>
+      <c r="O51">
+        <v>-204.611818664</v>
+      </c>
+      <c r="P51">
+        <v>-725.441902536</v>
+      </c>
+      <c r="Q51">
+        <v>-597.341902536</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1276926596861492</v>
+      </c>
+      <c r="T51">
+        <v>1.50302752361854</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.003720718941346308</v>
+      </c>
+      <c r="W51">
+        <v>0.2379114923168065</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.01691235882430142</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1836998876751713</v>
+      </c>
+      <c r="C52">
+        <v>-1599.077565637084</v>
+      </c>
+      <c r="D52">
+        <v>2413.072434362916</v>
+      </c>
+      <c r="E52">
+        <v>2677.95</v>
+      </c>
+      <c r="F52">
+        <v>4042.55</v>
+      </c>
+      <c r="G52">
+        <v>30.4</v>
+      </c>
+      <c r="H52">
+        <v>6720.5</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>144.1</v>
+      </c>
+      <c r="K52">
+        <v>128.1</v>
+      </c>
+      <c r="L52">
+        <v>16</v>
+      </c>
+      <c r="M52">
+        <v>965.3609400000001</v>
+      </c>
+      <c r="N52">
+        <v>-949.3609400000001</v>
+      </c>
+      <c r="O52">
+        <v>-208.8594068</v>
+      </c>
+      <c r="P52">
+        <v>-740.5015332000002</v>
+      </c>
+      <c r="Q52">
+        <v>-612.4015332000001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1294705128798722</v>
+      </c>
+      <c r="T52">
+        <v>1.533088074090911</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.003646304562519382</v>
+      </c>
+      <c r="W52">
+        <v>0.2379292624704704</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.01657411164781541</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1856998876751713</v>
+      </c>
+      <c r="C53">
+        <v>-1712.781857393151</v>
+      </c>
+      <c r="D53">
+        <v>2380.219142606848</v>
+      </c>
+      <c r="E53">
+        <v>2758.801</v>
+      </c>
+      <c r="F53">
+        <v>4123.401</v>
+      </c>
+      <c r="G53">
+        <v>30.4</v>
+      </c>
+      <c r="H53">
+        <v>6720.5</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>144.1</v>
+      </c>
+      <c r="K53">
+        <v>128.1</v>
+      </c>
+      <c r="L53">
+        <v>16</v>
+      </c>
+      <c r="M53">
+        <v>984.6681588</v>
+      </c>
+      <c r="N53">
+        <v>-968.6681588</v>
+      </c>
+      <c r="O53">
+        <v>-213.106994936</v>
+      </c>
+      <c r="P53">
+        <v>-755.561163864</v>
+      </c>
+      <c r="Q53">
+        <v>-627.461163864</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1313209315100737</v>
+      </c>
+      <c r="T53">
+        <v>1.564375585807052</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.003574808394626845</v>
+      </c>
+      <c r="W53">
+        <v>0.2379463357553631</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.01624912906648568</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1876998876751713</v>
+      </c>
+      <c r="C54">
+        <v>-1825.603588597454</v>
+      </c>
+      <c r="D54">
+        <v>2348.248411402546</v>
+      </c>
+      <c r="E54">
+        <v>2839.652</v>
+      </c>
+      <c r="F54">
+        <v>4204.252</v>
+      </c>
+      <c r="G54">
+        <v>30.4</v>
+      </c>
+      <c r="H54">
+        <v>6720.5</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>144.1</v>
+      </c>
+      <c r="K54">
+        <v>128.1</v>
+      </c>
+      <c r="L54">
+        <v>16</v>
+      </c>
+      <c r="M54">
+        <v>1003.9753776</v>
+      </c>
+      <c r="N54">
+        <v>-987.9753776000001</v>
+      </c>
+      <c r="O54">
+        <v>-217.354583072</v>
+      </c>
+      <c r="P54">
+        <v>-770.6207945280001</v>
+      </c>
+      <c r="Q54">
+        <v>-642.5207945280001</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1332484509165336</v>
+      </c>
+      <c r="T54">
+        <v>1.596966743844699</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.003506062079345559</v>
+      </c>
+      <c r="W54">
+        <v>0.2379627523754523</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.01593664581520704</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1896998876751713</v>
+      </c>
+      <c r="C55">
+        <v>-1937.577851146957</v>
+      </c>
+      <c r="D55">
+        <v>2317.125148853043</v>
+      </c>
+      <c r="E55">
+        <v>2920.503</v>
+      </c>
+      <c r="F55">
+        <v>4285.103</v>
+      </c>
+      <c r="G55">
+        <v>30.4</v>
+      </c>
+      <c r="H55">
+        <v>6720.5</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>144.1</v>
+      </c>
+      <c r="K55">
+        <v>128.1</v>
+      </c>
+      <c r="L55">
+        <v>16</v>
+      </c>
+      <c r="M55">
+        <v>1023.2825964</v>
+      </c>
+      <c r="N55">
+        <v>-1007.2825964</v>
+      </c>
+      <c r="O55">
+        <v>-221.602171208</v>
+      </c>
+      <c r="P55">
+        <v>-785.6804251920001</v>
+      </c>
+      <c r="Q55">
+        <v>-657.5804251920001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.135257992425396</v>
+      </c>
+      <c r="T55">
+        <v>1.630944759671182</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.003439909964640926</v>
+      </c>
+      <c r="W55">
+        <v>0.2379785495004438</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.01563595438473153</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1916998876751713</v>
+      </c>
+      <c r="C56">
+        <v>-2048.737900866808</v>
+      </c>
+      <c r="D56">
+        <v>2286.816099133193</v>
+      </c>
+      <c r="E56">
+        <v>3001.354000000001</v>
+      </c>
+      <c r="F56">
+        <v>4365.954000000001</v>
+      </c>
+      <c r="G56">
+        <v>30.4</v>
+      </c>
+      <c r="H56">
+        <v>6720.5</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>144.1</v>
+      </c>
+      <c r="K56">
+        <v>128.1</v>
+      </c>
+      <c r="L56">
+        <v>16</v>
+      </c>
+      <c r="M56">
+        <v>1042.5898152</v>
+      </c>
+      <c r="N56">
+        <v>-1026.5898152</v>
+      </c>
+      <c r="O56">
+        <v>-225.849759344</v>
+      </c>
+      <c r="P56">
+        <v>-800.7400558560003</v>
+      </c>
+      <c r="Q56">
+        <v>-672.6400558560002</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1373549053042089</v>
+      </c>
+      <c r="T56">
+        <v>1.666400080533599</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.003376207928258686</v>
+      </c>
+      <c r="W56">
+        <v>0.2379937615467319</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.01534639967390317</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1936998876751713</v>
+      </c>
+      <c r="C57">
+        <v>-2159.115276043123</v>
+      </c>
+      <c r="D57">
+        <v>2257.289723956877</v>
+      </c>
+      <c r="E57">
+        <v>3082.205</v>
+      </c>
+      <c r="F57">
+        <v>4446.805</v>
+      </c>
+      <c r="G57">
+        <v>30.4</v>
+      </c>
+      <c r="H57">
+        <v>6720.5</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>144.1</v>
+      </c>
+      <c r="K57">
+        <v>128.1</v>
+      </c>
+      <c r="L57">
+        <v>16</v>
+      </c>
+      <c r="M57">
+        <v>1061.897034</v>
+      </c>
+      <c r="N57">
+        <v>-1045.897034</v>
+      </c>
+      <c r="O57">
+        <v>-230.09734748</v>
+      </c>
+      <c r="P57">
+        <v>-815.79968652</v>
+      </c>
+      <c r="Q57">
+        <v>-687.69968652</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1395450143109692</v>
+      </c>
+      <c r="T57">
+        <v>1.703431193434346</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.003314822329563075</v>
+      </c>
+      <c r="W57">
+        <v>0.2380084204277003</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.0150673742252867</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1956998876751713</v>
+      </c>
+      <c r="C58">
+        <v>-2268.739906890204</v>
+      </c>
+      <c r="D58">
+        <v>2228.516093109797</v>
+      </c>
+      <c r="E58">
+        <v>3163.056000000001</v>
+      </c>
+      <c r="F58">
+        <v>4527.656000000001</v>
+      </c>
+      <c r="G58">
+        <v>30.4</v>
+      </c>
+      <c r="H58">
+        <v>6720.5</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>144.1</v>
+      </c>
+      <c r="K58">
+        <v>128.1</v>
+      </c>
+      <c r="L58">
+        <v>16</v>
+      </c>
+      <c r="M58">
+        <v>1081.2042528</v>
+      </c>
+      <c r="N58">
+        <v>-1065.2042528</v>
+      </c>
+      <c r="O58">
+        <v>-234.344935616</v>
+      </c>
+      <c r="P58">
+        <v>-830.8593171840001</v>
+      </c>
+      <c r="Q58">
+        <v>-702.7593171840001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1418346737271275</v>
+      </c>
+      <c r="T58">
+        <v>1.742145538739672</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.003255629073678019</v>
+      </c>
+      <c r="W58">
+        <v>0.2380225557772057</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.01479831397126374</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1976998876751713</v>
+      </c>
+      <c r="C59">
+        <v>-2377.64021675083</v>
+      </c>
+      <c r="D59">
+        <v>2200.46678324917</v>
+      </c>
+      <c r="E59">
+        <v>3243.907000000001</v>
+      </c>
+      <c r="F59">
+        <v>4608.507000000001</v>
+      </c>
+      <c r="G59">
+        <v>30.4</v>
+      </c>
+      <c r="H59">
+        <v>6720.5</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>144.1</v>
+      </c>
+      <c r="K59">
+        <v>128.1</v>
+      </c>
+      <c r="L59">
+        <v>16</v>
+      </c>
+      <c r="M59">
+        <v>1100.5114716</v>
+      </c>
+      <c r="N59">
+        <v>-1084.5114716</v>
+      </c>
+      <c r="O59">
+        <v>-238.592523752</v>
+      </c>
+      <c r="P59">
+        <v>-845.9189478480002</v>
+      </c>
+      <c r="Q59">
+        <v>-717.8189478480002</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.144230828930084</v>
+      </c>
+      <c r="T59">
+        <v>1.782660551268501</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.003198512774139808</v>
+      </c>
+      <c r="W59">
+        <v>0.2380361951495354</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.01453869442790823</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1996998876751713</v>
+      </c>
+      <c r="C60">
+        <v>-2485.843215749008</v>
+      </c>
+      <c r="D60">
+        <v>2173.114784250992</v>
+      </c>
+      <c r="E60">
+        <v>3324.758</v>
+      </c>
+      <c r="F60">
+        <v>4689.358</v>
+      </c>
+      <c r="G60">
+        <v>30.4</v>
+      </c>
+      <c r="H60">
+        <v>6720.5</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>144.1</v>
+      </c>
+      <c r="K60">
+        <v>128.1</v>
+      </c>
+      <c r="L60">
+        <v>16</v>
+      </c>
+      <c r="M60">
+        <v>1119.8186904</v>
+      </c>
+      <c r="N60">
+        <v>-1103.8186904</v>
+      </c>
+      <c r="O60">
+        <v>-242.840111888</v>
+      </c>
+      <c r="P60">
+        <v>-860.9785785120001</v>
+      </c>
+      <c r="Q60">
+        <v>-732.8785785120001</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1467410867617526</v>
+      </c>
+      <c r="T60">
+        <v>1.825104850108227</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.003143366002171881</v>
+      </c>
+      <c r="W60">
+        <v>0.2380493641986814</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.01428802728259948</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2016998876751713</v>
+      </c>
+      <c r="C61">
+        <v>-2593.374587543791</v>
+      </c>
+      <c r="D61">
+        <v>2146.434412456209</v>
+      </c>
+      <c r="E61">
+        <v>3405.609</v>
+      </c>
+      <c r="F61">
+        <v>4770.209</v>
+      </c>
+      <c r="G61">
+        <v>30.4</v>
+      </c>
+      <c r="H61">
+        <v>6720.5</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>144.1</v>
+      </c>
+      <c r="K61">
+        <v>128.1</v>
+      </c>
+      <c r="L61">
+        <v>16</v>
+      </c>
+      <c r="M61">
+        <v>1139.1259092</v>
+      </c>
+      <c r="N61">
+        <v>-1123.1259092</v>
+      </c>
+      <c r="O61">
+        <v>-247.087700024</v>
+      </c>
+      <c r="P61">
+        <v>-876.038209176</v>
+      </c>
+      <c r="Q61">
+        <v>-747.938209176</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1493737961949661</v>
+      </c>
+      <c r="T61">
+        <v>1.869619602549891</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.003090088612304561</v>
+      </c>
+      <c r="W61">
+        <v>0.2380620868393817</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.01404585732865715</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2036998876751713</v>
+      </c>
+      <c r="C62">
+        <v>-2700.2587697699</v>
+      </c>
+      <c r="D62">
+        <v>2120.401230230101</v>
+      </c>
+      <c r="E62">
+        <v>3486.46</v>
+      </c>
+      <c r="F62">
+        <v>4851.06</v>
+      </c>
+      <c r="G62">
+        <v>30.4</v>
+      </c>
+      <c r="H62">
+        <v>6720.5</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>144.1</v>
+      </c>
+      <c r="K62">
+        <v>128.1</v>
+      </c>
+      <c r="L62">
+        <v>16</v>
+      </c>
+      <c r="M62">
+        <v>1158.433128</v>
+      </c>
+      <c r="N62">
+        <v>-1142.433128</v>
+      </c>
+      <c r="O62">
+        <v>-251.33528816</v>
+      </c>
+      <c r="P62">
+        <v>-891.0978398400001</v>
+      </c>
+      <c r="Q62">
+        <v>-762.9978398400001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1521381410998403</v>
+      </c>
+      <c r="T62">
+        <v>1.916360092613638</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.003038587135432818</v>
+      </c>
+      <c r="W62">
+        <v>0.2380743853920587</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.01381175970651283</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2056998876751713</v>
+      </c>
+      <c r="C63">
+        <v>-2806.51902869471</v>
+      </c>
+      <c r="D63">
+        <v>2094.99197130529</v>
+      </c>
+      <c r="E63">
+        <v>3567.311</v>
+      </c>
+      <c r="F63">
+        <v>4931.911</v>
+      </c>
+      <c r="G63">
+        <v>30.4</v>
+      </c>
+      <c r="H63">
+        <v>6720.5</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>144.1</v>
+      </c>
+      <c r="K63">
+        <v>128.1</v>
+      </c>
+      <c r="L63">
+        <v>16</v>
+      </c>
+      <c r="M63">
+        <v>1177.7403468</v>
+      </c>
+      <c r="N63">
+        <v>-1161.7403468</v>
+      </c>
+      <c r="O63">
+        <v>-255.582876296</v>
+      </c>
+      <c r="P63">
+        <v>-906.157470504</v>
+      </c>
+      <c r="Q63">
+        <v>-778.057470504</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1550442472818875</v>
+      </c>
+      <c r="T63">
+        <v>1.965497530885783</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.002988774231573264</v>
+      </c>
+      <c r="W63">
+        <v>0.2380862807135003</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.01358533741624213</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2076998876751713</v>
+      </c>
+      <c r="C64">
+        <v>-2912.177528571021</v>
+      </c>
+      <c r="D64">
+        <v>2070.18447142898</v>
+      </c>
+      <c r="E64">
+        <v>3648.162000000001</v>
+      </c>
+      <c r="F64">
+        <v>5012.762000000001</v>
+      </c>
+      <c r="G64">
+        <v>30.4</v>
+      </c>
+      <c r="H64">
+        <v>6720.5</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>144.1</v>
+      </c>
+      <c r="K64">
+        <v>128.1</v>
+      </c>
+      <c r="L64">
+        <v>16</v>
+      </c>
+      <c r="M64">
+        <v>1197.0475656</v>
+      </c>
+      <c r="N64">
+        <v>-1181.0475656</v>
+      </c>
+      <c r="O64">
+        <v>-259.830464432</v>
+      </c>
+      <c r="P64">
+        <v>-921.2171011680001</v>
+      </c>
+      <c r="Q64">
+        <v>-793.1171011680001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1581033064208845</v>
+      </c>
+      <c r="T64">
+        <v>2.01722115011962</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.002940568195580146</v>
+      </c>
+      <c r="W64">
+        <v>0.2380977923148955</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.01336621907081881</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2096998876751713</v>
+      </c>
+      <c r="C65">
+        <v>-3017.255396120094</v>
+      </c>
+      <c r="D65">
+        <v>2045.957603879907</v>
+      </c>
+      <c r="E65">
+        <v>3729.013</v>
+      </c>
+      <c r="F65">
+        <v>5093.613</v>
+      </c>
+      <c r="G65">
+        <v>30.4</v>
+      </c>
+      <c r="H65">
+        <v>6720.5</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>144.1</v>
+      </c>
+      <c r="K65">
+        <v>128.1</v>
+      </c>
+      <c r="L65">
+        <v>16</v>
+      </c>
+      <c r="M65">
+        <v>1216.3547844</v>
+      </c>
+      <c r="N65">
+        <v>-1200.3547844</v>
+      </c>
+      <c r="O65">
+        <v>-264.078052568</v>
+      </c>
+      <c r="P65">
+        <v>-936.2767318320002</v>
+      </c>
+      <c r="Q65">
+        <v>-808.1767318320002</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1613277201079354</v>
+      </c>
+      <c r="T65">
+        <v>2.071740640663393</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.002893892509936017</v>
+      </c>
+      <c r="W65">
+        <v>0.2381089384686273</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.01315405686334559</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2116998876751713</v>
+      </c>
+      <c r="C66">
+        <v>-3121.772780539308</v>
+      </c>
+      <c r="D66">
+        <v>2022.291219460692</v>
+      </c>
+      <c r="E66">
+        <v>3809.864</v>
+      </c>
+      <c r="F66">
+        <v>5174.464</v>
+      </c>
+      <c r="G66">
+        <v>30.4</v>
+      </c>
+      <c r="H66">
+        <v>6720.5</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>144.1</v>
+      </c>
+      <c r="K66">
+        <v>128.1</v>
+      </c>
+      <c r="L66">
+        <v>16</v>
+      </c>
+      <c r="M66">
+        <v>1235.6620032</v>
+      </c>
+      <c r="N66">
+        <v>-1219.6620032</v>
+      </c>
+      <c r="O66">
+        <v>-268.325640704</v>
+      </c>
+      <c r="P66">
+        <v>-951.3363624960001</v>
+      </c>
+      <c r="Q66">
+        <v>-823.2363624960001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1647312678887114</v>
+      </c>
+      <c r="T66">
+        <v>2.129288991792932</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.002848675439468267</v>
+      </c>
+      <c r="W66">
+        <v>0.238119736305055</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.01294852472485575</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2136998876751713</v>
+      </c>
+      <c r="C67">
+        <v>-3225.74890939264</v>
+      </c>
+      <c r="D67">
+        <v>1999.166090607361</v>
+      </c>
+      <c r="E67">
+        <v>3890.715000000001</v>
+      </c>
+      <c r="F67">
+        <v>5255.315000000001</v>
+      </c>
+      <c r="G67">
+        <v>30.4</v>
+      </c>
+      <c r="H67">
+        <v>6720.5</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>144.1</v>
+      </c>
+      <c r="K67">
+        <v>128.1</v>
+      </c>
+      <c r="L67">
+        <v>16</v>
+      </c>
+      <c r="M67">
+        <v>1254.969222</v>
+      </c>
+      <c r="N67">
+        <v>-1238.969222</v>
+      </c>
+      <c r="O67">
+        <v>-272.57322884</v>
+      </c>
+      <c r="P67">
+        <v>-966.3959931600002</v>
+      </c>
+      <c r="Q67">
+        <v>-838.2959931600002</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1683293041141032</v>
+      </c>
+      <c r="T67">
+        <v>2.190125820129873</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.002804849663476448</v>
+      </c>
+      <c r="W67">
+        <v>0.2381302019003618</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.01274931665216572</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2156998876751713</v>
+      </c>
+      <c r="C68">
+        <v>-3329.202140709805</v>
+      </c>
+      <c r="D68">
+        <v>1976.563859290196</v>
+      </c>
+      <c r="E68">
+        <v>3971.566</v>
+      </c>
+      <c r="F68">
+        <v>5336.166</v>
+      </c>
+      <c r="G68">
+        <v>30.4</v>
+      </c>
+      <c r="H68">
+        <v>6720.5</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>144.1</v>
+      </c>
+      <c r="K68">
+        <v>128.1</v>
+      </c>
+      <c r="L68">
+        <v>16</v>
+      </c>
+      <c r="M68">
+        <v>1274.2764408</v>
+      </c>
+      <c r="N68">
+        <v>-1258.2764408</v>
+      </c>
+      <c r="O68">
+        <v>-276.820816976</v>
+      </c>
+      <c r="P68">
+        <v>-981.455623824</v>
+      </c>
+      <c r="Q68">
+        <v>-853.355623824</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1721389895292239</v>
+      </c>
+      <c r="T68">
+        <v>2.25454128542781</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.002762351941302563</v>
+      </c>
+      <c r="W68">
+        <v>0.238140350356417</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.01255614518773895</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2176998876751713</v>
+      </c>
+      <c r="C69">
+        <v>-3432.150011590787</v>
+      </c>
+      <c r="D69">
+        <v>1954.466988409213</v>
+      </c>
+      <c r="E69">
+        <v>4052.417000000001</v>
+      </c>
+      <c r="F69">
+        <v>5417.017000000001</v>
+      </c>
+      <c r="G69">
+        <v>30.4</v>
+      </c>
+      <c r="H69">
+        <v>6720.5</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>144.1</v>
+      </c>
+      <c r="K69">
+        <v>128.1</v>
+      </c>
+      <c r="L69">
+        <v>16</v>
+      </c>
+      <c r="M69">
+        <v>1293.5836596</v>
+      </c>
+      <c r="N69">
+        <v>-1277.5836596</v>
+      </c>
+      <c r="O69">
+        <v>-281.068405112</v>
+      </c>
+      <c r="P69">
+        <v>-996.5152544880002</v>
+      </c>
+      <c r="Q69">
+        <v>-868.4152544880002</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1761795649695034</v>
+      </c>
+      <c r="T69">
+        <v>2.322860718319562</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.002721122807850285</v>
+      </c>
+      <c r="W69">
+        <v>0.2381501958734853</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.01236874003568311</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2196998876751713</v>
+      </c>
+      <c r="C70">
+        <v>-3534.609283586164</v>
+      </c>
+      <c r="D70">
+        <v>1932.858716413836</v>
+      </c>
+      <c r="E70">
+        <v>4133.268</v>
+      </c>
+      <c r="F70">
+        <v>5497.868</v>
+      </c>
+      <c r="G70">
+        <v>30.4</v>
+      </c>
+      <c r="H70">
+        <v>6720.5</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>144.1</v>
+      </c>
+      <c r="K70">
+        <v>128.1</v>
+      </c>
+      <c r="L70">
+        <v>16</v>
+      </c>
+      <c r="M70">
+        <v>1312.8908784</v>
+      </c>
+      <c r="N70">
+        <v>-1296.8908784</v>
+      </c>
+      <c r="O70">
+        <v>-285.315993248</v>
+      </c>
+      <c r="P70">
+        <v>-1011.574885152</v>
+      </c>
+      <c r="Q70">
+        <v>-883.4748851520002</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1804726763748004</v>
+      </c>
+      <c r="T70">
+        <v>2.395450115767049</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.002681106295970133</v>
+      </c>
+      <c r="W70">
+        <v>0.2381597518165223</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.01218684679986426</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2216998876751713</v>
+      </c>
+      <c r="C71">
+        <v>-3636.595985100062</v>
+      </c>
+      <c r="D71">
+        <v>1911.723014899939</v>
+      </c>
+      <c r="E71">
+        <v>4214.119000000001</v>
+      </c>
+      <c r="F71">
+        <v>5578.719000000001</v>
+      </c>
+      <c r="G71">
+        <v>30.4</v>
+      </c>
+      <c r="H71">
+        <v>6720.5</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>144.1</v>
+      </c>
+      <c r="K71">
+        <v>128.1</v>
+      </c>
+      <c r="L71">
+        <v>16</v>
+      </c>
+      <c r="M71">
+        <v>1332.1980972</v>
+      </c>
+      <c r="N71">
+        <v>-1316.1980972</v>
+      </c>
+      <c r="O71">
+        <v>-289.563581384</v>
+      </c>
+      <c r="P71">
+        <v>-1026.634515816</v>
+      </c>
+      <c r="Q71">
+        <v>-898.5345158160002</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1850427627094713</v>
+      </c>
+      <c r="T71">
+        <v>2.472722700146631</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.002642249682985059</v>
+      </c>
+      <c r="W71">
+        <v>0.2381690307757032</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.01201022583175027</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2236998876751713</v>
+      </c>
+      <c r="C72">
+        <v>-3738.125451041138</v>
+      </c>
+      <c r="D72">
+        <v>1891.044548958863</v>
+      </c>
+      <c r="E72">
+        <v>4294.970000000001</v>
+      </c>
+      <c r="F72">
+        <v>5659.570000000001</v>
+      </c>
+      <c r="G72">
+        <v>30.4</v>
+      </c>
+      <c r="H72">
+        <v>6720.5</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>144.1</v>
+      </c>
+      <c r="K72">
+        <v>128.1</v>
+      </c>
+      <c r="L72">
+        <v>16</v>
+      </c>
+      <c r="M72">
+        <v>1351.505316</v>
+      </c>
+      <c r="N72">
+        <v>-1335.505316</v>
+      </c>
+      <c r="O72">
+        <v>-293.81116952</v>
+      </c>
+      <c r="P72">
+        <v>-1041.69414648</v>
+      </c>
+      <c r="Q72">
+        <v>-913.5941464800002</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1899175214664537</v>
+      </c>
+      <c r="T72">
+        <v>2.555146790151519</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.002604503258942415</v>
+      </c>
+      <c r="W72">
+        <v>0.2381780446217646</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.01183865117701099</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2256998876751713</v>
+      </c>
+      <c r="C73">
+        <v>-3839.212359927776</v>
+      </c>
+      <c r="D73">
+        <v>1870.808640072224</v>
+      </c>
+      <c r="E73">
+        <v>4375.821</v>
+      </c>
+      <c r="F73">
+        <v>5740.421</v>
+      </c>
+      <c r="G73">
+        <v>30.4</v>
+      </c>
+      <c r="H73">
+        <v>6720.5</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>144.1</v>
+      </c>
+      <c r="K73">
+        <v>128.1</v>
+      </c>
+      <c r="L73">
+        <v>16</v>
+      </c>
+      <c r="M73">
+        <v>1370.8125348</v>
+      </c>
+      <c r="N73">
+        <v>-1354.8125348</v>
+      </c>
+      <c r="O73">
+        <v>-298.058757656</v>
+      </c>
+      <c r="P73">
+        <v>-1056.753777144</v>
+      </c>
+      <c r="Q73">
+        <v>-928.6537771440002</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1951284704825383</v>
+      </c>
+      <c r="T73">
+        <v>2.643255300156743</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.002567820114450269</v>
+      </c>
+      <c r="W73">
+        <v>0.2381868045566693</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.01167190961113762</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2276998876751713</v>
+      </c>
+      <c r="C74">
+        <v>-3939.87076863613</v>
+      </c>
+      <c r="D74">
+        <v>1851.001231363869</v>
+      </c>
+      <c r="E74">
+        <v>4456.672</v>
+      </c>
+      <c r="F74">
+        <v>5821.272</v>
+      </c>
+      <c r="G74">
+        <v>30.4</v>
+      </c>
+      <c r="H74">
+        <v>6720.5</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>144.1</v>
+      </c>
+      <c r="K74">
+        <v>128.1</v>
+      </c>
+      <c r="L74">
+        <v>16</v>
+      </c>
+      <c r="M74">
+        <v>1390.1197536</v>
+      </c>
+      <c r="N74">
+        <v>-1374.1197536</v>
+      </c>
+      <c r="O74">
+        <v>-302.3063457919999</v>
+      </c>
+      <c r="P74">
+        <v>-1071.813407808</v>
+      </c>
+      <c r="Q74">
+        <v>-943.7134078079999</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2007116301426289</v>
+      </c>
+      <c r="T74">
+        <v>2.73765727516234</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.002532155946194015</v>
+      </c>
+      <c r="W74">
+        <v>0.2381953211600489</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.01150979975542732</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2296998876751713</v>
+      </c>
+      <c r="C75">
+        <v>-4040.114144963911</v>
+      </c>
+      <c r="D75">
+        <v>1831.60885503609</v>
+      </c>
+      <c r="E75">
+        <v>4537.523000000001</v>
+      </c>
+      <c r="F75">
+        <v>5902.123000000001</v>
+      </c>
+      <c r="G75">
+        <v>30.4</v>
+      </c>
+      <c r="H75">
+        <v>6720.5</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>144.1</v>
+      </c>
+      <c r="K75">
+        <v>128.1</v>
+      </c>
+      <c r="L75">
+        <v>16</v>
+      </c>
+      <c r="M75">
+        <v>1409.4269724</v>
+      </c>
+      <c r="N75">
+        <v>-1393.4269724</v>
+      </c>
+      <c r="O75">
+        <v>-306.553933928</v>
+      </c>
+      <c r="P75">
+        <v>-1086.873038472</v>
+      </c>
+      <c r="Q75">
+        <v>-958.7730384720002</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2067083571849485</v>
+      </c>
+      <c r="T75">
+        <v>2.839051989057242</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.002497468878437933</v>
+      </c>
+      <c r="W75">
+        <v>0.238203604431829</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.01135213126562695</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2316998876751713</v>
+      </c>
+      <c r="C76">
+        <v>-4139.955398168415</v>
+      </c>
+      <c r="D76">
+        <v>1812.618601831585</v>
+      </c>
+      <c r="E76">
+        <v>4618.374</v>
+      </c>
+      <c r="F76">
+        <v>5982.974</v>
+      </c>
+      <c r="G76">
+        <v>30.4</v>
+      </c>
+      <c r="H76">
+        <v>6720.5</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>144.1</v>
+      </c>
+      <c r="K76">
+        <v>128.1</v>
+      </c>
+      <c r="L76">
+        <v>16</v>
+      </c>
+      <c r="M76">
+        <v>1428.7341912</v>
+      </c>
+      <c r="N76">
+        <v>-1412.7341912</v>
+      </c>
+      <c r="O76">
+        <v>-310.801522064</v>
+      </c>
+      <c r="P76">
+        <v>-1101.932669136</v>
+      </c>
+      <c r="Q76">
+        <v>-973.8326691360002</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2131663709228312</v>
+      </c>
+      <c r="T76">
+        <v>2.948246296328675</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.002463719298999582</v>
+      </c>
+      <c r="W76">
+        <v>0.2382116638313989</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.01119872408636169</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2336998876751713</v>
+      </c>
+      <c r="C77">
+        <v>-4239.406907624353</v>
+      </c>
+      <c r="D77">
+        <v>1794.018092375647</v>
+      </c>
+      <c r="E77">
+        <v>4699.225</v>
+      </c>
+      <c r="F77">
+        <v>6063.825000000001</v>
+      </c>
+      <c r="G77">
+        <v>30.4</v>
+      </c>
+      <c r="H77">
+        <v>6720.5</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>144.1</v>
+      </c>
+      <c r="K77">
+        <v>128.1</v>
+      </c>
+      <c r="L77">
+        <v>16</v>
+      </c>
+      <c r="M77">
+        <v>1448.04141</v>
+      </c>
+      <c r="N77">
+        <v>-1432.04141</v>
+      </c>
+      <c r="O77">
+        <v>-315.0491102</v>
+      </c>
+      <c r="P77">
+        <v>-1116.9922998</v>
+      </c>
+      <c r="Q77">
+        <v>-988.8922998000002</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2201410257597444</v>
+      </c>
+      <c r="T77">
+        <v>3.066176148181821</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.002430869708346254</v>
+      </c>
+      <c r="W77">
+        <v>0.2382195083136469</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.01104940776521024</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2356998876751713</v>
+      </c>
+      <c r="C78">
+        <v>-4338.480549735103</v>
+      </c>
+      <c r="D78">
+        <v>1775.795450264898</v>
+      </c>
+      <c r="E78">
+        <v>4780.076000000001</v>
+      </c>
+      <c r="F78">
+        <v>6144.676</v>
+      </c>
+      <c r="G78">
+        <v>30.4</v>
+      </c>
+      <c r="H78">
+        <v>6720.5</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>144.1</v>
+      </c>
+      <c r="K78">
+        <v>128.1</v>
+      </c>
+      <c r="L78">
+        <v>16</v>
+      </c>
+      <c r="M78">
+        <v>1467.3486288</v>
+      </c>
+      <c r="N78">
+        <v>-1451.3486288</v>
+      </c>
+      <c r="O78">
+        <v>-319.296698336</v>
+      </c>
+      <c r="P78">
+        <v>-1132.051930464</v>
+      </c>
+      <c r="Q78">
+        <v>-1003.951930464</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2276969018330671</v>
+      </c>
+      <c r="T78">
+        <v>3.193933487689398</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.002398884580604856</v>
+      </c>
+      <c r="W78">
+        <v>0.2382271463621516</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.01090402082093112</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2376998876751713</v>
+      </c>
+      <c r="C79">
+        <v>-4437.187723220378</v>
+      </c>
+      <c r="D79">
+        <v>1757.939276779622</v>
+      </c>
+      <c r="E79">
+        <v>4860.927</v>
+      </c>
+      <c r="F79">
+        <v>6225.527</v>
+      </c>
+      <c r="G79">
+        <v>30.4</v>
+      </c>
+      <c r="H79">
+        <v>6720.5</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>144.1</v>
+      </c>
+      <c r="K79">
+        <v>128.1</v>
+      </c>
+      <c r="L79">
+        <v>16</v>
+      </c>
+      <c r="M79">
+        <v>1486.6558476</v>
+      </c>
+      <c r="N79">
+        <v>-1470.6558476</v>
+      </c>
+      <c r="O79">
+        <v>-323.544286472</v>
+      </c>
+      <c r="P79">
+        <v>-1147.111561128</v>
+      </c>
+      <c r="Q79">
+        <v>-1019.011561128</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2359098106084179</v>
+      </c>
+      <c r="T79">
+        <v>3.332800161067198</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.002367730235402196</v>
+      </c>
+      <c r="W79">
+        <v>0.238234586019786</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.01076241016091906</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2396998876751713</v>
+      </c>
+      <c r="C80">
+        <v>-4535.539372893433</v>
+      </c>
+      <c r="D80">
+        <v>1740.438627106567</v>
+      </c>
+      <c r="E80">
+        <v>4941.778</v>
+      </c>
+      <c r="F80">
+        <v>6306.378000000001</v>
+      </c>
+      <c r="G80">
+        <v>30.4</v>
+      </c>
+      <c r="H80">
+        <v>6720.5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>144.1</v>
+      </c>
+      <c r="K80">
+        <v>128.1</v>
+      </c>
+      <c r="L80">
+        <v>16</v>
+      </c>
+      <c r="M80">
+        <v>1505.9630664</v>
+      </c>
+      <c r="N80">
+        <v>-1489.9630664</v>
+      </c>
+      <c r="O80">
+        <v>-327.791874608</v>
+      </c>
+      <c r="P80">
+        <v>-1162.171191792</v>
+      </c>
+      <c r="Q80">
+        <v>-1034.071191792</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2448693474542551</v>
+      </c>
+      <c r="T80">
+        <v>3.484291077479344</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.002337374719563706</v>
+      </c>
+      <c r="W80">
+        <v>0.2382418349169682</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.0106244305434714</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2416998876751713</v>
+      </c>
+      <c r="C81">
+        <v>-4633.54601203201</v>
+      </c>
+      <c r="D81">
+        <v>1723.28298796799</v>
+      </c>
+      <c r="E81">
+        <v>5022.629000000001</v>
+      </c>
+      <c r="F81">
+        <v>6387.229</v>
+      </c>
+      <c r="G81">
+        <v>30.4</v>
+      </c>
+      <c r="H81">
+        <v>6720.5</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>144.1</v>
+      </c>
+      <c r="K81">
+        <v>128.1</v>
+      </c>
+      <c r="L81">
+        <v>16</v>
+      </c>
+      <c r="M81">
+        <v>1525.2702852</v>
+      </c>
+      <c r="N81">
+        <v>-1509.2702852</v>
+      </c>
+      <c r="O81">
+        <v>-332.039462744</v>
+      </c>
+      <c r="P81">
+        <v>-1177.230822456</v>
+      </c>
+      <c r="Q81">
+        <v>-1049.130822456</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2546821735235053</v>
+      </c>
+      <c r="T81">
+        <v>3.650209700216456</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.002307787697797077</v>
+      </c>
+      <c r="W81">
+        <v>0.2382489002977661</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.01048994408089576</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2436998876751713</v>
+      </c>
+      <c r="C82">
+        <v>-4731.217743439145</v>
+      </c>
+      <c r="D82">
+        <v>1706.462256560856</v>
+      </c>
+      <c r="E82">
+        <v>5103.480000000001</v>
+      </c>
+      <c r="F82">
+        <v>6468.080000000001</v>
+      </c>
+      <c r="G82">
+        <v>30.4</v>
+      </c>
+      <c r="H82">
+        <v>6720.5</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>144.1</v>
+      </c>
+      <c r="K82">
+        <v>128.1</v>
+      </c>
+      <c r="L82">
+        <v>16</v>
+      </c>
+      <c r="M82">
+        <v>1544.577504</v>
+      </c>
+      <c r="N82">
+        <v>-1528.577504</v>
+      </c>
+      <c r="O82">
+        <v>-336.28705088</v>
+      </c>
+      <c r="P82">
+        <v>-1192.29045312</v>
+      </c>
+      <c r="Q82">
+        <v>-1064.19045312</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2654762821996806</v>
+      </c>
+      <c r="T82">
+        <v>3.832720185227278</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.002278940351574614</v>
+      </c>
+      <c r="W82">
+        <v>0.238255789044044</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.01035881977988462</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2456998876751713</v>
+      </c>
+      <c r="C83">
+        <v>-4828.56427928245</v>
+      </c>
+      <c r="D83">
+        <v>1689.96672071755</v>
+      </c>
+      <c r="E83">
+        <v>5184.331</v>
+      </c>
+      <c r="F83">
+        <v>6548.931</v>
+      </c>
+      <c r="G83">
+        <v>30.4</v>
+      </c>
+      <c r="H83">
+        <v>6720.5</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>144.1</v>
+      </c>
+      <c r="K83">
+        <v>128.1</v>
+      </c>
+      <c r="L83">
+        <v>16</v>
+      </c>
+      <c r="M83">
+        <v>1563.8847228</v>
+      </c>
+      <c r="N83">
+        <v>-1547.8847228</v>
+      </c>
+      <c r="O83">
+        <v>-340.534639016</v>
+      </c>
+      <c r="P83">
+        <v>-1207.350083784</v>
+      </c>
+      <c r="Q83">
+        <v>-1079.250083784</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.277406612841769</v>
+      </c>
+      <c r="T83">
+        <v>4.03444230023924</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.002250805285505791</v>
+      </c>
+      <c r="W83">
+        <v>0.2382625076978212</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.01023093311593537</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2476998876751713</v>
+      </c>
+      <c r="C84">
+        <v>-4925.594959793772</v>
+      </c>
+      <c r="D84">
+        <v>1673.787040206229</v>
+      </c>
+      <c r="E84">
+        <v>5265.182000000001</v>
+      </c>
+      <c r="F84">
+        <v>6629.782000000001</v>
+      </c>
+      <c r="G84">
+        <v>30.4</v>
+      </c>
+      <c r="H84">
+        <v>6720.5</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>144.1</v>
+      </c>
+      <c r="K84">
+        <v>128.1</v>
+      </c>
+      <c r="L84">
+        <v>16</v>
+      </c>
+      <c r="M84">
+        <v>1583.1919416</v>
+      </c>
+      <c r="N84">
+        <v>-1567.1919416</v>
+      </c>
+      <c r="O84">
+        <v>-344.782227152</v>
+      </c>
+      <c r="P84">
+        <v>-1222.409714448</v>
+      </c>
+      <c r="Q84">
+        <v>-1094.309714448</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2906625357774229</v>
+      </c>
+      <c r="T84">
+        <v>4.258577983585865</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.002223356440560599</v>
+      </c>
+      <c r="W84">
+        <v>0.2382690624819941</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.01010616563891176</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2496998876751713</v>
+      </c>
+      <c r="C85">
+        <v>-5022.318770904834</v>
+      </c>
+      <c r="D85">
+        <v>1657.914229095166</v>
+      </c>
+      <c r="E85">
+        <v>5346.033000000001</v>
+      </c>
+      <c r="F85">
+        <v>6710.633000000001</v>
+      </c>
+      <c r="G85">
+        <v>30.4</v>
+      </c>
+      <c r="H85">
+        <v>6720.5</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>144.1</v>
+      </c>
+      <c r="K85">
+        <v>128.1</v>
+      </c>
+      <c r="L85">
+        <v>16</v>
+      </c>
+      <c r="M85">
+        <v>1602.4991604</v>
+      </c>
+      <c r="N85">
+        <v>-1586.4991604</v>
+      </c>
+      <c r="O85">
+        <v>-349.029815288</v>
+      </c>
+      <c r="P85">
+        <v>-1237.469345112</v>
+      </c>
+      <c r="Q85">
+        <v>-1109.369345112</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3054779790584478</v>
+      </c>
+      <c r="T85">
+        <v>4.509082570855622</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.002196569013565893</v>
+      </c>
+      <c r="W85">
+        <v>0.2382754593195605</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.009984404607117692</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2516998876751713</v>
+      </c>
+      <c r="C86">
+        <v>-5118.744360888881</v>
+      </c>
+      <c r="D86">
+        <v>1642.33963911112</v>
+      </c>
+      <c r="E86">
+        <v>5426.884</v>
+      </c>
+      <c r="F86">
+        <v>6791.484</v>
+      </c>
+      <c r="G86">
+        <v>30.4</v>
+      </c>
+      <c r="H86">
+        <v>6720.5</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>144.1</v>
+      </c>
+      <c r="K86">
+        <v>128.1</v>
+      </c>
+      <c r="L86">
+        <v>16</v>
+      </c>
+      <c r="M86">
+        <v>1621.8063792</v>
+      </c>
+      <c r="N86">
+        <v>-1605.8063792</v>
+      </c>
+      <c r="O86">
+        <v>-353.277403424</v>
+      </c>
+      <c r="P86">
+        <v>-1252.528975776</v>
+      </c>
+      <c r="Q86">
+        <v>-1124.428975776</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3221453527496006</v>
+      </c>
+      <c r="T86">
+        <v>4.790900231534096</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.002170419382452013</v>
+      </c>
+      <c r="W86">
+        <v>0.2382817038514705</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.009865542647509162</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2536998876751713</v>
+      </c>
+      <c r="C87">
+        <v>-5214.880056073027</v>
+      </c>
+      <c r="D87">
+        <v>1627.054943926973</v>
+      </c>
+      <c r="E87">
+        <v>5507.735000000001</v>
+      </c>
+      <c r="F87">
+        <v>6872.335</v>
+      </c>
+      <c r="G87">
+        <v>30.4</v>
+      </c>
+      <c r="H87">
+        <v>6720.5</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>144.1</v>
+      </c>
+      <c r="K87">
+        <v>128.1</v>
+      </c>
+      <c r="L87">
+        <v>16</v>
+      </c>
+      <c r="M87">
+        <v>1641.113598</v>
+      </c>
+      <c r="N87">
+        <v>-1625.113598</v>
+      </c>
+      <c r="O87">
+        <v>-357.52499156</v>
+      </c>
+      <c r="P87">
+        <v>-1267.58860644</v>
+      </c>
+      <c r="Q87">
+        <v>-1139.48860644</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3410350429329074</v>
+      </c>
+      <c r="T87">
+        <v>5.110293580303036</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.002144885036776107</v>
+      </c>
+      <c r="W87">
+        <v>0.2382878014532179</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.009749477439891407</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2556998876751713</v>
+      </c>
+      <c r="C88">
+        <v>-5310.733875681341</v>
+      </c>
+      <c r="D88">
+        <v>1612.05212431866</v>
+      </c>
+      <c r="E88">
+        <v>5588.586000000001</v>
+      </c>
+      <c r="F88">
+        <v>6953.186000000001</v>
+      </c>
+      <c r="G88">
+        <v>30.4</v>
+      </c>
+      <c r="H88">
+        <v>6720.5</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>144.1</v>
+      </c>
+      <c r="K88">
+        <v>128.1</v>
+      </c>
+      <c r="L88">
+        <v>16</v>
+      </c>
+      <c r="M88">
+        <v>1660.4208168</v>
+      </c>
+      <c r="N88">
+        <v>-1644.4208168</v>
+      </c>
+      <c r="O88">
+        <v>-361.772579696</v>
+      </c>
+      <c r="P88">
+        <v>-1282.648237104</v>
+      </c>
+      <c r="Q88">
+        <v>-1154.548237104</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3626232602852579</v>
+      </c>
+      <c r="T88">
+        <v>5.475314550324682</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.002119944513092664</v>
+      </c>
+      <c r="W88">
+        <v>0.2382937572502735</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.009636111423148463</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2576998876751713</v>
+      </c>
+      <c r="C89">
+        <v>-5406.313545864221</v>
+      </c>
+      <c r="D89">
+        <v>1597.323454135779</v>
+      </c>
+      <c r="E89">
+        <v>5669.437</v>
+      </c>
+      <c r="F89">
+        <v>7034.037</v>
+      </c>
+      <c r="G89">
+        <v>30.4</v>
+      </c>
+      <c r="H89">
+        <v>6720.5</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>144.1</v>
+      </c>
+      <c r="K89">
+        <v>128.1</v>
+      </c>
+      <c r="L89">
+        <v>16</v>
+      </c>
+      <c r="M89">
+        <v>1679.7280356</v>
+      </c>
+      <c r="N89">
+        <v>-1663.7280356</v>
+      </c>
+      <c r="O89">
+        <v>-366.020167832</v>
+      </c>
+      <c r="P89">
+        <v>-1297.707867768</v>
+      </c>
+      <c r="Q89">
+        <v>-1169.607867768</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.3875327418456623</v>
+      </c>
+      <c r="T89">
+        <v>5.896492592657348</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.002095577334781254</v>
+      </c>
+      <c r="W89">
+        <v>0.2382995761324543</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.00952535152173295</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2596998876751713</v>
+      </c>
+      <c r="C90">
+        <v>-5501.626512965668</v>
+      </c>
+      <c r="D90">
+        <v>1582.861487034332</v>
+      </c>
+      <c r="E90">
+        <v>5750.288</v>
+      </c>
+      <c r="F90">
+        <v>7114.888</v>
+      </c>
+      <c r="G90">
+        <v>30.4</v>
+      </c>
+      <c r="H90">
+        <v>6720.5</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>144.1</v>
+      </c>
+      <c r="K90">
+        <v>128.1</v>
+      </c>
+      <c r="L90">
+        <v>16</v>
+      </c>
+      <c r="M90">
+        <v>1699.0352544</v>
+      </c>
+      <c r="N90">
+        <v>-1683.0352544</v>
+      </c>
+      <c r="O90">
+        <v>-370.267755968</v>
+      </c>
+      <c r="P90">
+        <v>-1312.767498432</v>
+      </c>
+      <c r="Q90">
+        <v>-1184.667498432</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4165938036661342</v>
+      </c>
+      <c r="T90">
+        <v>6.387866975378795</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.002071763955976922</v>
+      </c>
+      <c r="W90">
+        <v>0.2383052627673127</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.00941710889080416</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2616998876751713</v>
+      </c>
+      <c r="C91">
+        <v>-5596.679956076281</v>
+      </c>
+      <c r="D91">
+        <v>1568.659043923719</v>
+      </c>
+      <c r="E91">
+        <v>5831.139000000001</v>
+      </c>
+      <c r="F91">
+        <v>7195.739</v>
+      </c>
+      <c r="G91">
+        <v>30.4</v>
+      </c>
+      <c r="H91">
+        <v>6720.5</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>144.1</v>
+      </c>
+      <c r="K91">
+        <v>128.1</v>
+      </c>
+      <c r="L91">
+        <v>16</v>
+      </c>
+      <c r="M91">
+        <v>1718.3424732</v>
+      </c>
+      <c r="N91">
+        <v>-1702.3424732</v>
+      </c>
+      <c r="O91">
+        <v>-374.515344104</v>
+      </c>
+      <c r="P91">
+        <v>-1327.827129096</v>
+      </c>
+      <c r="Q91">
+        <v>-1199.727129096</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.4509386949085101</v>
+      </c>
+      <c r="T91">
+        <v>6.968582154958687</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.002048485709280551</v>
+      </c>
+      <c r="W91">
+        <v>0.2383108216126238</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.009311298678547963</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2636998876751713</v>
+      </c>
+      <c r="C92">
+        <v>-5691.480798916482</v>
+      </c>
+      <c r="D92">
+        <v>1554.709201083518</v>
+      </c>
+      <c r="E92">
+        <v>5911.99</v>
+      </c>
+      <c r="F92">
+        <v>7276.59</v>
+      </c>
+      <c r="G92">
+        <v>30.4</v>
+      </c>
+      <c r="H92">
+        <v>6720.5</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>144.1</v>
+      </c>
+      <c r="K92">
+        <v>128.1</v>
+      </c>
+      <c r="L92">
+        <v>16</v>
+      </c>
+      <c r="M92">
+        <v>1737.649692</v>
+      </c>
+      <c r="N92">
+        <v>-1721.649692</v>
+      </c>
+      <c r="O92">
+        <v>-378.76293224</v>
+      </c>
+      <c r="P92">
+        <v>-1342.88675976</v>
+      </c>
+      <c r="Q92">
+        <v>-1214.78675976</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.4921525643993612</v>
+      </c>
+      <c r="T92">
+        <v>7.665440370454556</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.002025724756955212</v>
+      </c>
+      <c r="W92">
+        <v>0.2383162569280391</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.009207839804341922</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2656998876751713</v>
+      </c>
+      <c r="C93">
+        <v>-5786.035721091263</v>
+      </c>
+      <c r="D93">
+        <v>1541.005278908739</v>
+      </c>
+      <c r="E93">
+        <v>5992.841</v>
+      </c>
+      <c r="F93">
+        <v>7357.441000000001</v>
+      </c>
+      <c r="G93">
+        <v>30.4</v>
+      </c>
+      <c r="H93">
+        <v>6720.5</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>144.1</v>
+      </c>
+      <c r="K93">
+        <v>128.1</v>
+      </c>
+      <c r="L93">
+        <v>16</v>
+      </c>
+      <c r="M93">
+        <v>1756.9569108</v>
+      </c>
+      <c r="N93">
+        <v>-1740.9569108</v>
+      </c>
+      <c r="O93">
+        <v>-383.010520376</v>
+      </c>
+      <c r="P93">
+        <v>-1357.946390424</v>
+      </c>
+      <c r="Q93">
+        <v>-1229.846390424</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.5425250715548458</v>
+      </c>
+      <c r="T93">
+        <v>8.517155967171728</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.00200346404534032</v>
+      </c>
+      <c r="W93">
+        <v>0.2383215727859727</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.009106654751546928</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2676998876751713</v>
+      </c>
+      <c r="C94">
+        <v>-5880.351168754911</v>
+      </c>
+      <c r="D94">
+        <v>1527.540831245089</v>
+      </c>
+      <c r="E94">
+        <v>6073.692000000001</v>
+      </c>
+      <c r="F94">
+        <v>7438.292</v>
+      </c>
+      <c r="G94">
+        <v>30.4</v>
+      </c>
+      <c r="H94">
+        <v>6720.5</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>144.1</v>
+      </c>
+      <c r="K94">
+        <v>128.1</v>
+      </c>
+      <c r="L94">
+        <v>16</v>
+      </c>
+      <c r="M94">
+        <v>1776.2641296</v>
+      </c>
+      <c r="N94">
+        <v>-1760.2641296</v>
+      </c>
+      <c r="O94">
+        <v>-387.258108512</v>
+      </c>
+      <c r="P94">
+        <v>-1373.006021088</v>
+      </c>
+      <c r="Q94">
+        <v>-1244.906021088</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.6054907054992016</v>
+      </c>
+      <c r="T94">
+        <v>9.581800463068198</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.001981687262238795</v>
+      </c>
+      <c r="W94">
+        <v>0.2383267730817774</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.009007669373812699</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2696998876751713</v>
+      </c>
+      <c r="C95">
+        <v>-5974.433364721486</v>
+      </c>
+      <c r="D95">
+        <v>1514.309635278515</v>
+      </c>
+      <c r="E95">
+        <v>6154.543000000001</v>
+      </c>
+      <c r="F95">
+        <v>7519.143000000001</v>
+      </c>
+      <c r="G95">
+        <v>30.4</v>
+      </c>
+      <c r="H95">
+        <v>6720.5</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>144.1</v>
+      </c>
+      <c r="K95">
+        <v>128.1</v>
+      </c>
+      <c r="L95">
+        <v>16</v>
+      </c>
+      <c r="M95">
+        <v>1795.5713484</v>
+      </c>
+      <c r="N95">
+        <v>-1779.5713484</v>
+      </c>
+      <c r="O95">
+        <v>-391.505696648</v>
+      </c>
+      <c r="P95">
+        <v>-1388.065651752</v>
+      </c>
+      <c r="Q95">
+        <v>-1259.965651752</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.6864465205705161</v>
+      </c>
+      <c r="T95">
+        <v>10.95062910064937</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.001960378797053431</v>
+      </c>
+      <c r="W95">
+        <v>0.2383318615432636</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.008910812713879279</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2716998876751713</v>
+      </c>
+      <c r="C96">
+        <v>-6068.288318054349</v>
+      </c>
+      <c r="D96">
+        <v>1501.305681945651</v>
+      </c>
+      <c r="E96">
+        <v>6235.394</v>
+      </c>
+      <c r="F96">
+        <v>7599.994000000001</v>
+      </c>
+      <c r="G96">
+        <v>30.4</v>
+      </c>
+      <c r="H96">
+        <v>6720.5</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>144.1</v>
+      </c>
+      <c r="K96">
+        <v>128.1</v>
+      </c>
+      <c r="L96">
+        <v>16</v>
+      </c>
+      <c r="M96">
+        <v>1814.8785672</v>
+      </c>
+      <c r="N96">
+        <v>-1798.8785672</v>
+      </c>
+      <c r="O96">
+        <v>-395.753284784</v>
+      </c>
+      <c r="P96">
+        <v>-1403.125282416</v>
+      </c>
+      <c r="Q96">
+        <v>-1275.025282416</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.7943876073322691</v>
+      </c>
+      <c r="T96">
+        <v>12.7757339507576</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.001939523703467757</v>
+      </c>
+      <c r="W96">
+        <v>0.2383368417396119</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.008816016833944396</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2736998876751713</v>
+      </c>
+      <c r="C97">
+        <v>-6161.921833165823</v>
+      </c>
+      <c r="D97">
+        <v>1488.523166834178</v>
+      </c>
+      <c r="E97">
+        <v>6316.245000000001</v>
+      </c>
+      <c r="F97">
+        <v>7680.845000000001</v>
+      </c>
+      <c r="G97">
+        <v>30.4</v>
+      </c>
+      <c r="H97">
+        <v>6720.5</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>144.1</v>
+      </c>
+      <c r="K97">
+        <v>128.1</v>
+      </c>
+      <c r="L97">
+        <v>16</v>
+      </c>
+      <c r="M97">
+        <v>1834.185786</v>
+      </c>
+      <c r="N97">
+        <v>-1818.185786</v>
+      </c>
+      <c r="O97">
+        <v>-400.0008729200001</v>
+      </c>
+      <c r="P97">
+        <v>-1418.18491308</v>
+      </c>
+      <c r="Q97">
+        <v>-1290.08491308</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.9455051287987235</v>
+      </c>
+      <c r="T97">
+        <v>15.33088074090913</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.001919107664483885</v>
+      </c>
+      <c r="W97">
+        <v>0.2383417170897213</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.008723216656744914</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2756998876751713</v>
+      </c>
+      <c r="C98">
+        <v>-6255.339518455899</v>
+      </c>
+      <c r="D98">
+        <v>1475.956481544102</v>
+      </c>
+      <c r="E98">
+        <v>6397.096</v>
+      </c>
+      <c r="F98">
+        <v>7761.696</v>
+      </c>
+      <c r="G98">
+        <v>30.4</v>
+      </c>
+      <c r="H98">
+        <v>6720.5</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>144.1</v>
+      </c>
+      <c r="K98">
+        <v>128.1</v>
+      </c>
+      <c r="L98">
+        <v>16</v>
+      </c>
+      <c r="M98">
+        <v>1853.4930048</v>
+      </c>
+      <c r="N98">
+        <v>-1837.4930048</v>
+      </c>
+      <c r="O98">
+        <v>-404.248461056</v>
+      </c>
+      <c r="P98">
+        <v>-1433.244543744</v>
+      </c>
+      <c r="Q98">
+        <v>-1305.144543744</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.172181410998401</v>
+      </c>
+      <c r="T98">
+        <v>19.16360092613637</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.001899116959645512</v>
+      </c>
+      <c r="W98">
+        <v>0.2383464908700367</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.008632349816570462</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2776998876751713</v>
+      </c>
+      <c r="C99">
+        <v>-6348.546794517033</v>
+      </c>
+      <c r="D99">
+        <v>1463.600205482968</v>
+      </c>
+      <c r="E99">
+        <v>6477.947</v>
+      </c>
+      <c r="F99">
+        <v>7842.547</v>
+      </c>
+      <c r="G99">
+        <v>30.4</v>
+      </c>
+      <c r="H99">
+        <v>6720.5</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>144.1</v>
+      </c>
+      <c r="K99">
+        <v>128.1</v>
+      </c>
+      <c r="L99">
+        <v>16</v>
+      </c>
+      <c r="M99">
+        <v>1872.8002236</v>
+      </c>
+      <c r="N99">
+        <v>-1856.8002236</v>
+      </c>
+      <c r="O99">
+        <v>-408.496049192</v>
+      </c>
+      <c r="P99">
+        <v>-1448.304174408</v>
+      </c>
+      <c r="Q99">
+        <v>-1320.204174408</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.549975214664536</v>
+      </c>
+      <c r="T99">
+        <v>25.55146790151516</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.001879538434288341</v>
+      </c>
+      <c r="W99">
+        <v>0.238351166221892</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.008543356519492451</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2796998876751713</v>
+      </c>
+      <c r="C100">
+        <v>-6441.548901930219</v>
+      </c>
+      <c r="D100">
+        <v>1451.44909806978</v>
+      </c>
+      <c r="E100">
+        <v>6558.798000000001</v>
+      </c>
+      <c r="F100">
+        <v>7923.398</v>
+      </c>
+      <c r="G100">
+        <v>30.4</v>
+      </c>
+      <c r="H100">
+        <v>6720.5</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>144.1</v>
+      </c>
+      <c r="K100">
+        <v>128.1</v>
+      </c>
+      <c r="L100">
+        <v>16</v>
+      </c>
+      <c r="M100">
+        <v>1892.1074424</v>
+      </c>
+      <c r="N100">
+        <v>-1876.1074424</v>
+      </c>
+      <c r="O100">
+        <v>-412.743637328</v>
+      </c>
+      <c r="P100">
+        <v>-1463.363805072</v>
+      </c>
+      <c r="Q100">
+        <v>-1335.263805072</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.305562821996803</v>
+      </c>
+      <c r="T100">
+        <v>38.32720185227274</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.001860359470673154</v>
+      </c>
+      <c r="W100">
+        <v>0.2383557461584032</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.008456179412150711</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2816998876751713</v>
+      </c>
+      <c r="C101">
+        <v>-6534.350908675937</v>
+      </c>
+      <c r="D101">
+        <v>1439.498091324064</v>
+      </c>
+      <c r="E101">
+        <v>6639.649000000001</v>
+      </c>
+      <c r="F101">
+        <v>8004.249000000001</v>
+      </c>
+      <c r="G101">
+        <v>30.4</v>
+      </c>
+      <c r="H101">
+        <v>6720.5</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>144.1</v>
+      </c>
+      <c r="K101">
+        <v>128.1</v>
+      </c>
+      <c r="L101">
+        <v>16</v>
+      </c>
+      <c r="M101">
+        <v>1911.4146612</v>
+      </c>
+      <c r="N101">
+        <v>-1895.4146612</v>
+      </c>
+      <c r="O101">
+        <v>-416.991225464</v>
+      </c>
+      <c r="P101">
+        <v>-1478.423435736</v>
+      </c>
+      <c r="Q101">
+        <v>-1350.323435736</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.572325643993606</v>
+      </c>
+      <c r="T101">
+        <v>76.65440370454547</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.001841567960868375</v>
+      </c>
+      <c r="W101">
+        <v>0.2383602335709446</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.008370763458492636</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/denmark/denmark_air_transport.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_air_transport.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08062267324884481</v>
+        <v>0.08048040336769735</v>
       </c>
       <c r="C2">
-        <v>7663.43235184098</v>
+        <v>7613.993822485197</v>
       </c>
       <c r="D2">
-        <v>7650.43235184098</v>
+        <v>7681.816822485197</v>
       </c>
       <c r="E2">
-        <v>-1414.7</v>
+        <v>-1333.877</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>80.82300000000001</v>
       </c>
       <c r="G2">
         <v>13</v>
@@ -1451,28 +1451,28 @@
         <v>189.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4.065396900000001</v>
       </c>
       <c r="N2">
-        <v>189.5</v>
+        <v>185.4346031</v>
       </c>
       <c r="O2">
-        <v>41.69</v>
+        <v>40.795612682</v>
       </c>
       <c r="P2">
-        <v>147.81</v>
+        <v>144.638990418</v>
       </c>
       <c r="Q2">
-        <v>294.51</v>
+        <v>291.338990418</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08062267324884481</v>
+        <v>0.0808970337047448</v>
       </c>
       <c r="T2">
-        <v>0.8042187817285175</v>
+        <v>0.8105550509178936</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>46.61291496532601</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08048040336769735</v>
+        <v>0.08033813348654988</v>
       </c>
       <c r="C3">
-        <v>7613.993822485197</v>
+        <v>7564.813851682396</v>
       </c>
       <c r="D3">
-        <v>7681.816822485197</v>
+        <v>7713.459851682395</v>
       </c>
       <c r="E3">
-        <v>-1333.877</v>
+        <v>-1253.054</v>
       </c>
       <c r="F3">
-        <v>80.82300000000001</v>
+        <v>161.646</v>
       </c>
       <c r="G3">
         <v>13</v>
@@ -1533,28 +1533,28 @@
         <v>189.5</v>
       </c>
       <c r="M3">
-        <v>4.065396900000001</v>
+        <v>8.130793800000001</v>
       </c>
       <c r="N3">
-        <v>185.4346031</v>
+        <v>181.3692062</v>
       </c>
       <c r="O3">
-        <v>40.795612682</v>
+        <v>39.90122536400001</v>
       </c>
       <c r="P3">
-        <v>144.638990418</v>
+        <v>141.467980836</v>
       </c>
       <c r="Q3">
-        <v>291.338990418</v>
+        <v>288.167980836</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0808970337047448</v>
+        <v>0.08117699335362233</v>
       </c>
       <c r="T3">
-        <v>0.8105550509178936</v>
+        <v>0.8170206317233796</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>46.61291496532601</v>
+        <v>23.30645748266301</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08033813348654988</v>
+        <v>0.08019586360540243</v>
       </c>
       <c r="C4">
-        <v>7564.813851682396</v>
+        <v>7515.895647820792</v>
       </c>
       <c r="D4">
-        <v>7713.459851682395</v>
+        <v>7745.364647820792</v>
       </c>
       <c r="E4">
-        <v>-1253.054</v>
+        <v>-1172.231</v>
       </c>
       <c r="F4">
-        <v>161.646</v>
+        <v>242.469</v>
       </c>
       <c r="G4">
         <v>13</v>
@@ -1615,28 +1615,28 @@
         <v>189.5</v>
       </c>
       <c r="M4">
-        <v>8.130793800000001</v>
+        <v>12.1961907</v>
       </c>
       <c r="N4">
-        <v>181.3692062</v>
+        <v>177.3038093</v>
       </c>
       <c r="O4">
-        <v>39.90122536400001</v>
+        <v>39.00683804600001</v>
       </c>
       <c r="P4">
-        <v>141.467980836</v>
+        <v>138.296971254</v>
       </c>
       <c r="Q4">
-        <v>288.167980836</v>
+        <v>284.996971254</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08117699335362233</v>
+        <v>0.08146272536639426</v>
       </c>
       <c r="T4">
-        <v>0.8170206317233796</v>
+        <v>0.8236195234733085</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>23.30645748266301</v>
+        <v>15.53763832177534</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08019586360540243</v>
+        <v>0.08005359372425498</v>
       </c>
       <c r="C5">
-        <v>7515.895647820792</v>
+        <v>7467.242472591874</v>
       </c>
       <c r="D5">
-        <v>7745.364647820792</v>
+        <v>7777.534472591874</v>
       </c>
       <c r="E5">
-        <v>-1172.231</v>
+        <v>-1091.408</v>
       </c>
       <c r="F5">
-        <v>242.469</v>
+        <v>323.292</v>
       </c>
       <c r="G5">
         <v>13</v>
@@ -1697,28 +1697,28 @@
         <v>189.5</v>
       </c>
       <c r="M5">
-        <v>12.1961907</v>
+        <v>16.2615876</v>
       </c>
       <c r="N5">
-        <v>177.3038093</v>
+        <v>173.2384124</v>
       </c>
       <c r="O5">
-        <v>39.00683804600001</v>
+        <v>38.112450728</v>
       </c>
       <c r="P5">
-        <v>138.296971254</v>
+        <v>135.125961672</v>
       </c>
       <c r="Q5">
-        <v>284.996971254</v>
+        <v>281.8259616719999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08146272536639426</v>
+        <v>0.08175441012943227</v>
       </c>
       <c r="T5">
-        <v>0.8236195234733085</v>
+        <v>0.8303558921346943</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>15.53763832177534</v>
+        <v>11.6532287413315</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08005359372425498</v>
+        <v>0.07991132384310751</v>
       </c>
       <c r="C6">
-        <v>7467.242472591874</v>
+        <v>7418.857642101956</v>
       </c>
       <c r="D6">
-        <v>7777.534472591874</v>
+        <v>7809.972642101956</v>
       </c>
       <c r="E6">
-        <v>-1091.408</v>
+        <v>-1010.585</v>
       </c>
       <c r="F6">
-        <v>323.292</v>
+        <v>404.115</v>
       </c>
       <c r="G6">
         <v>13</v>
@@ -1779,28 +1779,28 @@
         <v>189.5</v>
       </c>
       <c r="M6">
-        <v>16.2615876</v>
+        <v>20.3269845</v>
       </c>
       <c r="N6">
-        <v>173.2384124</v>
+        <v>169.1730155</v>
       </c>
       <c r="O6">
-        <v>38.112450728</v>
+        <v>37.21806341</v>
       </c>
       <c r="P6">
-        <v>135.125961672</v>
+        <v>131.95495209</v>
       </c>
       <c r="Q6">
-        <v>281.8259616719999</v>
+        <v>278.65495209</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08175441012943227</v>
+        <v>0.0820522356243237</v>
       </c>
       <c r="T6">
-        <v>0.8303558921346943</v>
+        <v>0.8372340790836883</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>11.6532287413315</v>
+        <v>9.322582993065204</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07991132384310751</v>
+        <v>0.07983925396196005</v>
       </c>
       <c r="C7">
-        <v>7418.857642101956</v>
+        <v>7354.5703687871</v>
       </c>
       <c r="D7">
-        <v>7809.972642101956</v>
+        <v>7826.5083687871</v>
       </c>
       <c r="E7">
-        <v>-1010.585</v>
+        <v>-929.7619999999999</v>
       </c>
       <c r="F7">
-        <v>404.115</v>
+        <v>484.938</v>
       </c>
       <c r="G7">
         <v>13</v>
@@ -1861,45 +1861,45 @@
         <v>189.5</v>
       </c>
       <c r="M7">
-        <v>20.3269845</v>
+        <v>25.1197884</v>
       </c>
       <c r="N7">
-        <v>169.1730155</v>
+        <v>164.3802116</v>
       </c>
       <c r="O7">
-        <v>37.21806341</v>
+        <v>36.163646552</v>
       </c>
       <c r="P7">
-        <v>131.95495209</v>
+        <v>128.216565048</v>
       </c>
       <c r="Q7">
-        <v>278.65495209</v>
+        <v>274.916565048</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0820522356243237</v>
+        <v>0.0823563978318724</v>
       </c>
       <c r="T7">
-        <v>0.8372340790836883</v>
+        <v>0.8442586104358522</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.22</v>
       </c>
       <c r="W7">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>9.322582993065204</v>
+        <v>7.543853355070459</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07983925396196005</v>
+        <v>0.07980150408081259</v>
       </c>
       <c r="C8">
-        <v>7354.5703687871</v>
+        <v>7282.436683236812</v>
       </c>
       <c r="D8">
-        <v>7826.5083687871</v>
+        <v>7835.197683236812</v>
       </c>
       <c r="E8">
-        <v>-929.7620000000001</v>
+        <v>-848.9390000000001</v>
       </c>
       <c r="F8">
-        <v>484.938</v>
+        <v>565.761</v>
       </c>
       <c r="G8">
         <v>13</v>
@@ -1943,45 +1943,45 @@
         <v>189.5</v>
       </c>
       <c r="M8">
-        <v>25.1197884</v>
+        <v>30.2682135</v>
       </c>
       <c r="N8">
-        <v>164.3802116</v>
+        <v>159.2317865</v>
       </c>
       <c r="O8">
-        <v>36.163646552</v>
+        <v>35.03099303</v>
       </c>
       <c r="P8">
-        <v>128.216565048</v>
+        <v>124.20079347</v>
       </c>
       <c r="Q8">
-        <v>274.916565048</v>
+        <v>270.90079347</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0823563978318724</v>
+        <v>0.08266710116216408</v>
       </c>
       <c r="T8">
-        <v>0.8442586104358522</v>
+        <v>0.8514342069783851</v>
       </c>
       <c r="U8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V8">
         <v>0.22</v>
       </c>
       <c r="W8">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>7.54385335507046</v>
+        <v>6.260693251684643</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07980150408081259</v>
+        <v>0.07973411419966514</v>
       </c>
       <c r="C9">
-        <v>7282.436683236811</v>
+        <v>7217.17363089106</v>
       </c>
       <c r="D9">
-        <v>7835.197683236812</v>
+        <v>7850.75763089106</v>
       </c>
       <c r="E9">
-        <v>-848.939</v>
+        <v>-768.116</v>
       </c>
       <c r="F9">
-        <v>565.7610000000001</v>
+        <v>646.5840000000001</v>
       </c>
       <c r="G9">
         <v>13</v>
@@ -2025,45 +2025,45 @@
         <v>189.5</v>
       </c>
       <c r="M9">
-        <v>30.26821350000001</v>
+        <v>35.10951120000001</v>
       </c>
       <c r="N9">
-        <v>159.2317865</v>
+        <v>154.3904888</v>
       </c>
       <c r="O9">
-        <v>35.03099303</v>
+        <v>33.965907536</v>
       </c>
       <c r="P9">
-        <v>124.20079347</v>
+        <v>120.424581264</v>
       </c>
       <c r="Q9">
-        <v>270.90079347</v>
+        <v>267.124581264</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08266710116216408</v>
+        <v>0.0829845589126795</v>
       </c>
       <c r="T9">
-        <v>0.8514342069783853</v>
+        <v>0.8587657947501038</v>
       </c>
       <c r="U9">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y9">
-        <v>6.260693251684642</v>
+        <v>5.397397842439913</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07973411419966514</v>
+        <v>0.07962304431851767</v>
       </c>
       <c r="C10">
-        <v>7217.17363089106</v>
+        <v>7162.131359224354</v>
       </c>
       <c r="D10">
-        <v>7850.75763089106</v>
+        <v>7876.538359224354</v>
       </c>
       <c r="E10">
-        <v>-768.116</v>
+        <v>-687.293</v>
       </c>
       <c r="F10">
-        <v>646.5840000000001</v>
+        <v>727.407</v>
       </c>
       <c r="G10">
         <v>13</v>
@@ -2107,28 +2107,28 @@
         <v>189.5</v>
       </c>
       <c r="M10">
-        <v>35.10951120000001</v>
+        <v>39.49820010000001</v>
       </c>
       <c r="N10">
-        <v>154.3904888</v>
+        <v>150.0017999</v>
       </c>
       <c r="O10">
-        <v>33.965907536</v>
+        <v>33.00039597799999</v>
       </c>
       <c r="P10">
-        <v>120.424581264</v>
+        <v>117.001403922</v>
       </c>
       <c r="Q10">
-        <v>267.124581264</v>
+        <v>263.7014039219999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0829845589126795</v>
+        <v>0.08330899375661283</v>
       </c>
       <c r="T10">
-        <v>0.8587657947501038</v>
+        <v>0.8662585163190031</v>
       </c>
       <c r="U10">
         <v>0.0543</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>5.397397842439913</v>
+        <v>4.797686971057701</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07962304431851767</v>
+        <v>0.07951197443737022</v>
       </c>
       <c r="C11">
-        <v>7162.131359224354</v>
+        <v>7107.258965619054</v>
       </c>
       <c r="D11">
-        <v>7876.538359224354</v>
+        <v>7902.488965619053</v>
       </c>
       <c r="E11">
-        <v>-687.293</v>
+        <v>-606.4700000000001</v>
       </c>
       <c r="F11">
-        <v>727.407</v>
+        <v>808.2299999999999</v>
       </c>
       <c r="G11">
         <v>13</v>
@@ -2189,28 +2189,28 @@
         <v>189.5</v>
       </c>
       <c r="M11">
-        <v>39.49820010000001</v>
+        <v>43.886889</v>
       </c>
       <c r="N11">
-        <v>150.0017999</v>
+        <v>145.613111</v>
       </c>
       <c r="O11">
-        <v>33.00039597799999</v>
+        <v>32.03488442</v>
       </c>
       <c r="P11">
-        <v>117.001403922</v>
+        <v>113.57822658</v>
       </c>
       <c r="Q11">
-        <v>263.7014039219999</v>
+        <v>260.27822658</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08330899375661283</v>
+        <v>0.08364063826374468</v>
       </c>
       <c r="T11">
-        <v>0.8662585163190031</v>
+        <v>0.8739177428116557</v>
       </c>
       <c r="U11">
         <v>0.0543</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>4.797686971057701</v>
+        <v>4.317918273951932</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07951197443737022</v>
+        <v>0.07948670455622275</v>
       </c>
       <c r="C12">
-        <v>7107.258965619054</v>
+        <v>7032.363970734457</v>
       </c>
       <c r="D12">
-        <v>7902.488965619053</v>
+        <v>7908.416970734457</v>
       </c>
       <c r="E12">
-        <v>-606.47</v>
+        <v>-525.647</v>
       </c>
       <c r="F12">
-        <v>808.23</v>
+        <v>889.053</v>
       </c>
       <c r="G12">
         <v>13</v>
@@ -2271,45 +2271,45 @@
         <v>189.5</v>
       </c>
       <c r="M12">
-        <v>43.886889</v>
+        <v>49.1646309</v>
       </c>
       <c r="N12">
-        <v>145.613111</v>
+        <v>140.3353691</v>
       </c>
       <c r="O12">
-        <v>32.03488442</v>
+        <v>30.873781202</v>
       </c>
       <c r="P12">
-        <v>113.57822658</v>
+        <v>109.461587898</v>
       </c>
       <c r="Q12">
-        <v>260.27822658</v>
+        <v>256.161587898</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08364063826374468</v>
+        <v>0.08397973545643006</v>
       </c>
       <c r="T12">
-        <v>0.8739177428116557</v>
+        <v>0.8817490867535813</v>
       </c>
       <c r="U12">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V12">
         <v>0.22</v>
       </c>
       <c r="W12">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>4.317918273951931</v>
+        <v>3.854396881071673</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07948670455622275</v>
+        <v>0.0793834346750753</v>
       </c>
       <c r="C13">
-        <v>7032.363970734457</v>
+        <v>6975.859545905041</v>
       </c>
       <c r="D13">
-        <v>7908.416970734457</v>
+        <v>7932.735545905041</v>
       </c>
       <c r="E13">
-        <v>-525.647</v>
+        <v>-444.8240000000001</v>
       </c>
       <c r="F13">
-        <v>889.053</v>
+        <v>969.876</v>
       </c>
       <c r="G13">
         <v>13</v>
@@ -2353,28 +2353,28 @@
         <v>189.5</v>
       </c>
       <c r="M13">
-        <v>49.1646309</v>
+        <v>53.6341428</v>
       </c>
       <c r="N13">
-        <v>140.3353691</v>
+        <v>135.8658572</v>
       </c>
       <c r="O13">
-        <v>30.873781202</v>
+        <v>29.890488584</v>
       </c>
       <c r="P13">
-        <v>109.461587898</v>
+        <v>105.975368616</v>
       </c>
       <c r="Q13">
-        <v>256.161587898</v>
+        <v>252.675368616</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08397973545643006</v>
+        <v>0.08432653940349466</v>
       </c>
       <c r="T13">
-        <v>0.8817490867535813</v>
+        <v>0.8897584157850962</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>3.854396881071673</v>
+        <v>3.533197140982367</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0793834346750753</v>
+        <v>0.07928016479392785</v>
       </c>
       <c r="C14">
-        <v>6975.859545905041</v>
+        <v>6919.505142820321</v>
       </c>
       <c r="D14">
-        <v>7932.735545905041</v>
+        <v>7957.204142820321</v>
       </c>
       <c r="E14">
-        <v>-444.8240000000001</v>
+        <v>-364.001</v>
       </c>
       <c r="F14">
-        <v>969.876</v>
+        <v>1050.699</v>
       </c>
       <c r="G14">
         <v>13</v>
@@ -2435,28 +2435,28 @@
         <v>189.5</v>
       </c>
       <c r="M14">
-        <v>53.6341428</v>
+        <v>58.10365470000001</v>
       </c>
       <c r="N14">
-        <v>135.8658572</v>
+        <v>131.3963453</v>
       </c>
       <c r="O14">
-        <v>29.890488584</v>
+        <v>28.907195966</v>
       </c>
       <c r="P14">
-        <v>105.975368616</v>
+        <v>102.489149334</v>
       </c>
       <c r="Q14">
-        <v>252.675368616</v>
+        <v>249.189149334</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08432653940349466</v>
+        <v>0.08468131585508948</v>
       </c>
       <c r="T14">
-        <v>0.8897584157850962</v>
+        <v>0.8979518673230826</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>3.533197140982367</v>
+        <v>3.261412745522185</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07928016479392785</v>
+        <v>0.07917689491278039</v>
       </c>
       <c r="C15">
-        <v>6919.505142820321</v>
+        <v>6863.302154005979</v>
       </c>
       <c r="D15">
-        <v>7957.204142820321</v>
+        <v>7981.824154005979</v>
       </c>
       <c r="E15">
-        <v>-364.001</v>
+        <v>-283.1779999999999</v>
       </c>
       <c r="F15">
-        <v>1050.699</v>
+        <v>1131.522</v>
       </c>
       <c r="G15">
         <v>13</v>
@@ -2517,28 +2517,28 @@
         <v>189.5</v>
       </c>
       <c r="M15">
-        <v>58.10365470000001</v>
+        <v>62.57316660000001</v>
       </c>
       <c r="N15">
-        <v>131.3963453</v>
+        <v>126.9268334</v>
       </c>
       <c r="O15">
-        <v>28.907195966</v>
+        <v>27.923903348</v>
       </c>
       <c r="P15">
-        <v>102.489149334</v>
+        <v>99.002930052</v>
       </c>
       <c r="Q15">
-        <v>249.189149334</v>
+        <v>245.702930052</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08468131585508948</v>
+        <v>0.08504434292183766</v>
       </c>
       <c r="T15">
-        <v>0.8979518673230826</v>
+        <v>0.9063358642456735</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>3.261412745522185</v>
+        <v>3.028454692270599</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07917689491278039</v>
+        <v>0.07936612503163294</v>
       </c>
       <c r="C16">
-        <v>6863.302154005979</v>
+        <v>6737.481361383228</v>
       </c>
       <c r="D16">
-        <v>7981.824154005979</v>
+        <v>7936.826361383229</v>
       </c>
       <c r="E16">
-        <v>-283.1779999999999</v>
+        <v>-202.3549999999998</v>
       </c>
       <c r="F16">
-        <v>1131.522</v>
+        <v>1212.345</v>
       </c>
       <c r="G16">
         <v>13</v>
@@ -2599,45 +2599,45 @@
         <v>189.5</v>
       </c>
       <c r="M16">
-        <v>62.57316660000001</v>
+        <v>70.07354100000002</v>
       </c>
       <c r="N16">
-        <v>126.9268334</v>
+        <v>119.426459</v>
       </c>
       <c r="O16">
-        <v>27.923903348</v>
+        <v>26.27382098</v>
       </c>
       <c r="P16">
-        <v>99.002930052</v>
+        <v>93.15263801999998</v>
       </c>
       <c r="Q16">
-        <v>245.702930052</v>
+        <v>239.85263802</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08504434292183766</v>
+        <v>0.0854159118019211</v>
       </c>
       <c r="T16">
-        <v>0.9063358642456735</v>
+        <v>0.9149171316840899</v>
       </c>
       <c r="U16">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>3.028454692270599</v>
+        <v>2.704301756350517</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07936612503163293</v>
+        <v>0.07928235515048547</v>
       </c>
       <c r="C17">
-        <v>6737.481361383231</v>
+        <v>6676.515596574511</v>
       </c>
       <c r="D17">
-        <v>7936.826361383231</v>
+        <v>7956.68359657451</v>
       </c>
       <c r="E17">
-        <v>-202.355</v>
+        <v>-121.5319999999999</v>
       </c>
       <c r="F17">
-        <v>1212.345</v>
+        <v>1293.168</v>
       </c>
       <c r="G17">
         <v>13</v>
@@ -2681,28 +2681,28 @@
         <v>189.5</v>
       </c>
       <c r="M17">
-        <v>70.07354100000001</v>
+        <v>74.74511040000002</v>
       </c>
       <c r="N17">
-        <v>119.426459</v>
+        <v>114.7548896</v>
       </c>
       <c r="O17">
-        <v>26.27382098</v>
+        <v>25.246075712</v>
       </c>
       <c r="P17">
-        <v>93.15263802</v>
+        <v>89.50881388799999</v>
       </c>
       <c r="Q17">
-        <v>239.85263802</v>
+        <v>236.208813888</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0854159118019211</v>
+        <v>0.08579632756010175</v>
       </c>
       <c r="T17">
-        <v>0.9149171316840899</v>
+        <v>0.9237027150138972</v>
       </c>
       <c r="U17">
         <v>0.0578</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>2.704301756350517</v>
+        <v>2.53528289657861</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07928235515048547</v>
+        <v>0.08003396526933801</v>
       </c>
       <c r="C18">
-        <v>6676.515596574511</v>
+        <v>6421.002815339914</v>
       </c>
       <c r="D18">
-        <v>7956.68359657451</v>
+        <v>7781.993815339914</v>
       </c>
       <c r="E18">
-        <v>-121.5319999999999</v>
+        <v>-40.70899999999983</v>
       </c>
       <c r="F18">
-        <v>1293.168</v>
+        <v>1373.991</v>
       </c>
       <c r="G18">
         <v>13</v>
@@ -2763,45 +2763,45 @@
         <v>189.5</v>
       </c>
       <c r="M18">
-        <v>74.74511040000002</v>
+        <v>88.07282310000002</v>
       </c>
       <c r="N18">
-        <v>114.7548896</v>
+        <v>101.4271769</v>
       </c>
       <c r="O18">
-        <v>25.246075712</v>
+        <v>22.313978918</v>
       </c>
       <c r="P18">
-        <v>89.50881388799999</v>
+        <v>79.11319798199997</v>
       </c>
       <c r="Q18">
-        <v>236.208813888</v>
+        <v>225.813197982</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08579632756010175</v>
+        <v>0.08618590996305785</v>
       </c>
       <c r="T18">
-        <v>0.9237027150138972</v>
+        <v>0.9326999991468325</v>
       </c>
       <c r="U18">
-        <v>0.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="V18">
         <v>0.22</v>
       </c>
       <c r="W18">
-        <v>0.04508400000000001</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>2.53528289657861</v>
+        <v>2.151628542494171</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08003396526933801</v>
+        <v>0.07999933538819055</v>
       </c>
       <c r="C19">
-        <v>6421.002815339914</v>
+        <v>6348.05977902507</v>
       </c>
       <c r="D19">
-        <v>7781.993815339914</v>
+        <v>7789.873779025071</v>
       </c>
       <c r="E19">
-        <v>-40.70899999999983</v>
+        <v>40.11400000000026</v>
       </c>
       <c r="F19">
-        <v>1373.991</v>
+        <v>1454.814</v>
       </c>
       <c r="G19">
         <v>13</v>
@@ -2845,28 +2845,28 @@
         <v>189.5</v>
       </c>
       <c r="M19">
-        <v>88.07282310000002</v>
+        <v>93.25357740000003</v>
       </c>
       <c r="N19">
-        <v>101.4271769</v>
+        <v>96.24642259999997</v>
       </c>
       <c r="O19">
-        <v>22.313978918</v>
+        <v>21.174212972</v>
       </c>
       <c r="P19">
-        <v>79.11319798199997</v>
+        <v>75.07220962799998</v>
       </c>
       <c r="Q19">
-        <v>225.813197982</v>
+        <v>221.772209628</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08618590996305785</v>
+        <v>0.08658499437584213</v>
       </c>
       <c r="T19">
-        <v>0.9326999991468325</v>
+        <v>0.9419167292342296</v>
       </c>
       <c r="U19">
         <v>0.0641</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>2.151628542494171</v>
+        <v>2.032093623466717</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07999933538819055</v>
+        <v>0.0816986455070431</v>
       </c>
       <c r="C20">
-        <v>6348.05977902507</v>
+        <v>5898.492745641295</v>
       </c>
       <c r="D20">
-        <v>7789.873779025071</v>
+        <v>7421.129745641295</v>
       </c>
       <c r="E20">
-        <v>40.11400000000003</v>
+        <v>120.9369999999999</v>
       </c>
       <c r="F20">
-        <v>1454.814</v>
+        <v>1535.637</v>
       </c>
       <c r="G20">
         <v>13</v>
@@ -2927,45 +2927,45 @@
         <v>189.5</v>
       </c>
       <c r="M20">
-        <v>93.25357740000001</v>
+        <v>116.4012846</v>
       </c>
       <c r="N20">
-        <v>96.24642259999999</v>
+        <v>73.09871539999999</v>
       </c>
       <c r="O20">
-        <v>21.174212972</v>
+        <v>16.081717388</v>
       </c>
       <c r="P20">
-        <v>75.072209628</v>
+        <v>57.01699801199999</v>
       </c>
       <c r="Q20">
-        <v>221.772209628</v>
+        <v>203.716998012</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08658499437584213</v>
+        <v>0.08699393272474457</v>
       </c>
       <c r="T20">
-        <v>0.9419167292342294</v>
+        <v>0.9513610329040314</v>
       </c>
       <c r="U20">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V20">
         <v>0.22</v>
       </c>
       <c r="W20">
-        <v>0.04999800000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y20">
-        <v>2.032093623466717</v>
+        <v>1.627988906232397</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0816986455070431</v>
+        <v>0.08175527562589566</v>
       </c>
       <c r="C21">
-        <v>5898.492745641295</v>
+        <v>5805.981350761818</v>
       </c>
       <c r="D21">
-        <v>7421.129745641295</v>
+        <v>7409.441350761818</v>
       </c>
       <c r="E21">
-        <v>120.9369999999999</v>
+        <v>201.76</v>
       </c>
       <c r="F21">
-        <v>1535.637</v>
+        <v>1616.46</v>
       </c>
       <c r="G21">
         <v>13</v>
@@ -3009,28 +3009,28 @@
         <v>189.5</v>
       </c>
       <c r="M21">
-        <v>116.4012846</v>
+        <v>122.527668</v>
       </c>
       <c r="N21">
-        <v>73.09871539999999</v>
+        <v>66.97233199999998</v>
       </c>
       <c r="O21">
-        <v>16.081717388</v>
+        <v>14.73391304</v>
       </c>
       <c r="P21">
-        <v>57.01699801199999</v>
+        <v>52.23841895999998</v>
       </c>
       <c r="Q21">
-        <v>203.716998012</v>
+        <v>198.93841896</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08699393272474457</v>
+        <v>0.08741309453236955</v>
       </c>
       <c r="T21">
-        <v>0.9513610329040314</v>
+        <v>0.9610414441655785</v>
       </c>
       <c r="U21">
         <v>0.07580000000000001</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>1.627988906232397</v>
+        <v>1.546589460920777</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08175527562589566</v>
+        <v>0.08923797039974186</v>
       </c>
       <c r="C22">
-        <v>5805.981350761818</v>
+        <v>4448.796044644612</v>
       </c>
       <c r="D22">
-        <v>7409.441350761818</v>
+        <v>6133.079044644613</v>
       </c>
       <c r="E22">
-        <v>201.76</v>
+        <v>282.5830000000001</v>
       </c>
       <c r="F22">
-        <v>1616.46</v>
+        <v>1697.283</v>
       </c>
       <c r="G22">
         <v>13</v>
@@ -3091,45 +3091,45 @@
         <v>189.5</v>
       </c>
       <c r="M22">
-        <v>122.527668</v>
+        <v>201.2977638</v>
       </c>
       <c r="N22">
-        <v>66.97233199999998</v>
+        <v>-11.79776380000004</v>
       </c>
       <c r="O22">
-        <v>14.73391304</v>
+        <v>-2.595508036000009</v>
       </c>
       <c r="P22">
-        <v>52.23841895999998</v>
+        <v>-9.202255764000032</v>
       </c>
       <c r="Q22">
-        <v>198.93841896</v>
+        <v>137.497744236</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08741309453236955</v>
+        <v>0.08796222224025929</v>
       </c>
       <c r="T22">
-        <v>0.9610414441655785</v>
+        <v>0.9737233773731937</v>
       </c>
       <c r="U22">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V22">
-        <v>0.22</v>
+        <v>0.2071061258356611</v>
       </c>
       <c r="W22">
-        <v>0.05912400000000001</v>
+        <v>0.0940372134758906</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y22">
-        <v>1.546589460920777</v>
+        <v>0.941391481071187</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08923797039974186</v>
+        <v>0.08996597039974186</v>
       </c>
       <c r="C23">
-        <v>4448.796044644612</v>
+        <v>4266.879793345252</v>
       </c>
       <c r="D23">
-        <v>6133.079044644613</v>
+        <v>6031.985793345251</v>
       </c>
       <c r="E23">
-        <v>282.5829999999999</v>
+        <v>363.4059999999999</v>
       </c>
       <c r="F23">
-        <v>1697.283</v>
+        <v>1778.106</v>
       </c>
       <c r="G23">
         <v>13</v>
@@ -3173,37 +3173,37 @@
         <v>189.5</v>
       </c>
       <c r="M23">
-        <v>201.2977638</v>
+        <v>210.8833716</v>
       </c>
       <c r="N23">
-        <v>-11.79776380000001</v>
+        <v>-21.38337160000003</v>
       </c>
       <c r="O23">
-        <v>-2.595508036000003</v>
+        <v>-4.704341752000007</v>
       </c>
       <c r="P23">
-        <v>-9.202255764000011</v>
+        <v>-16.67902984800002</v>
       </c>
       <c r="Q23">
-        <v>137.497744236</v>
+        <v>130.020970152</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08796222224025929</v>
+        <v>0.08850276355103184</v>
       </c>
       <c r="T23">
-        <v>0.9737233773731937</v>
+        <v>0.9862070104164398</v>
       </c>
       <c r="U23">
         <v>0.1186</v>
       </c>
       <c r="V23">
-        <v>0.2071061258356612</v>
+        <v>0.1976922110249493</v>
       </c>
       <c r="W23">
-        <v>0.0940372134758906</v>
+        <v>0.09515370377244102</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.9413914810711871</v>
+        <v>0.8986009592043148</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08996597039974186</v>
+        <v>0.09069397039974186</v>
       </c>
       <c r="C24">
-        <v>4266.879793345252</v>
+        <v>4088.242195561746</v>
       </c>
       <c r="D24">
-        <v>6031.985793345251</v>
+        <v>5934.171195561746</v>
       </c>
       <c r="E24">
-        <v>363.4059999999999</v>
+        <v>444.229</v>
       </c>
       <c r="F24">
-        <v>1778.106</v>
+        <v>1858.929</v>
       </c>
       <c r="G24">
         <v>13</v>
@@ -3255,37 +3255,37 @@
         <v>189.5</v>
       </c>
       <c r="M24">
-        <v>210.8833716</v>
+        <v>220.4689794</v>
       </c>
       <c r="N24">
-        <v>-21.38337160000003</v>
+        <v>-30.96897940000002</v>
       </c>
       <c r="O24">
-        <v>-4.704341752000007</v>
+        <v>-6.813175468000005</v>
       </c>
       <c r="P24">
-        <v>-16.67902984800002</v>
+        <v>-24.15580393200002</v>
       </c>
       <c r="Q24">
-        <v>130.020970152</v>
+        <v>122.544196068</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08850276355103184</v>
+        <v>0.08905734489585043</v>
       </c>
       <c r="T24">
-        <v>0.9862070104164398</v>
+        <v>0.9990148936686013</v>
       </c>
       <c r="U24">
         <v>0.1186</v>
       </c>
       <c r="V24">
-        <v>0.1976922110249493</v>
+        <v>0.1890968975021254</v>
       </c>
       <c r="W24">
-        <v>0.09515370377244102</v>
+        <v>0.09617310795624794</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.8986009592043148</v>
+        <v>0.8595313522823882</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09069397039974186</v>
+        <v>0.09142197039974187</v>
       </c>
       <c r="C25">
-        <v>4088.242195561746</v>
+        <v>3912.726296668596</v>
       </c>
       <c r="D25">
-        <v>5934.171195561746</v>
+        <v>5839.478296668596</v>
       </c>
       <c r="E25">
-        <v>444.229</v>
+        <v>525.0520000000001</v>
       </c>
       <c r="F25">
-        <v>1858.929</v>
+        <v>1939.752</v>
       </c>
       <c r="G25">
         <v>13</v>
@@ -3337,37 +3337,37 @@
         <v>189.5</v>
       </c>
       <c r="M25">
-        <v>220.4689794</v>
+        <v>230.0545872</v>
       </c>
       <c r="N25">
-        <v>-30.96897940000002</v>
+        <v>-40.55458720000004</v>
       </c>
       <c r="O25">
-        <v>-6.813175468000005</v>
+        <v>-8.922009184000009</v>
       </c>
       <c r="P25">
-        <v>-24.15580393200002</v>
+        <v>-31.63257801600003</v>
       </c>
       <c r="Q25">
-        <v>122.544196068</v>
+        <v>115.067421984</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08905734489585043</v>
+        <v>0.08962652048658531</v>
       </c>
       <c r="T25">
-        <v>0.9990148936686013</v>
+        <v>1.01215982648003</v>
       </c>
       <c r="U25">
         <v>0.1186</v>
       </c>
       <c r="V25">
-        <v>0.1890968975021254</v>
+        <v>0.1812178601062035</v>
       </c>
       <c r="W25">
-        <v>0.09617310795624794</v>
+        <v>0.09710756179140427</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.8595313522823882</v>
+        <v>0.8237175459372886</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09142197039974187</v>
+        <v>0.113319957218552</v>
       </c>
       <c r="C26">
-        <v>3912.726296668596</v>
+        <v>1938.051107822094</v>
       </c>
       <c r="D26">
-        <v>5839.478296668596</v>
+        <v>3945.626107822094</v>
       </c>
       <c r="E26">
-        <v>525.0519999999999</v>
+        <v>605.875</v>
       </c>
       <c r="F26">
-        <v>1939.752</v>
+        <v>2020.575</v>
       </c>
       <c r="G26">
         <v>13</v>
@@ -3419,45 +3419,45 @@
         <v>189.5</v>
       </c>
       <c r="M26">
-        <v>230.0545872</v>
+        <v>405.73146</v>
       </c>
       <c r="N26">
-        <v>-40.55458720000001</v>
+        <v>-216.23146</v>
       </c>
       <c r="O26">
-        <v>-8.922009184000004</v>
+        <v>-47.57092120000001</v>
       </c>
       <c r="P26">
-        <v>-31.63257801600001</v>
+        <v>-168.6605388</v>
       </c>
       <c r="Q26">
-        <v>115.067421984</v>
+        <v>-21.96053880000002</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08962652048658531</v>
+        <v>0.09103752318482003</v>
       </c>
       <c r="T26">
-        <v>1.01215982648003</v>
+        <v>1.044746493875751</v>
       </c>
       <c r="U26">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.1812178601062035</v>
+        <v>0.1027526926307366</v>
       </c>
       <c r="W26">
-        <v>0.09710756179140427</v>
+        <v>0.1801672593197481</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y26">
-        <v>0.8237175459372887</v>
+        <v>0.4670576937760754</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.113319957218552</v>
+        <v>0.1148699572185521</v>
       </c>
       <c r="C27">
-        <v>1938.051107822094</v>
+        <v>1768.68425006679</v>
       </c>
       <c r="D27">
-        <v>3945.626107822094</v>
+        <v>3857.08225006679</v>
       </c>
       <c r="E27">
-        <v>605.875</v>
+        <v>686.6980000000001</v>
       </c>
       <c r="F27">
-        <v>2020.575</v>
+        <v>2101.398</v>
       </c>
       <c r="G27">
         <v>13</v>
@@ -3501,37 +3501,37 @@
         <v>189.5</v>
       </c>
       <c r="M27">
-        <v>405.73146</v>
+        <v>421.9607184</v>
       </c>
       <c r="N27">
-        <v>-216.23146</v>
+        <v>-232.4607184</v>
       </c>
       <c r="O27">
-        <v>-47.57092120000001</v>
+        <v>-51.14135804800001</v>
       </c>
       <c r="P27">
-        <v>-168.6605388</v>
+        <v>-181.319360352</v>
       </c>
       <c r="Q27">
-        <v>-21.96053880000002</v>
+        <v>-34.61936035200003</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09103752318482003</v>
+        <v>0.09164884106569599</v>
       </c>
       <c r="T27">
-        <v>1.044746493875751</v>
+        <v>1.058864689738937</v>
       </c>
       <c r="U27">
         <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.1027526926307366</v>
+        <v>0.09880066599109287</v>
       </c>
       <c r="W27">
-        <v>0.1801672593197481</v>
+        <v>0.1809608262689886</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.4670576937760754</v>
+        <v>0.4490939363231494</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1148699572185521</v>
+        <v>0.116419957218552</v>
       </c>
       <c r="C28">
-        <v>1768.68425006679</v>
+        <v>1603.204196691618</v>
       </c>
       <c r="D28">
-        <v>3857.08225006679</v>
+        <v>3772.425196691618</v>
       </c>
       <c r="E28">
-        <v>686.6980000000001</v>
+        <v>767.521</v>
       </c>
       <c r="F28">
-        <v>2101.398</v>
+        <v>2182.221</v>
       </c>
       <c r="G28">
         <v>13</v>
@@ -3583,37 +3583,37 @@
         <v>189.5</v>
       </c>
       <c r="M28">
-        <v>421.9607184</v>
+        <v>438.1899768</v>
       </c>
       <c r="N28">
-        <v>-232.4607184</v>
+        <v>-248.6899768</v>
       </c>
       <c r="O28">
-        <v>-51.14135804800001</v>
+        <v>-54.711794896</v>
       </c>
       <c r="P28">
-        <v>-181.319360352</v>
+        <v>-193.978181904</v>
       </c>
       <c r="Q28">
-        <v>-34.61936035200003</v>
+        <v>-47.27818190400001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09164884106569599</v>
+        <v>0.09227690738166441</v>
       </c>
       <c r="T28">
-        <v>1.058864689738937</v>
+        <v>1.073369685488786</v>
       </c>
       <c r="U28">
         <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.09880066599109287</v>
+        <v>0.09514138206549684</v>
       </c>
       <c r="W28">
-        <v>0.1809608262689886</v>
+        <v>0.1816956104812482</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.4490939363231494</v>
+        <v>0.4324608275704402</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.116419957218552</v>
+        <v>0.1179699572185521</v>
       </c>
       <c r="C29">
-        <v>1603.204196691618</v>
+        <v>1441.360516061797</v>
       </c>
       <c r="D29">
-        <v>3772.425196691618</v>
+        <v>3691.404516061797</v>
       </c>
       <c r="E29">
-        <v>767.521</v>
+        <v>848.3440000000003</v>
       </c>
       <c r="F29">
-        <v>2182.221</v>
+        <v>2263.044</v>
       </c>
       <c r="G29">
         <v>13</v>
@@ -3665,37 +3665,37 @@
         <v>189.5</v>
       </c>
       <c r="M29">
-        <v>438.1899768</v>
+        <v>454.4192352000001</v>
       </c>
       <c r="N29">
-        <v>-248.6899768</v>
+        <v>-264.9192352000001</v>
       </c>
       <c r="O29">
-        <v>-54.711794896</v>
+        <v>-58.28223174400001</v>
       </c>
       <c r="P29">
-        <v>-193.978181904</v>
+        <v>-206.6370034560001</v>
       </c>
       <c r="Q29">
-        <v>-47.27818190400001</v>
+        <v>-59.93700345600007</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09227690738166441</v>
+        <v>0.09292241998418754</v>
       </c>
       <c r="T29">
-        <v>1.073369685488786</v>
+        <v>1.088277597787241</v>
       </c>
       <c r="U29">
         <v>0.2008</v>
       </c>
       <c r="V29">
-        <v>0.09514138206549684</v>
+        <v>0.09174347556315766</v>
       </c>
       <c r="W29">
-        <v>0.1816956104812482</v>
+        <v>0.182377910106918</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.4324608275704402</v>
+        <v>0.4170157980143531</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1179699572185521</v>
+        <v>0.1195199572185521</v>
       </c>
       <c r="C30">
-        <v>1441.360516061797</v>
+        <v>1282.923838358036</v>
       </c>
       <c r="D30">
-        <v>3691.404516061797</v>
+        <v>3613.790838358037</v>
       </c>
       <c r="E30">
-        <v>848.3440000000003</v>
+        <v>929.1670000000001</v>
       </c>
       <c r="F30">
-        <v>2263.044</v>
+        <v>2343.867</v>
       </c>
       <c r="G30">
         <v>13</v>
@@ -3747,37 +3747,37 @@
         <v>189.5</v>
       </c>
       <c r="M30">
-        <v>454.4192352000001</v>
+        <v>470.6484936000001</v>
       </c>
       <c r="N30">
-        <v>-264.9192352000001</v>
+        <v>-281.1484936000001</v>
       </c>
       <c r="O30">
-        <v>-58.28223174400001</v>
+        <v>-61.85266859200001</v>
       </c>
       <c r="P30">
-        <v>-206.6370034560001</v>
+        <v>-219.295825008</v>
       </c>
       <c r="Q30">
-        <v>-59.93700345600007</v>
+        <v>-72.59582500800005</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09292241998418754</v>
+        <v>0.09358611604030286</v>
       </c>
       <c r="T30">
-        <v>1.088277597787241</v>
+        <v>1.103605451277202</v>
       </c>
       <c r="U30">
         <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.09174347556315766</v>
+        <v>0.08857990744029016</v>
       </c>
       <c r="W30">
-        <v>0.182377910106918</v>
+        <v>0.1830131545859897</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.4170157980143531</v>
+        <v>0.4026359429104098</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.119519957218552</v>
+        <v>0.121069957218552</v>
       </c>
       <c r="C31">
-        <v>1282.923838358037</v>
+        <v>1127.683686994566</v>
       </c>
       <c r="D31">
-        <v>3613.790838358037</v>
+        <v>3539.373686994566</v>
       </c>
       <c r="E31">
-        <v>929.1669999999997</v>
+        <v>1009.99</v>
       </c>
       <c r="F31">
-        <v>2343.867</v>
+        <v>2424.69</v>
       </c>
       <c r="G31">
         <v>13</v>
@@ -3829,37 +3829,37 @@
         <v>189.5</v>
       </c>
       <c r="M31">
-        <v>470.6484935999999</v>
+        <v>486.877752</v>
       </c>
       <c r="N31">
-        <v>-281.1484935999999</v>
+        <v>-297.377752</v>
       </c>
       <c r="O31">
-        <v>-61.85266859199999</v>
+        <v>-65.42310544000001</v>
       </c>
       <c r="P31">
-        <v>-219.295825008</v>
+        <v>-231.95464656</v>
       </c>
       <c r="Q31">
-        <v>-72.59582500799996</v>
+        <v>-85.25464656000003</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09358611604030286</v>
+        <v>0.0942687748408786</v>
       </c>
       <c r="T31">
-        <v>1.103605451277202</v>
+        <v>1.119371243438305</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.08857990744029019</v>
+        <v>0.08562724385894716</v>
       </c>
       <c r="W31">
-        <v>0.1830131545859897</v>
+        <v>0.1836060494331234</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.4026359429104099</v>
+        <v>0.3892147448133961</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.121069957218552</v>
+        <v>0.122619957218552</v>
       </c>
       <c r="C32">
-        <v>1127.683686994566</v>
+        <v>975.4465725707073</v>
       </c>
       <c r="D32">
-        <v>3539.373686994566</v>
+        <v>3467.959572570707</v>
       </c>
       <c r="E32">
-        <v>1009.99</v>
+        <v>1090.813</v>
       </c>
       <c r="F32">
-        <v>2424.69</v>
+        <v>2505.513</v>
       </c>
       <c r="G32">
         <v>13</v>
@@ -3911,37 +3911,37 @@
         <v>189.5</v>
       </c>
       <c r="M32">
-        <v>486.877752</v>
+        <v>503.1070104</v>
       </c>
       <c r="N32">
-        <v>-297.377752</v>
+        <v>-313.6070104</v>
       </c>
       <c r="O32">
-        <v>-65.42310544000001</v>
+        <v>-68.993542288</v>
       </c>
       <c r="P32">
-        <v>-231.95464656</v>
+        <v>-244.613468112</v>
       </c>
       <c r="Q32">
-        <v>-85.25464656000003</v>
+        <v>-97.91346811199998</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0942687748408786</v>
+        <v>0.09497122085306525</v>
       </c>
       <c r="T32">
-        <v>1.119371243438305</v>
+        <v>1.135594015082338</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.08562724385894716</v>
+        <v>0.08286507470220694</v>
       </c>
       <c r="W32">
-        <v>0.1836060494331234</v>
+        <v>0.1841606929997968</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3892147448133961</v>
+        <v>0.3766594304645769</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.122619957218552</v>
+        <v>0.124169957218552</v>
       </c>
       <c r="C33">
-        <v>975.4465725707073</v>
+        <v>826.0343130092365</v>
       </c>
       <c r="D33">
-        <v>3467.959572570707</v>
+        <v>3399.370313009237</v>
       </c>
       <c r="E33">
-        <v>1090.813</v>
+        <v>1171.636</v>
       </c>
       <c r="F33">
-        <v>2505.513</v>
+        <v>2586.336</v>
       </c>
       <c r="G33">
         <v>13</v>
@@ -3993,37 +3993,37 @@
         <v>189.5</v>
       </c>
       <c r="M33">
-        <v>503.1070104</v>
+        <v>519.3362688000001</v>
       </c>
       <c r="N33">
-        <v>-313.6070104</v>
+        <v>-329.8362688000001</v>
       </c>
       <c r="O33">
-        <v>-68.993542288</v>
+        <v>-72.56397913600001</v>
       </c>
       <c r="P33">
-        <v>-244.613468112</v>
+        <v>-257.2722896640001</v>
       </c>
       <c r="Q33">
-        <v>-97.91346811199998</v>
+        <v>-110.5722896640001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09497122085306525</v>
+        <v>0.09569432704208092</v>
       </c>
       <c r="T33">
-        <v>1.135594015082338</v>
+        <v>1.152293927068843</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.08286507470220694</v>
+        <v>0.08027554111776296</v>
       </c>
       <c r="W33">
-        <v>0.1841606929997968</v>
+        <v>0.1846806713435532</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3766594304645769</v>
+        <v>0.3648888232625589</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.124169957218552</v>
+        <v>0.125719957218552</v>
       </c>
       <c r="C34">
-        <v>826.0343130092365</v>
+        <v>679.2825491742487</v>
       </c>
       <c r="D34">
-        <v>3399.370313009237</v>
+        <v>3333.441549174249</v>
       </c>
       <c r="E34">
-        <v>1171.636</v>
+        <v>1252.459</v>
       </c>
       <c r="F34">
-        <v>2586.336</v>
+        <v>2667.159</v>
       </c>
       <c r="G34">
         <v>13</v>
@@ -4075,37 +4075,37 @@
         <v>189.5</v>
       </c>
       <c r="M34">
-        <v>519.3362688000001</v>
+        <v>535.5655272</v>
       </c>
       <c r="N34">
-        <v>-329.8362688000001</v>
+        <v>-346.0655272</v>
       </c>
       <c r="O34">
-        <v>-72.56397913600001</v>
+        <v>-76.134415984</v>
       </c>
       <c r="P34">
-        <v>-257.2722896640001</v>
+        <v>-269.931111216</v>
       </c>
       <c r="Q34">
-        <v>-110.5722896640001</v>
+        <v>-123.231111216</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09569432704208092</v>
+        <v>0.09643901849047018</v>
       </c>
       <c r="T34">
-        <v>1.152293927068843</v>
+        <v>1.169492343890767</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.08027554111776296</v>
+        <v>0.07784294896267924</v>
       </c>
       <c r="W34">
-        <v>0.1846806713435532</v>
+        <v>0.185169135848294</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3648888232625589</v>
+        <v>0.3538315861939966</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.125719957218552</v>
+        <v>0.1272699572185521</v>
       </c>
       <c r="C35">
-        <v>679.2825491742487</v>
+        <v>535.0394299349614</v>
       </c>
       <c r="D35">
-        <v>3333.441549174249</v>
+        <v>3270.021429934962</v>
       </c>
       <c r="E35">
-        <v>1252.459</v>
+        <v>1333.282</v>
       </c>
       <c r="F35">
-        <v>2667.159</v>
+        <v>2747.982</v>
       </c>
       <c r="G35">
         <v>13</v>
@@ -4157,37 +4157,37 @@
         <v>189.5</v>
       </c>
       <c r="M35">
-        <v>535.5655272</v>
+        <v>551.7947856000001</v>
       </c>
       <c r="N35">
-        <v>-346.0655272</v>
+        <v>-362.2947856000001</v>
       </c>
       <c r="O35">
-        <v>-76.134415984</v>
+        <v>-79.70485283200001</v>
       </c>
       <c r="P35">
-        <v>-269.931111216</v>
+        <v>-282.589932768</v>
       </c>
       <c r="Q35">
-        <v>-123.231111216</v>
+        <v>-135.8899327680001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09643901849047018</v>
+        <v>0.0972062763463864</v>
       </c>
       <c r="T35">
-        <v>1.169492343890767</v>
+        <v>1.187211924858808</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.07784294896267924</v>
+        <v>0.0755534504637769</v>
       </c>
       <c r="W35">
-        <v>0.185169135848294</v>
+        <v>0.1856288671468736</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3538315861939966</v>
+        <v>0.3434247748353495</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1272699572185521</v>
+        <v>0.1288199572185521</v>
       </c>
       <c r="C36">
-        <v>535.0394299349614</v>
+        <v>393.1644445303418</v>
       </c>
       <c r="D36">
-        <v>3270.021429934962</v>
+        <v>3208.969444530342</v>
       </c>
       <c r="E36">
-        <v>1333.282</v>
+        <v>1414.105</v>
       </c>
       <c r="F36">
-        <v>2747.982</v>
+        <v>2828.805</v>
       </c>
       <c r="G36">
         <v>13</v>
@@ -4239,37 +4239,37 @@
         <v>189.5</v>
       </c>
       <c r="M36">
-        <v>551.7947856000001</v>
+        <v>568.0240440000001</v>
       </c>
       <c r="N36">
-        <v>-362.2947856000001</v>
+        <v>-378.5240440000001</v>
       </c>
       <c r="O36">
-        <v>-79.70485283200001</v>
+        <v>-83.27528968000003</v>
       </c>
       <c r="P36">
-        <v>-282.589932768</v>
+        <v>-295.2487543200001</v>
       </c>
       <c r="Q36">
-        <v>-135.8899327680001</v>
+        <v>-148.5487543200001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.0972062763463864</v>
+        <v>0.09799714213633082</v>
       </c>
       <c r="T36">
-        <v>1.187211924858808</v>
+        <v>1.20547672370279</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.0755534504637769</v>
+        <v>0.07339478045052612</v>
       </c>
       <c r="W36">
-        <v>0.1856288671468736</v>
+        <v>0.1860623280855344</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3434247748353495</v>
+        <v>0.3336126384114824</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1288199572185521</v>
+        <v>0.130369957218552</v>
       </c>
       <c r="C37">
-        <v>393.1644445303418</v>
+        <v>253.5273833363876</v>
       </c>
       <c r="D37">
-        <v>3208.969444530342</v>
+        <v>3150.155383336388</v>
       </c>
       <c r="E37">
-        <v>1414.105</v>
+        <v>1494.928000000001</v>
       </c>
       <c r="F37">
-        <v>2828.805</v>
+        <v>2909.628000000001</v>
       </c>
       <c r="G37">
         <v>13</v>
@@ -4321,37 +4321,37 @@
         <v>189.5</v>
       </c>
       <c r="M37">
-        <v>568.0240440000001</v>
+        <v>584.2533024000002</v>
       </c>
       <c r="N37">
-        <v>-378.5240440000001</v>
+        <v>-394.7533024000002</v>
       </c>
       <c r="O37">
-        <v>-83.27528968000003</v>
+        <v>-86.84572652800004</v>
       </c>
       <c r="P37">
-        <v>-295.2487543200001</v>
+        <v>-307.9075758720001</v>
       </c>
       <c r="Q37">
-        <v>-148.5487543200001</v>
+        <v>-161.2075758720001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09799714213633082</v>
+        <v>0.09881272248221099</v>
       </c>
       <c r="T37">
-        <v>1.20547672370279</v>
+        <v>1.224312297510646</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.07339478045052612</v>
+        <v>0.07135603654912262</v>
       </c>
       <c r="W37">
-        <v>0.1860623280855344</v>
+        <v>0.1864717078609362</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3336126384114824</v>
+        <v>0.3243456206778301</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.130369957218552</v>
+        <v>0.131919957218552</v>
       </c>
       <c r="C38">
-        <v>253.5273833363881</v>
+        <v>116.0074108590316</v>
       </c>
       <c r="D38">
-        <v>3150.155383336388</v>
+        <v>3093.458410859032</v>
       </c>
       <c r="E38">
-        <v>1494.928</v>
+        <v>1575.751</v>
       </c>
       <c r="F38">
-        <v>2909.628</v>
+        <v>2990.451</v>
       </c>
       <c r="G38">
         <v>13</v>
@@ -4403,37 +4403,37 @@
         <v>189.5</v>
       </c>
       <c r="M38">
-        <v>584.2533024000001</v>
+        <v>600.4825608</v>
       </c>
       <c r="N38">
-        <v>-394.7533024000001</v>
+        <v>-410.9825608</v>
       </c>
       <c r="O38">
-        <v>-86.84572652800001</v>
+        <v>-90.416163376</v>
       </c>
       <c r="P38">
-        <v>-307.9075758720001</v>
+        <v>-320.566397424</v>
       </c>
       <c r="Q38">
-        <v>-161.2075758720001</v>
+        <v>-173.866397424</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09881272248221099</v>
+        <v>0.0996541942676429</v>
       </c>
       <c r="T38">
-        <v>1.224312297510646</v>
+        <v>1.243745826042561</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.07135603654912263</v>
+        <v>0.06942749502076798</v>
       </c>
       <c r="W38">
-        <v>0.1864717078609362</v>
+        <v>0.1868589589998298</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3243456206778301</v>
+        <v>0.3155795228216726</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.131919957218552</v>
+        <v>0.133469957218552</v>
       </c>
       <c r="C39">
-        <v>116.0074108590316</v>
+        <v>-19.50776293635863</v>
       </c>
       <c r="D39">
-        <v>3093.458410859032</v>
+        <v>3038.766237063641</v>
       </c>
       <c r="E39">
-        <v>1575.751</v>
+        <v>1656.574</v>
       </c>
       <c r="F39">
-        <v>2990.451</v>
+        <v>3071.274</v>
       </c>
       <c r="G39">
         <v>13</v>
@@ -4485,37 +4485,37 @@
         <v>189.5</v>
       </c>
       <c r="M39">
-        <v>600.4825608</v>
+        <v>616.7118192</v>
       </c>
       <c r="N39">
-        <v>-410.9825608</v>
+        <v>-427.2118192</v>
       </c>
       <c r="O39">
-        <v>-90.416163376</v>
+        <v>-93.98660022400001</v>
       </c>
       <c r="P39">
-        <v>-320.566397424</v>
+        <v>-333.225218976</v>
       </c>
       <c r="Q39">
-        <v>-173.866397424</v>
+        <v>-186.525218976</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.0996541942676429</v>
+        <v>0.1005228103042178</v>
       </c>
       <c r="T39">
-        <v>1.243745826042561</v>
+        <v>1.263806242591635</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.06942749502076798</v>
+        <v>0.06760045567811618</v>
       </c>
       <c r="W39">
-        <v>0.1868589589998298</v>
+        <v>0.1872258284998343</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3155795228216726</v>
+        <v>0.3072747985368918</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.133469957218552</v>
+        <v>0.1350199572185521</v>
       </c>
       <c r="C40">
-        <v>-19.50776293635863</v>
+        <v>-153.1226249175406</v>
       </c>
       <c r="D40">
-        <v>3038.766237063641</v>
+        <v>2985.97437508246</v>
       </c>
       <c r="E40">
-        <v>1656.574</v>
+        <v>1737.397</v>
       </c>
       <c r="F40">
-        <v>3071.274</v>
+        <v>3152.097</v>
       </c>
       <c r="G40">
         <v>13</v>
@@ -4567,37 +4567,37 @@
         <v>189.5</v>
       </c>
       <c r="M40">
-        <v>616.7118192</v>
+        <v>632.9410776000001</v>
       </c>
       <c r="N40">
-        <v>-427.2118192</v>
+        <v>-443.4410776000001</v>
       </c>
       <c r="O40">
-        <v>-93.98660022400001</v>
+        <v>-97.55703707200001</v>
       </c>
       <c r="P40">
-        <v>-333.225218976</v>
+        <v>-345.8840405280001</v>
       </c>
       <c r="Q40">
-        <v>-186.525218976</v>
+        <v>-199.1840405280001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1005228103042178</v>
+        <v>0.1014199055551066</v>
       </c>
       <c r="T40">
-        <v>1.263806242591635</v>
+        <v>1.284524377716088</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.06760045567811618</v>
+        <v>0.06586711066072858</v>
       </c>
       <c r="W40">
-        <v>0.1872258284998343</v>
+        <v>0.1875738841793257</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3072747985368918</v>
+        <v>0.2993959575487662</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1350199572185521</v>
+        <v>0.136569957218552</v>
       </c>
       <c r="C41">
-        <v>-153.1226249175406</v>
+        <v>-284.9345250250285</v>
       </c>
       <c r="D41">
-        <v>2985.97437508246</v>
+        <v>2934.985474974972</v>
       </c>
       <c r="E41">
-        <v>1737.397</v>
+        <v>1818.22</v>
       </c>
       <c r="F41">
-        <v>3152.097</v>
+        <v>3232.92</v>
       </c>
       <c r="G41">
         <v>13</v>
@@ -4649,37 +4649,37 @@
         <v>189.5</v>
       </c>
       <c r="M41">
-        <v>632.9410776000001</v>
+        <v>649.170336</v>
       </c>
       <c r="N41">
-        <v>-443.4410776000001</v>
+        <v>-459.670336</v>
       </c>
       <c r="O41">
-        <v>-97.55703707200001</v>
+        <v>-101.12747392</v>
       </c>
       <c r="P41">
-        <v>-345.8840405280001</v>
+        <v>-358.54286208</v>
       </c>
       <c r="Q41">
-        <v>-199.1840405280001</v>
+        <v>-211.84286208</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1014199055551066</v>
+        <v>0.102346903981025</v>
       </c>
       <c r="T41">
-        <v>1.284524377716088</v>
+        <v>1.305933117344689</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.06586711066072858</v>
+        <v>0.06422043289421037</v>
       </c>
       <c r="W41">
-        <v>0.1875738841793257</v>
+        <v>0.1879045370748426</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2993959575487662</v>
+        <v>0.2919110586100472</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.136569957218552</v>
+        <v>0.1381199572185521</v>
       </c>
       <c r="C42">
-        <v>-284.9345250250285</v>
+        <v>-415.0342753970176</v>
       </c>
       <c r="D42">
-        <v>2934.985474974972</v>
+        <v>2885.708724602983</v>
       </c>
       <c r="E42">
-        <v>1818.22</v>
+        <v>1899.043</v>
       </c>
       <c r="F42">
-        <v>3232.92</v>
+        <v>3313.743</v>
       </c>
       <c r="G42">
         <v>13</v>
@@ -4731,37 +4731,37 @@
         <v>189.5</v>
       </c>
       <c r="M42">
-        <v>649.170336</v>
+        <v>665.3995944000001</v>
       </c>
       <c r="N42">
-        <v>-459.670336</v>
+        <v>-475.8995944000001</v>
       </c>
       <c r="O42">
-        <v>-101.12747392</v>
+        <v>-104.697910768</v>
       </c>
       <c r="P42">
-        <v>-358.54286208</v>
+        <v>-371.201683632</v>
       </c>
       <c r="Q42">
-        <v>-211.84286208</v>
+        <v>-224.501683632</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.102346903981025</v>
+        <v>0.1033053260823983</v>
       </c>
       <c r="T42">
-        <v>1.305933117344689</v>
+        <v>1.328067576960701</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.06422043289421037</v>
+        <v>0.06265408087240036</v>
       </c>
       <c r="W42">
-        <v>0.1879045370748426</v>
+        <v>0.188219060560822</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2919110586100472</v>
+        <v>0.2847912766927289</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1381199572185521</v>
+        <v>0.1396699572185521</v>
       </c>
       <c r="C43">
-        <v>-415.0342753970176</v>
+        <v>-543.5066901370374</v>
       </c>
       <c r="D43">
-        <v>2885.708724602983</v>
+        <v>2838.059309862963</v>
       </c>
       <c r="E43">
-        <v>1899.043</v>
+        <v>1979.866</v>
       </c>
       <c r="F43">
-        <v>3313.743</v>
+        <v>3394.566</v>
       </c>
       <c r="G43">
         <v>13</v>
@@ -4813,37 +4813,37 @@
         <v>189.5</v>
       </c>
       <c r="M43">
-        <v>665.3995944000001</v>
+        <v>681.6288528000001</v>
       </c>
       <c r="N43">
-        <v>-475.8995944000001</v>
+        <v>-492.1288528000001</v>
       </c>
       <c r="O43">
-        <v>-104.697910768</v>
+        <v>-108.268347616</v>
       </c>
       <c r="P43">
-        <v>-371.201683632</v>
+        <v>-383.8605051840001</v>
       </c>
       <c r="Q43">
-        <v>-224.501683632</v>
+        <v>-237.1605051840001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1033053260823983</v>
+        <v>0.10429679722175</v>
       </c>
       <c r="T43">
-        <v>1.328067576960701</v>
+        <v>1.350965293804851</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.06265408087240036</v>
+        <v>0.0611623170421051</v>
       </c>
       <c r="W43">
-        <v>0.188219060560822</v>
+        <v>0.1885186067379453</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2847912766927289</v>
+        <v>0.2780105320095687</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.139669957218552</v>
+        <v>0.1412199572185521</v>
       </c>
       <c r="C44">
-        <v>-543.506690137036</v>
+        <v>-670.4310724737743</v>
       </c>
       <c r="D44">
-        <v>2838.059309862964</v>
+        <v>2791.957927526226</v>
       </c>
       <c r="E44">
-        <v>1979.866</v>
+        <v>2060.689</v>
       </c>
       <c r="F44">
-        <v>3394.566</v>
+        <v>3475.389</v>
       </c>
       <c r="G44">
         <v>13</v>
@@ -4895,37 +4895,37 @@
         <v>189.5</v>
       </c>
       <c r="M44">
-        <v>681.6288528</v>
+        <v>697.8581112000001</v>
       </c>
       <c r="N44">
-        <v>-492.1288528</v>
+        <v>-508.3581112000001</v>
       </c>
       <c r="O44">
-        <v>-108.268347616</v>
+        <v>-111.838784464</v>
       </c>
       <c r="P44">
-        <v>-383.860505184</v>
+        <v>-396.519326736</v>
       </c>
       <c r="Q44">
-        <v>-237.160505184</v>
+        <v>-249.8193267360001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.10429679722175</v>
+        <v>0.1053230568221316</v>
       </c>
       <c r="T44">
-        <v>1.350965293804851</v>
+        <v>1.374666439310199</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.06116231704210512</v>
+        <v>0.05973993757600964</v>
       </c>
       <c r="W44">
-        <v>0.1885186067379453</v>
+        <v>0.1888042205347373</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2780105320095687</v>
+        <v>0.2715451708000438</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1412199572185521</v>
+        <v>0.1427699572185521</v>
       </c>
       <c r="C45">
-        <v>-670.4310724737743</v>
+        <v>-795.8816551993414</v>
       </c>
       <c r="D45">
-        <v>2791.957927526226</v>
+        <v>2747.330344800659</v>
       </c>
       <c r="E45">
-        <v>2060.689</v>
+        <v>2141.512</v>
       </c>
       <c r="F45">
-        <v>3475.389</v>
+        <v>3556.212</v>
       </c>
       <c r="G45">
         <v>13</v>
@@ -4977,37 +4977,37 @@
         <v>189.5</v>
       </c>
       <c r="M45">
-        <v>697.8581112000001</v>
+        <v>714.0873696</v>
       </c>
       <c r="N45">
-        <v>-508.3581112000001</v>
+        <v>-524.5873696</v>
       </c>
       <c r="O45">
-        <v>-111.838784464</v>
+        <v>-115.409221312</v>
       </c>
       <c r="P45">
-        <v>-396.519326736</v>
+        <v>-409.178148288</v>
       </c>
       <c r="Q45">
-        <v>-249.8193267360001</v>
+        <v>-262.478148288</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1053230568221316</v>
+        <v>0.1063859685510982</v>
       </c>
       <c r="T45">
-        <v>1.374666439310199</v>
+        <v>1.399214054297881</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.05973993757600964</v>
+        <v>0.05838221172200943</v>
       </c>
       <c r="W45">
-        <v>0.1888042205347373</v>
+        <v>0.1890768518862205</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2715451708000438</v>
+        <v>0.2653736896454975</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1427699572185521</v>
+        <v>0.1443199572185521</v>
       </c>
       <c r="C46">
-        <v>-795.8816551993414</v>
+        <v>-919.9279995314396</v>
       </c>
       <c r="D46">
-        <v>2747.330344800659</v>
+        <v>2704.107000468561</v>
       </c>
       <c r="E46">
-        <v>2141.512</v>
+        <v>2222.335</v>
       </c>
       <c r="F46">
-        <v>3556.212</v>
+        <v>3637.035</v>
       </c>
       <c r="G46">
         <v>13</v>
@@ -5059,37 +5059,37 @@
         <v>189.5</v>
       </c>
       <c r="M46">
-        <v>714.0873696</v>
+        <v>730.316628</v>
       </c>
       <c r="N46">
-        <v>-524.5873696</v>
+        <v>-540.816628</v>
       </c>
       <c r="O46">
-        <v>-115.409221312</v>
+        <v>-118.97965816</v>
       </c>
       <c r="P46">
-        <v>-409.178148288</v>
+        <v>-421.8369698400001</v>
       </c>
       <c r="Q46">
-        <v>-262.478148288</v>
+        <v>-275.1369698400001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1063859685510982</v>
+        <v>0.1074875316156637</v>
       </c>
       <c r="T46">
-        <v>1.399214054297881</v>
+        <v>1.42465430983057</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.05838221172200943</v>
+        <v>0.05708482923929811</v>
       </c>
       <c r="W46">
-        <v>0.1890768518862205</v>
+        <v>0.1893373662887489</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2653736896454975</v>
+        <v>0.2594764965422641</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1443199572185521</v>
+        <v>0.1458699572185521</v>
       </c>
       <c r="C47">
-        <v>-919.9279995314396</v>
+        <v>-1042.635356907274</v>
       </c>
       <c r="D47">
-        <v>2704.107000468561</v>
+        <v>2662.222643092726</v>
       </c>
       <c r="E47">
-        <v>2222.335</v>
+        <v>2303.158</v>
       </c>
       <c r="F47">
-        <v>3637.035</v>
+        <v>3717.858</v>
       </c>
       <c r="G47">
         <v>13</v>
@@ -5141,37 +5141,37 @@
         <v>189.5</v>
       </c>
       <c r="M47">
-        <v>730.316628</v>
+        <v>746.5458864000001</v>
       </c>
       <c r="N47">
-        <v>-540.816628</v>
+        <v>-557.0458864000001</v>
       </c>
       <c r="O47">
-        <v>-118.97965816</v>
+        <v>-122.550095008</v>
       </c>
       <c r="P47">
-        <v>-421.8369698400001</v>
+        <v>-434.4957913920001</v>
       </c>
       <c r="Q47">
-        <v>-275.1369698400001</v>
+        <v>-287.7957913920001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1074875316156637</v>
+        <v>0.10862989331225</v>
       </c>
       <c r="T47">
-        <v>1.42465430983057</v>
+        <v>1.451036797049655</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.05708482923929811</v>
+        <v>0.05584385469061771</v>
       </c>
       <c r="W47">
-        <v>0.1893373662887489</v>
+        <v>0.189586553978124</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2594764965422641</v>
+        <v>0.2538357031391714</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1458699572185521</v>
+        <v>0.1474199572185521</v>
       </c>
       <c r="C48">
-        <v>-1042.635356907274</v>
+        <v>-1164.064997667012</v>
       </c>
       <c r="D48">
-        <v>2662.222643092726</v>
+        <v>2621.616002332989</v>
       </c>
       <c r="E48">
-        <v>2303.158</v>
+        <v>2383.981000000001</v>
       </c>
       <c r="F48">
-        <v>3717.858</v>
+        <v>3798.681</v>
       </c>
       <c r="G48">
         <v>13</v>
@@ -5223,37 +5223,37 @@
         <v>189.5</v>
       </c>
       <c r="M48">
-        <v>746.5458864000001</v>
+        <v>762.7751448000001</v>
       </c>
       <c r="N48">
-        <v>-557.0458864000001</v>
+        <v>-573.2751448000001</v>
       </c>
       <c r="O48">
-        <v>-122.550095008</v>
+        <v>-126.120531856</v>
       </c>
       <c r="P48">
-        <v>-434.4957913920001</v>
+        <v>-447.1546129440001</v>
       </c>
       <c r="Q48">
-        <v>-287.7957913920001</v>
+        <v>-300.4546129440001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.10862989331225</v>
+        <v>0.1098153629973868</v>
       </c>
       <c r="T48">
-        <v>1.451036797049655</v>
+        <v>1.478414849824176</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.05584385469061771</v>
+        <v>0.05465568756954074</v>
       </c>
       <c r="W48">
-        <v>0.189586553978124</v>
+        <v>0.1898251379360362</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2538357031391714</v>
+        <v>0.2484349434979124</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1474199572185521</v>
+        <v>0.1489699572185521</v>
       </c>
       <c r="C49">
-        <v>-1164.064997667012</v>
+        <v>-1284.274510108886</v>
       </c>
       <c r="D49">
-        <v>2621.616002332989</v>
+        <v>2582.229489891115</v>
       </c>
       <c r="E49">
-        <v>2383.981000000001</v>
+        <v>2464.804</v>
       </c>
       <c r="F49">
-        <v>3798.681</v>
+        <v>3879.504</v>
       </c>
       <c r="G49">
         <v>13</v>
@@ -5305,37 +5305,37 @@
         <v>189.5</v>
       </c>
       <c r="M49">
-        <v>762.7751448000001</v>
+        <v>779.0044032000001</v>
       </c>
       <c r="N49">
-        <v>-573.2751448000001</v>
+        <v>-589.5044032000001</v>
       </c>
       <c r="O49">
-        <v>-126.120531856</v>
+        <v>-129.690968704</v>
       </c>
       <c r="P49">
-        <v>-447.1546129440001</v>
+        <v>-459.813434496</v>
       </c>
       <c r="Q49">
-        <v>-300.4546129440001</v>
+        <v>-313.113434496</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1098153629973868</v>
+        <v>0.1110464276704135</v>
       </c>
       <c r="T49">
-        <v>1.478414849824176</v>
+        <v>1.506845904628488</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.05465568756954074</v>
+        <v>0.05351702741184197</v>
       </c>
       <c r="W49">
-        <v>0.1898251379360362</v>
+        <v>0.1900537808957022</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2484349434979124</v>
+        <v>0.2432592155083726</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1489699572185521</v>
+        <v>0.150519957218552</v>
       </c>
       <c r="C50">
-        <v>-1284.274510108885</v>
+        <v>-1403.318072985722</v>
       </c>
       <c r="D50">
-        <v>2582.229489891115</v>
+        <v>2544.008927014278</v>
       </c>
       <c r="E50">
-        <v>2464.804</v>
+        <v>2545.627</v>
       </c>
       <c r="F50">
-        <v>3879.504</v>
+        <v>3960.327</v>
       </c>
       <c r="G50">
         <v>13</v>
@@ -5387,37 +5387,37 @@
         <v>189.5</v>
       </c>
       <c r="M50">
-        <v>779.0044032</v>
+        <v>795.2336616000001</v>
       </c>
       <c r="N50">
-        <v>-589.5044032</v>
+        <v>-605.7336616000001</v>
       </c>
       <c r="O50">
-        <v>-129.690968704</v>
+        <v>-133.261405552</v>
       </c>
       <c r="P50">
-        <v>-459.813434496</v>
+        <v>-472.4722560480001</v>
       </c>
       <c r="Q50">
-        <v>-313.113434496</v>
+        <v>-325.7722560480001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1110464276704135</v>
+        <v>0.1123257693894412</v>
       </c>
       <c r="T50">
-        <v>1.506845904628488</v>
+        <v>1.536391902758458</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.05351702741184199</v>
+        <v>0.05242484317894724</v>
       </c>
       <c r="W50">
-        <v>0.1900537808957022</v>
+        <v>0.1902730914896674</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2432592155083726</v>
+        <v>0.2382947417224874</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.150519957218552</v>
+        <v>0.152069957218552</v>
       </c>
       <c r="C51">
-        <v>-1403.318072985722</v>
+        <v>-1521.246704154487</v>
       </c>
       <c r="D51">
-        <v>2544.008927014278</v>
+        <v>2506.903295845513</v>
       </c>
       <c r="E51">
-        <v>2545.627</v>
+        <v>2626.45</v>
       </c>
       <c r="F51">
-        <v>3960.327</v>
+        <v>4041.15</v>
       </c>
       <c r="G51">
         <v>13</v>
@@ -5469,37 +5469,37 @@
         <v>189.5</v>
       </c>
       <c r="M51">
-        <v>795.2336616000001</v>
+        <v>811.4629200000001</v>
       </c>
       <c r="N51">
-        <v>-605.7336616000001</v>
+        <v>-621.9629200000001</v>
       </c>
       <c r="O51">
-        <v>-133.261405552</v>
+        <v>-136.8318424</v>
       </c>
       <c r="P51">
-        <v>-472.4722560480001</v>
+        <v>-485.1310776</v>
       </c>
       <c r="Q51">
-        <v>-325.7722560480001</v>
+        <v>-338.4310776</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1123257693894412</v>
+        <v>0.1136562847772301</v>
       </c>
       <c r="T51">
-        <v>1.536391902758458</v>
+        <v>1.567119740813627</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.05242484317894724</v>
+        <v>0.0513763463153683</v>
       </c>
       <c r="W51">
-        <v>0.1902730914896674</v>
+        <v>0.1904836296598741</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2382947417224874</v>
+        <v>0.2335288468880377</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.152069957218552</v>
+        <v>0.153619957218552</v>
       </c>
       <c r="C52">
-        <v>-1521.246704154487</v>
+        <v>-1638.1084877786</v>
       </c>
       <c r="D52">
-        <v>2506.903295845513</v>
+        <v>2470.8645122214</v>
       </c>
       <c r="E52">
-        <v>2626.45</v>
+        <v>2707.273</v>
       </c>
       <c r="F52">
-        <v>4041.15</v>
+        <v>4121.973</v>
       </c>
       <c r="G52">
         <v>13</v>
@@ -5551,37 +5551,37 @@
         <v>189.5</v>
       </c>
       <c r="M52">
-        <v>811.4629200000001</v>
+        <v>827.6921784</v>
       </c>
       <c r="N52">
-        <v>-621.9629200000001</v>
+        <v>-638.1921784</v>
       </c>
       <c r="O52">
-        <v>-136.8318424</v>
+        <v>-140.402279248</v>
       </c>
       <c r="P52">
-        <v>-485.1310776</v>
+        <v>-497.789899152</v>
       </c>
       <c r="Q52">
-        <v>-338.4310776</v>
+        <v>-351.089899152</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1136562847772301</v>
+        <v>0.1150411069155409</v>
       </c>
       <c r="T52">
-        <v>1.567119740813627</v>
+        <v>1.599101776340436</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.0513763463153683</v>
+        <v>0.05036896697585128</v>
       </c>
       <c r="W52">
-        <v>0.1904836296598741</v>
+        <v>0.1906859114312491</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2335288468880377</v>
+        <v>0.228949849890233</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.153619957218552</v>
+        <v>0.155169957218552</v>
       </c>
       <c r="C53">
-        <v>-1638.1084877786</v>
+        <v>-1753.948782210654</v>
       </c>
       <c r="D53">
-        <v>2470.8645122214</v>
+        <v>2435.847217789346</v>
       </c>
       <c r="E53">
-        <v>2707.273</v>
+        <v>2788.096</v>
       </c>
       <c r="F53">
-        <v>4121.973</v>
+        <v>4202.796</v>
       </c>
       <c r="G53">
         <v>13</v>
@@ -5633,37 +5633,37 @@
         <v>189.5</v>
       </c>
       <c r="M53">
-        <v>827.6921784</v>
+        <v>843.9214368</v>
       </c>
       <c r="N53">
-        <v>-638.1921784</v>
+        <v>-654.4214368</v>
       </c>
       <c r="O53">
-        <v>-140.402279248</v>
+        <v>-143.972716096</v>
       </c>
       <c r="P53">
-        <v>-497.789899152</v>
+        <v>-510.448720704</v>
       </c>
       <c r="Q53">
-        <v>-351.089899152</v>
+        <v>-363.748720704</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1150411069155409</v>
+        <v>0.1164836299762813</v>
       </c>
       <c r="T53">
-        <v>1.599101776340436</v>
+        <v>1.632416396680862</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.05036896697585128</v>
+        <v>0.04940033299554644</v>
       </c>
       <c r="W53">
-        <v>0.1906859114312491</v>
+        <v>0.1908804131344943</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.228949849890233</v>
+        <v>0.2245469681615747</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.155169957218552</v>
+        <v>0.1567199572185521</v>
       </c>
       <c r="C54">
-        <v>-1753.948782210654</v>
+        <v>-1868.810410445378</v>
       </c>
       <c r="D54">
-        <v>2435.847217789346</v>
+        <v>2401.808589554623</v>
       </c>
       <c r="E54">
-        <v>2788.096</v>
+        <v>2868.919000000001</v>
       </c>
       <c r="F54">
-        <v>4202.796</v>
+        <v>4283.619000000001</v>
       </c>
       <c r="G54">
         <v>13</v>
@@ -5715,37 +5715,37 @@
         <v>189.5</v>
       </c>
       <c r="M54">
-        <v>843.9214368</v>
+        <v>860.1506952000002</v>
       </c>
       <c r="N54">
-        <v>-654.4214368</v>
+        <v>-670.6506952000002</v>
       </c>
       <c r="O54">
-        <v>-143.972716096</v>
+        <v>-147.543152944</v>
       </c>
       <c r="P54">
-        <v>-510.448720704</v>
+        <v>-523.1075422560002</v>
       </c>
       <c r="Q54">
-        <v>-363.748720704</v>
+        <v>-376.4075422560002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1164836299762813</v>
+        <v>0.1179875369970532</v>
       </c>
       <c r="T54">
-        <v>1.632416396680862</v>
+        <v>1.667148660440029</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.04940033299554644</v>
+        <v>0.04846825124091348</v>
       </c>
       <c r="W54">
-        <v>0.1908804131344943</v>
+        <v>0.1910675751508246</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2245469681615747</v>
+        <v>0.220310232913243</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1567199572185521</v>
+        <v>0.1582699572185521</v>
       </c>
       <c r="C55">
-        <v>-1868.810410445378</v>
+        <v>-1982.733834824266</v>
       </c>
       <c r="D55">
-        <v>2401.808589554623</v>
+        <v>2368.708165175734</v>
       </c>
       <c r="E55">
-        <v>2868.919000000001</v>
+        <v>2949.742</v>
       </c>
       <c r="F55">
-        <v>4283.619000000001</v>
+        <v>4364.442</v>
       </c>
       <c r="G55">
         <v>13</v>
@@ -5797,37 +5797,37 @@
         <v>189.5</v>
       </c>
       <c r="M55">
-        <v>860.1506952000002</v>
+        <v>876.3799536</v>
       </c>
       <c r="N55">
-        <v>-670.6506952000002</v>
+        <v>-686.8799536</v>
       </c>
       <c r="O55">
-        <v>-147.543152944</v>
+        <v>-151.113589792</v>
       </c>
       <c r="P55">
-        <v>-523.1075422560002</v>
+        <v>-535.7663638080001</v>
       </c>
       <c r="Q55">
-        <v>-376.4075422560002</v>
+        <v>-389.0663638080001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1179875369970532</v>
+        <v>0.1195568312795979</v>
       </c>
       <c r="T55">
-        <v>1.667148660440029</v>
+        <v>1.703391022623508</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.04846825124091348</v>
+        <v>0.04757069103274842</v>
       </c>
       <c r="W55">
-        <v>0.1910675751508246</v>
+        <v>0.1912478052406241</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.220310232913243</v>
+        <v>0.2162304137852201</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1582699572185521</v>
+        <v>0.1598199572185521</v>
       </c>
       <c r="C56">
-        <v>-1982.733834824266</v>
+        <v>-2095.757317490515</v>
       </c>
       <c r="D56">
-        <v>2368.708165175734</v>
+        <v>2336.507682509485</v>
       </c>
       <c r="E56">
-        <v>2949.742</v>
+        <v>3030.565000000001</v>
       </c>
       <c r="F56">
-        <v>4364.442</v>
+        <v>4445.265</v>
       </c>
       <c r="G56">
         <v>13</v>
@@ -5879,37 +5879,37 @@
         <v>189.5</v>
       </c>
       <c r="M56">
-        <v>876.3799536</v>
+        <v>892.6092120000001</v>
       </c>
       <c r="N56">
-        <v>-686.8799536</v>
+        <v>-703.1092120000001</v>
       </c>
       <c r="O56">
-        <v>-151.113589792</v>
+        <v>-154.68402664</v>
       </c>
       <c r="P56">
-        <v>-535.7663638080001</v>
+        <v>-548.4251853600001</v>
       </c>
       <c r="Q56">
-        <v>-389.0663638080001</v>
+        <v>-401.7251853600001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1195568312795979</v>
+        <v>0.1211958719747001</v>
       </c>
       <c r="T56">
-        <v>1.703391022623508</v>
+        <v>1.741244156459586</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.04757069103274842</v>
+        <v>0.04670576937760754</v>
       </c>
       <c r="W56">
-        <v>0.1912478052406241</v>
+        <v>0.1914214815089764</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2162304137852201</v>
+        <v>0.2122989517163979</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1598199572185521</v>
+        <v>0.1613699572185521</v>
       </c>
       <c r="C57">
-        <v>-2095.757317490515</v>
+        <v>-2207.917067931991</v>
       </c>
       <c r="D57">
-        <v>2336.507682509485</v>
+        <v>2305.17093206801</v>
       </c>
       <c r="E57">
-        <v>3030.565000000001</v>
+        <v>3111.388000000001</v>
       </c>
       <c r="F57">
-        <v>4445.265</v>
+        <v>4526.088000000001</v>
       </c>
       <c r="G57">
         <v>13</v>
@@ -5961,37 +5961,37 @@
         <v>189.5</v>
       </c>
       <c r="M57">
-        <v>892.6092120000001</v>
+        <v>908.8384704000001</v>
       </c>
       <c r="N57">
-        <v>-703.1092120000001</v>
+        <v>-719.3384704000001</v>
       </c>
       <c r="O57">
-        <v>-154.68402664</v>
+        <v>-158.254463488</v>
       </c>
       <c r="P57">
-        <v>-548.4251853600001</v>
+        <v>-561.0840069120001</v>
       </c>
       <c r="Q57">
-        <v>-401.7251853600001</v>
+        <v>-414.3840069120001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1211958719747001</v>
+        <v>0.1229094145195796</v>
       </c>
       <c r="T57">
-        <v>1.741244156459586</v>
+        <v>1.780817887288213</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.04670576937760754</v>
+        <v>0.04587173778157883</v>
       </c>
       <c r="W57">
-        <v>0.1914214815089764</v>
+        <v>0.191588955053459</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2122989517163979</v>
+        <v>0.2085078990071765</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1613699572185521</v>
+        <v>0.1629199572185521</v>
       </c>
       <c r="C58">
-        <v>-2207.917067931991</v>
+        <v>-2319.247378808462</v>
       </c>
       <c r="D58">
-        <v>2305.17093206801</v>
+        <v>2274.663621191539</v>
       </c>
       <c r="E58">
-        <v>3111.388000000001</v>
+        <v>3192.211000000001</v>
       </c>
       <c r="F58">
-        <v>4526.088000000001</v>
+        <v>4606.911000000001</v>
       </c>
       <c r="G58">
         <v>13</v>
@@ -6043,37 +6043,37 @@
         <v>189.5</v>
       </c>
       <c r="M58">
-        <v>908.8384704000001</v>
+        <v>925.0677288000002</v>
       </c>
       <c r="N58">
-        <v>-719.3384704000001</v>
+        <v>-735.5677288000002</v>
       </c>
       <c r="O58">
-        <v>-158.254463488</v>
+        <v>-161.824900336</v>
       </c>
       <c r="P58">
-        <v>-561.0840069120001</v>
+        <v>-573.7428284640001</v>
       </c>
       <c r="Q58">
-        <v>-414.3840069120001</v>
+        <v>-427.0428284640001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1229094145195796</v>
+        <v>0.1247026567177094</v>
       </c>
       <c r="T58">
-        <v>1.780817887288213</v>
+        <v>1.822232256760032</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.04587173778157883</v>
+        <v>0.04506697045207745</v>
       </c>
       <c r="W58">
-        <v>0.191588955053459</v>
+        <v>0.1917505523332229</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2085078990071765</v>
+        <v>0.2048498656912611</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1629199572185521</v>
+        <v>0.1644699572185521</v>
       </c>
       <c r="C59">
-        <v>-2319.247378808462</v>
+        <v>-2429.780751134236</v>
       </c>
       <c r="D59">
-        <v>2274.663621191539</v>
+        <v>2244.953248865765</v>
       </c>
       <c r="E59">
-        <v>3192.211000000001</v>
+        <v>3273.034000000001</v>
       </c>
       <c r="F59">
-        <v>4606.911000000001</v>
+        <v>4687.734</v>
       </c>
       <c r="G59">
         <v>13</v>
@@ -6125,37 +6125,37 @@
         <v>189.5</v>
       </c>
       <c r="M59">
-        <v>925.0677288000002</v>
+        <v>941.2969872000001</v>
       </c>
       <c r="N59">
-        <v>-735.5677288000002</v>
+        <v>-751.7969872000001</v>
       </c>
       <c r="O59">
-        <v>-161.824900336</v>
+        <v>-165.395337184</v>
       </c>
       <c r="P59">
-        <v>-573.7428284640001</v>
+        <v>-586.4016500160001</v>
       </c>
       <c r="Q59">
-        <v>-427.0428284640001</v>
+        <v>-439.7016500160001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1247026567177094</v>
+        <v>0.1265812914014644</v>
       </c>
       <c r="T59">
-        <v>1.822232256760032</v>
+        <v>1.865618739063842</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.04506697045207745</v>
+        <v>0.04428995372014508</v>
       </c>
       <c r="W59">
-        <v>0.1917505523332229</v>
+        <v>0.1919065772929949</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2048498656912611</v>
+        <v>0.2013179714552049</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.164469957218552</v>
+        <v>0.1868027332156175</v>
       </c>
       <c r="C60">
-        <v>-2429.780751134234</v>
+        <v>-2866.171596433637</v>
       </c>
       <c r="D60">
-        <v>2244.953248865766</v>
+        <v>1889.385403566363</v>
       </c>
       <c r="E60">
-        <v>3273.034</v>
+        <v>3353.857</v>
       </c>
       <c r="F60">
-        <v>4687.733999999999</v>
+        <v>4768.557</v>
       </c>
       <c r="G60">
         <v>13</v>
@@ -6207,45 +6207,45 @@
         <v>189.5</v>
       </c>
       <c r="M60">
-        <v>941.2969871999999</v>
+        <v>1124.4257406</v>
       </c>
       <c r="N60">
-        <v>-751.7969871999999</v>
+        <v>-934.9257405999999</v>
       </c>
       <c r="O60">
-        <v>-165.395337184</v>
+        <v>-205.683662932</v>
       </c>
       <c r="P60">
-        <v>-586.4016500159998</v>
+        <v>-729.242077668</v>
       </c>
       <c r="Q60">
-        <v>-439.7016500159999</v>
+        <v>-582.542077668</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1265812914014643</v>
+        <v>0.1288754106967817</v>
       </c>
       <c r="T60">
-        <v>1.865618739063841</v>
+        <v>1.918600708932603</v>
       </c>
       <c r="U60">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.0442899537201451</v>
+        <v>0.03707670368498855</v>
       </c>
       <c r="W60">
-        <v>0.1919065772929949</v>
+        <v>0.2270573132710797</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.2013179714552049</v>
+        <v>0.1685304712954026</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1868027332156175</v>
+        <v>0.1887027332156175</v>
       </c>
       <c r="C61">
-        <v>-2866.171596433637</v>
+        <v>-2972.115405434257</v>
       </c>
       <c r="D61">
-        <v>1889.385403566363</v>
+        <v>1864.264594565743</v>
       </c>
       <c r="E61">
-        <v>3353.857</v>
+        <v>3434.68</v>
       </c>
       <c r="F61">
-        <v>4768.557</v>
+        <v>4849.38</v>
       </c>
       <c r="G61">
         <v>13</v>
@@ -6289,37 +6289,37 @@
         <v>189.5</v>
       </c>
       <c r="M61">
-        <v>1124.4257406</v>
+        <v>1143.483804</v>
       </c>
       <c r="N61">
-        <v>-934.9257405999999</v>
+        <v>-953.983804</v>
       </c>
       <c r="O61">
-        <v>-205.683662932</v>
+        <v>-209.87643688</v>
       </c>
       <c r="P61">
-        <v>-729.242077668</v>
+        <v>-744.1073671199999</v>
       </c>
       <c r="Q61">
-        <v>-582.542077668</v>
+        <v>-597.4073671199999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1288754106967817</v>
+        <v>0.1309522959642013</v>
       </c>
       <c r="T61">
-        <v>1.918600708932603</v>
+        <v>1.966565726655919</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03707670368498855</v>
+        <v>0.03645875862357208</v>
       </c>
       <c r="W61">
-        <v>0.2270573132710797</v>
+        <v>0.2272030247165617</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1685304712954026</v>
+        <v>0.1657216301071458</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1887027332156175</v>
+        <v>0.1906027332156175</v>
       </c>
       <c r="C62">
-        <v>-2972.115405434257</v>
+        <v>-3077.399979128454</v>
       </c>
       <c r="D62">
-        <v>1864.264594565743</v>
+        <v>1839.803020871546</v>
       </c>
       <c r="E62">
-        <v>3434.68</v>
+        <v>3515.503000000001</v>
       </c>
       <c r="F62">
-        <v>4849.38</v>
+        <v>4930.203</v>
       </c>
       <c r="G62">
         <v>13</v>
@@ -6371,37 +6371,37 @@
         <v>189.5</v>
       </c>
       <c r="M62">
-        <v>1143.483804</v>
+        <v>1162.5418674</v>
       </c>
       <c r="N62">
-        <v>-953.983804</v>
+        <v>-973.0418674000002</v>
       </c>
       <c r="O62">
-        <v>-209.87643688</v>
+        <v>-214.0692108280001</v>
       </c>
       <c r="P62">
-        <v>-744.1073671199999</v>
+        <v>-758.9726565720002</v>
       </c>
       <c r="Q62">
-        <v>-597.4073671199999</v>
+        <v>-612.2726565720002</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1309522959642013</v>
+        <v>0.1331356881684116</v>
       </c>
       <c r="T62">
-        <v>1.966565726655919</v>
+        <v>2.016990488877866</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03645875862357208</v>
+        <v>0.03586107405597252</v>
       </c>
       <c r="W62">
-        <v>0.2272030247165617</v>
+        <v>0.2273439587376017</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1657216301071458</v>
+        <v>0.1630048820726024</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1906027332156175</v>
+        <v>0.1925027332156175</v>
       </c>
       <c r="C63">
-        <v>-3077.399979128454</v>
+        <v>-3182.050931498763</v>
       </c>
       <c r="D63">
-        <v>1839.803020871546</v>
+        <v>1815.975068501237</v>
       </c>
       <c r="E63">
-        <v>3515.503000000001</v>
+        <v>3596.326</v>
       </c>
       <c r="F63">
-        <v>4930.203</v>
+        <v>5011.026</v>
       </c>
       <c r="G63">
         <v>13</v>
@@ -6453,37 +6453,37 @@
         <v>189.5</v>
       </c>
       <c r="M63">
-        <v>1162.5418674</v>
+        <v>1181.5999308</v>
       </c>
       <c r="N63">
-        <v>-973.0418674000002</v>
+        <v>-992.0999308</v>
       </c>
       <c r="O63">
-        <v>-214.0692108280001</v>
+        <v>-218.261984776</v>
       </c>
       <c r="P63">
-        <v>-758.9726565720002</v>
+        <v>-773.8379460240001</v>
       </c>
       <c r="Q63">
-        <v>-612.2726565720002</v>
+        <v>-627.137946024</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1331356881684116</v>
+        <v>0.1354339957517908</v>
       </c>
       <c r="T63">
-        <v>2.016990488877866</v>
+        <v>2.070069185953598</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.03586107405597252</v>
+        <v>0.03528266963571491</v>
       </c>
       <c r="W63">
-        <v>0.2273439587376017</v>
+        <v>0.2274803464998984</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1630048820726024</v>
+        <v>0.1603757710714314</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1925027332156175</v>
+        <v>0.1944027332156175</v>
       </c>
       <c r="C64">
-        <v>-3182.050931498763</v>
+        <v>-3286.092566550017</v>
       </c>
       <c r="D64">
-        <v>1815.975068501237</v>
+        <v>1792.756433449983</v>
       </c>
       <c r="E64">
-        <v>3596.326</v>
+        <v>3677.149</v>
       </c>
       <c r="F64">
-        <v>5011.026</v>
+        <v>5091.849</v>
       </c>
       <c r="G64">
         <v>13</v>
@@ -6535,37 +6535,37 @@
         <v>189.5</v>
       </c>
       <c r="M64">
-        <v>1181.5999308</v>
+        <v>1200.6579942</v>
       </c>
       <c r="N64">
-        <v>-992.0999308</v>
+        <v>-1011.1579942</v>
       </c>
       <c r="O64">
-        <v>-218.261984776</v>
+        <v>-222.454758724</v>
       </c>
       <c r="P64">
-        <v>-773.8379460240001</v>
+        <v>-788.703235476</v>
       </c>
       <c r="Q64">
-        <v>-627.137946024</v>
+        <v>-642.0032354760001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1354339957517908</v>
+        <v>0.1378565361775149</v>
       </c>
       <c r="T64">
-        <v>2.070069185953598</v>
+        <v>2.126017001790182</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.03528266963571491</v>
+        <v>0.03472262726054483</v>
       </c>
       <c r="W64">
-        <v>0.2274803464998984</v>
+        <v>0.2276124044919635</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1603757710714314</v>
+        <v>0.1578301239115674</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1944027332156175</v>
+        <v>0.1963027332156176</v>
       </c>
       <c r="C65">
-        <v>-3286.092566550017</v>
+        <v>-3389.547960997467</v>
       </c>
       <c r="D65">
-        <v>1792.756433449983</v>
+        <v>1770.124039002534</v>
       </c>
       <c r="E65">
-        <v>3677.149</v>
+        <v>3757.972000000001</v>
       </c>
       <c r="F65">
-        <v>5091.849</v>
+        <v>5172.672</v>
       </c>
       <c r="G65">
         <v>13</v>
@@ -6617,37 +6617,37 @@
         <v>189.5</v>
       </c>
       <c r="M65">
-        <v>1200.6579942</v>
+        <v>1219.7160576</v>
       </c>
       <c r="N65">
-        <v>-1011.1579942</v>
+        <v>-1030.2160576</v>
       </c>
       <c r="O65">
-        <v>-222.454758724</v>
+        <v>-226.647532672</v>
       </c>
       <c r="P65">
-        <v>-788.703235476</v>
+        <v>-803.5685249280001</v>
       </c>
       <c r="Q65">
-        <v>-642.0032354760001</v>
+        <v>-656.8685249280002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1378565361775149</v>
+        <v>0.1404136621824459</v>
       </c>
       <c r="T65">
-        <v>2.126017001790182</v>
+        <v>2.185073029617688</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03472262726054483</v>
+        <v>0.03418008620959882</v>
       </c>
       <c r="W65">
-        <v>0.2276124044919635</v>
+        <v>0.2277403356717766</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1578301239115674</v>
+        <v>0.1553640282254491</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1963027332156176</v>
+        <v>0.1982027332156175</v>
       </c>
       <c r="C66">
-        <v>-3389.547960997467</v>
+        <v>-3492.439040769675</v>
       </c>
       <c r="D66">
-        <v>1770.124039002534</v>
+        <v>1748.055959230325</v>
       </c>
       <c r="E66">
-        <v>3757.972000000001</v>
+        <v>3838.795</v>
       </c>
       <c r="F66">
-        <v>5172.672</v>
+        <v>5253.495</v>
       </c>
       <c r="G66">
         <v>13</v>
@@ -6699,37 +6699,37 @@
         <v>189.5</v>
       </c>
       <c r="M66">
-        <v>1219.7160576</v>
+        <v>1238.774121</v>
       </c>
       <c r="N66">
-        <v>-1030.2160576</v>
+        <v>-1049.274121</v>
       </c>
       <c r="O66">
-        <v>-226.647532672</v>
+        <v>-230.84030662</v>
       </c>
       <c r="P66">
-        <v>-803.5685249280001</v>
+        <v>-818.4338143799999</v>
       </c>
       <c r="Q66">
-        <v>-656.8685249280002</v>
+        <v>-671.73381438</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1404136621824459</v>
+        <v>0.1431169096733729</v>
       </c>
       <c r="T66">
-        <v>2.185073029617688</v>
+        <v>2.247503687606764</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03418008620959882</v>
+        <v>0.03365423872945115</v>
       </c>
       <c r="W66">
-        <v>0.2277403356717766</v>
+        <v>0.2278643305075954</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1553640282254491</v>
+        <v>0.1529738124065961</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1982027332156175</v>
+        <v>0.2001027332156176</v>
       </c>
       <c r="C67">
-        <v>-3492.439040769675</v>
+        <v>-3594.786651859334</v>
       </c>
       <c r="D67">
-        <v>1748.055959230325</v>
+        <v>1726.531348140667</v>
       </c>
       <c r="E67">
-        <v>3838.795</v>
+        <v>3919.618</v>
       </c>
       <c r="F67">
-        <v>5253.495</v>
+        <v>5334.318</v>
       </c>
       <c r="G67">
         <v>13</v>
@@ -6781,37 +6781,37 @@
         <v>189.5</v>
       </c>
       <c r="M67">
-        <v>1238.774121</v>
+        <v>1257.8321844</v>
       </c>
       <c r="N67">
-        <v>-1049.274121</v>
+        <v>-1068.3321844</v>
       </c>
       <c r="O67">
-        <v>-230.84030662</v>
+        <v>-235.033080568</v>
       </c>
       <c r="P67">
-        <v>-818.4338143799999</v>
+        <v>-833.2991038320001</v>
       </c>
       <c r="Q67">
-        <v>-671.73381438</v>
+        <v>-686.5991038320001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1431169096733729</v>
+        <v>0.1459791717225898</v>
       </c>
       <c r="T67">
-        <v>2.247503687606764</v>
+        <v>2.313606737242258</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03365423872945115</v>
+        <v>0.03314432602142915</v>
       </c>
       <c r="W67">
-        <v>0.2278643305075954</v>
+        <v>0.227984567924147</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1529738124065961</v>
+        <v>0.1506560273701325</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2001027332156176</v>
+        <v>0.2020027332156175</v>
       </c>
       <c r="C68">
-        <v>-3594.786651859334</v>
+        <v>-3696.610626003231</v>
       </c>
       <c r="D68">
-        <v>1726.531348140667</v>
+        <v>1705.530373996769</v>
       </c>
       <c r="E68">
-        <v>3919.618</v>
+        <v>4000.441000000001</v>
       </c>
       <c r="F68">
-        <v>5334.318</v>
+        <v>5415.141000000001</v>
       </c>
       <c r="G68">
         <v>13</v>
@@ -6863,37 +6863,37 @@
         <v>189.5</v>
       </c>
       <c r="M68">
-        <v>1257.8321844</v>
+        <v>1276.8902478</v>
       </c>
       <c r="N68">
-        <v>-1068.3321844</v>
+        <v>-1087.3902478</v>
       </c>
       <c r="O68">
-        <v>-235.033080568</v>
+        <v>-239.2258545160001</v>
       </c>
       <c r="P68">
-        <v>-833.2991038320001</v>
+        <v>-848.1643932840002</v>
       </c>
       <c r="Q68">
-        <v>-686.5991038320001</v>
+        <v>-701.4643932840002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1459791717225898</v>
+        <v>0.1490149041990319</v>
       </c>
       <c r="T68">
-        <v>2.313606737242258</v>
+        <v>2.383716032310205</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03314432602142915</v>
+        <v>0.0326496345882735</v>
       </c>
       <c r="W68">
-        <v>0.227984567924147</v>
+        <v>0.2281012161640851</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1506560273701325</v>
+        <v>0.1484074299466976</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2020027332156175</v>
+        <v>0.2039027332156176</v>
       </c>
       <c r="C69">
-        <v>-3696.610626003231</v>
+        <v>-3797.929841626365</v>
       </c>
       <c r="D69">
-        <v>1705.530373996769</v>
+        <v>1685.034158373636</v>
       </c>
       <c r="E69">
-        <v>4000.441000000001</v>
+        <v>4081.264000000001</v>
       </c>
       <c r="F69">
-        <v>5415.141000000001</v>
+        <v>5495.964000000001</v>
       </c>
       <c r="G69">
         <v>13</v>
@@ -6945,37 +6945,37 @@
         <v>189.5</v>
       </c>
       <c r="M69">
-        <v>1276.8902478</v>
+        <v>1295.9483112</v>
       </c>
       <c r="N69">
-        <v>-1087.3902478</v>
+        <v>-1106.4483112</v>
       </c>
       <c r="O69">
-        <v>-239.2258545160001</v>
+        <v>-243.4186284640001</v>
       </c>
       <c r="P69">
-        <v>-848.1643932840002</v>
+        <v>-863.0296827360003</v>
       </c>
       <c r="Q69">
-        <v>-701.4643932840002</v>
+        <v>-716.3296827360002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1490149041990319</v>
+        <v>0.1522403699552516</v>
       </c>
       <c r="T69">
-        <v>2.383716032310205</v>
+        <v>2.458207158319899</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0326496345882735</v>
+        <v>0.03216949290315183</v>
       </c>
       <c r="W69">
-        <v>0.2281012161640851</v>
+        <v>0.2282144335734368</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1484074299466976</v>
+        <v>0.1462249677415992</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2039027332156176</v>
+        <v>0.2058027332156175</v>
       </c>
       <c r="C70">
-        <v>-3797.929841626365</v>
+        <v>-3898.762280443859</v>
       </c>
       <c r="D70">
-        <v>1685.034158373636</v>
+        <v>1665.024719556141</v>
       </c>
       <c r="E70">
-        <v>4081.264000000001</v>
+        <v>4162.087</v>
       </c>
       <c r="F70">
-        <v>5495.964000000001</v>
+        <v>5576.787</v>
       </c>
       <c r="G70">
         <v>13</v>
@@ -7027,37 +7027,37 @@
         <v>189.5</v>
       </c>
       <c r="M70">
-        <v>1295.9483112</v>
+        <v>1315.0063746</v>
       </c>
       <c r="N70">
-        <v>-1106.4483112</v>
+        <v>-1125.5063746</v>
       </c>
       <c r="O70">
-        <v>-243.4186284640001</v>
+        <v>-247.611402412</v>
       </c>
       <c r="P70">
-        <v>-863.0296827360003</v>
+        <v>-877.8949721880001</v>
       </c>
       <c r="Q70">
-        <v>-716.3296827360002</v>
+        <v>-731.1949721880001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1522403699552516</v>
+        <v>0.1556739302763888</v>
       </c>
       <c r="T70">
-        <v>2.458207158319899</v>
+        <v>2.537504163426993</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03216949290315183</v>
+        <v>0.03170326836832354</v>
       </c>
       <c r="W70">
-        <v>0.2282144335734368</v>
+        <v>0.2283243693187493</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1462249677415992</v>
+        <v>0.1441057653105615</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2058027332156175</v>
+        <v>0.2077027332156176</v>
       </c>
       <c r="C71">
-        <v>-3898.762280443859</v>
+        <v>-3999.125080077405</v>
       </c>
       <c r="D71">
-        <v>1665.024719556141</v>
+        <v>1645.484919922595</v>
       </c>
       <c r="E71">
-        <v>4162.087</v>
+        <v>4242.910000000001</v>
       </c>
       <c r="F71">
-        <v>5576.787</v>
+        <v>5657.610000000001</v>
       </c>
       <c r="G71">
         <v>13</v>
@@ -7109,37 +7109,37 @@
         <v>189.5</v>
       </c>
       <c r="M71">
-        <v>1315.0063746</v>
+        <v>1334.064438</v>
       </c>
       <c r="N71">
-        <v>-1125.5063746</v>
+        <v>-1144.564438</v>
       </c>
       <c r="O71">
-        <v>-247.611402412</v>
+        <v>-251.80417636</v>
       </c>
       <c r="P71">
-        <v>-877.8949721880001</v>
+        <v>-892.7602616400001</v>
       </c>
       <c r="Q71">
-        <v>-731.1949721880001</v>
+        <v>-746.0602616400001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1556739302763888</v>
+        <v>0.1593363946189351</v>
       </c>
       <c r="T71">
-        <v>2.537504163426993</v>
+        <v>2.622087635541225</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03170326836832354</v>
+        <v>0.03125036453449034</v>
       </c>
       <c r="W71">
-        <v>0.2283243693187493</v>
+        <v>0.2284311640427672</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1441057653105615</v>
+        <v>0.1420471115204107</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2077027332156176</v>
+        <v>0.2096027332156176</v>
       </c>
       <c r="C72">
-        <v>-3999.125080077405</v>
+        <v>-4099.034583009793</v>
       </c>
       <c r="D72">
-        <v>1645.484919922595</v>
+        <v>1626.398416990208</v>
       </c>
       <c r="E72">
-        <v>4242.910000000001</v>
+        <v>4323.733000000001</v>
       </c>
       <c r="F72">
-        <v>5657.610000000001</v>
+        <v>5738.433000000001</v>
       </c>
       <c r="G72">
         <v>13</v>
@@ -7191,37 +7191,37 @@
         <v>189.5</v>
       </c>
       <c r="M72">
-        <v>1334.064438</v>
+        <v>1353.1225014</v>
       </c>
       <c r="N72">
-        <v>-1144.564438</v>
+        <v>-1163.6225014</v>
       </c>
       <c r="O72">
-        <v>-251.80417636</v>
+        <v>-255.9969503080001</v>
       </c>
       <c r="P72">
-        <v>-892.7602616400001</v>
+        <v>-907.6255510920003</v>
       </c>
       <c r="Q72">
-        <v>-746.0602616400001</v>
+        <v>-760.9255510920002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1593363946189351</v>
+        <v>0.1632514427092432</v>
       </c>
       <c r="T72">
-        <v>2.622087635541225</v>
+        <v>2.712504450559889</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03125036453449034</v>
+        <v>0.03081021855513132</v>
       </c>
       <c r="W72">
-        <v>0.2284311640427672</v>
+        <v>0.2285349504647</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1420471115204107</v>
+        <v>0.1400464479778697</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2096027332156175</v>
+        <v>0.2115027332156175</v>
       </c>
       <c r="C73">
-        <v>-4099.034583009792</v>
+        <v>-4198.506382171484</v>
       </c>
       <c r="D73">
-        <v>1626.398416990208</v>
+        <v>1607.749617828517</v>
       </c>
       <c r="E73">
-        <v>4323.733</v>
+        <v>4404.556</v>
       </c>
       <c r="F73">
-        <v>5738.433</v>
+        <v>5819.256</v>
       </c>
       <c r="G73">
         <v>13</v>
@@ -7273,37 +7273,37 @@
         <v>189.5</v>
       </c>
       <c r="M73">
-        <v>1353.1225014</v>
+        <v>1372.1805648</v>
       </c>
       <c r="N73">
-        <v>-1163.6225014</v>
+        <v>-1182.6805648</v>
       </c>
       <c r="O73">
-        <v>-255.996950308</v>
+        <v>-260.189724256</v>
       </c>
       <c r="P73">
-        <v>-907.6255510920001</v>
+        <v>-922.4908405440001</v>
       </c>
       <c r="Q73">
-        <v>-760.9255510920002</v>
+        <v>-775.790840544</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1632514427092432</v>
+        <v>0.1674461370917161</v>
       </c>
       <c r="T73">
-        <v>2.712504450559888</v>
+        <v>2.809379609508455</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03081021855513133</v>
+        <v>0.03038229885297672</v>
       </c>
       <c r="W73">
-        <v>0.2285349504647</v>
+        <v>0.2286358539304681</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1400464479778697</v>
+        <v>0.1381013584226215</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2115027332156175</v>
+        <v>0.2134027332156175</v>
       </c>
       <c r="C74">
-        <v>-4198.506382171484</v>
+        <v>-4297.555363426481</v>
       </c>
       <c r="D74">
-        <v>1607.749617828517</v>
+        <v>1589.523636573519</v>
       </c>
       <c r="E74">
-        <v>4404.556</v>
+        <v>4485.379</v>
       </c>
       <c r="F74">
-        <v>5819.256</v>
+        <v>5900.079</v>
       </c>
       <c r="G74">
         <v>13</v>
@@ -7355,37 +7355,37 @@
         <v>189.5</v>
       </c>
       <c r="M74">
-        <v>1372.1805648</v>
+        <v>1391.2386282</v>
       </c>
       <c r="N74">
-        <v>-1182.6805648</v>
+        <v>-1201.7386282</v>
       </c>
       <c r="O74">
-        <v>-260.189724256</v>
+        <v>-264.382498204</v>
       </c>
       <c r="P74">
-        <v>-922.4908405440001</v>
+        <v>-937.3561299959999</v>
       </c>
       <c r="Q74">
-        <v>-775.790840544</v>
+        <v>-790.6561299959999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1674461370917161</v>
+        <v>0.1719515495765945</v>
       </c>
       <c r="T74">
-        <v>2.809379609508455</v>
+        <v>2.913430706156916</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03038229885297672</v>
+        <v>0.02996610297827842</v>
       </c>
       <c r="W74">
-        <v>0.2286358539304681</v>
+        <v>0.228733992917722</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1381013584226215</v>
+        <v>0.1362095589921746</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2134027332156175</v>
+        <v>0.2153027332156175</v>
       </c>
       <c r="C75">
-        <v>-4297.555363426481</v>
+        <v>-4396.195745200778</v>
       </c>
       <c r="D75">
-        <v>1589.523636573519</v>
+        <v>1571.706254799222</v>
       </c>
       <c r="E75">
-        <v>4485.379</v>
+        <v>4566.202</v>
       </c>
       <c r="F75">
-        <v>5900.079</v>
+        <v>5980.902</v>
       </c>
       <c r="G75">
         <v>13</v>
@@ -7437,37 +7437,37 @@
         <v>189.5</v>
       </c>
       <c r="M75">
-        <v>1391.2386282</v>
+        <v>1410.2966916</v>
       </c>
       <c r="N75">
-        <v>-1201.7386282</v>
+        <v>-1220.7966916</v>
       </c>
       <c r="O75">
-        <v>-264.382498204</v>
+        <v>-268.575272152</v>
       </c>
       <c r="P75">
-        <v>-937.3561299959999</v>
+        <v>-952.221419448</v>
       </c>
       <c r="Q75">
-        <v>-790.6561299959999</v>
+        <v>-805.521419448</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1719515495765945</v>
+        <v>0.1768035322526174</v>
       </c>
       <c r="T75">
-        <v>2.913430706156916</v>
+        <v>3.025485733316798</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02996610297827842</v>
+        <v>0.02956115564073412</v>
       </c>
       <c r="W75">
-        <v>0.228733992917722</v>
+        <v>0.2288294794999149</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1362095589921746</v>
+        <v>0.1343688892760642</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2153027332156175</v>
+        <v>0.2172027332156176</v>
       </c>
       <c r="C76">
-        <v>-4396.195745200778</v>
+        <v>-4494.441115475132</v>
       </c>
       <c r="D76">
-        <v>1571.706254799222</v>
+        <v>1554.283884524868</v>
       </c>
       <c r="E76">
-        <v>4566.202</v>
+        <v>4647.025000000001</v>
       </c>
       <c r="F76">
-        <v>5980.902</v>
+        <v>6061.725</v>
       </c>
       <c r="G76">
         <v>13</v>
@@ -7519,37 +7519,37 @@
         <v>189.5</v>
       </c>
       <c r="M76">
-        <v>1410.2966916</v>
+        <v>1429.354755</v>
       </c>
       <c r="N76">
-        <v>-1220.7966916</v>
+        <v>-1239.854755</v>
       </c>
       <c r="O76">
-        <v>-268.575272152</v>
+        <v>-272.7680461</v>
       </c>
       <c r="P76">
-        <v>-952.221419448</v>
+        <v>-967.0867089000001</v>
       </c>
       <c r="Q76">
-        <v>-805.521419448</v>
+        <v>-820.3867089</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1768035322526174</v>
+        <v>0.1820436735427221</v>
       </c>
       <c r="T76">
-        <v>3.025485733316798</v>
+        <v>3.14650516264947</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02956115564073412</v>
+        <v>0.02916700689885766</v>
       </c>
       <c r="W76">
-        <v>0.2288294794999149</v>
+        <v>0.2289224197732494</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1343688892760642</v>
+        <v>0.1325773040857167</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2172027332156176</v>
+        <v>0.2191027332156176</v>
       </c>
       <c r="C77">
-        <v>-4494.441115475132</v>
+        <v>-4592.304466344399</v>
       </c>
       <c r="D77">
-        <v>1554.283884524868</v>
+        <v>1537.243533655601</v>
       </c>
       <c r="E77">
-        <v>4647.025000000001</v>
+        <v>4727.848</v>
       </c>
       <c r="F77">
-        <v>6061.725</v>
+        <v>6142.548</v>
       </c>
       <c r="G77">
         <v>13</v>
@@ -7601,37 +7601,37 @@
         <v>189.5</v>
       </c>
       <c r="M77">
-        <v>1429.354755</v>
+        <v>1448.4128184</v>
       </c>
       <c r="N77">
-        <v>-1239.854755</v>
+        <v>-1258.9128184</v>
       </c>
       <c r="O77">
-        <v>-272.7680461</v>
+        <v>-276.960820048</v>
       </c>
       <c r="P77">
-        <v>-967.0867089000001</v>
+        <v>-981.9519983520001</v>
       </c>
       <c r="Q77">
-        <v>-820.3867089</v>
+        <v>-835.2519983520001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1820436735427221</v>
+        <v>0.1877204932736689</v>
       </c>
       <c r="T77">
-        <v>3.14650516264947</v>
+        <v>3.277609544426532</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02916700689885766</v>
+        <v>0.02878323049229374</v>
       </c>
       <c r="W77">
-        <v>0.2289224197732494</v>
+        <v>0.2290129142499172</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1325773040857167</v>
+        <v>0.1308328658740625</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2191027332156176</v>
+        <v>0.2210027332156175</v>
       </c>
       <c r="C78">
-        <v>-4592.304466344399</v>
+        <v>-4689.798226328212</v>
       </c>
       <c r="D78">
-        <v>1537.243533655601</v>
+        <v>1520.572773671788</v>
       </c>
       <c r="E78">
-        <v>4727.848</v>
+        <v>4808.671</v>
       </c>
       <c r="F78">
-        <v>6142.548</v>
+        <v>6223.371</v>
       </c>
       <c r="G78">
         <v>13</v>
@@ -7683,37 +7683,37 @@
         <v>189.5</v>
       </c>
       <c r="M78">
-        <v>1448.4128184</v>
+        <v>1467.4708818</v>
       </c>
       <c r="N78">
-        <v>-1258.9128184</v>
+        <v>-1277.9708818</v>
       </c>
       <c r="O78">
-        <v>-276.960820048</v>
+        <v>-281.153593996</v>
       </c>
       <c r="P78">
-        <v>-981.9519983520001</v>
+        <v>-996.8172878040001</v>
       </c>
       <c r="Q78">
-        <v>-835.2519983520001</v>
+        <v>-850.1172878040002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1877204932736689</v>
+        <v>0.1938909495029588</v>
       </c>
       <c r="T78">
-        <v>3.277609544426532</v>
+        <v>3.420114307227685</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02878323049229374</v>
+        <v>0.02840942230408213</v>
       </c>
       <c r="W78">
-        <v>0.2290129142499172</v>
+        <v>0.2291010582206974</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1308328658740625</v>
+        <v>0.1291337377458279</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2210027332156175</v>
+        <v>0.2229027332156175</v>
       </c>
       <c r="C79">
-        <v>-4689.798226328212</v>
+        <v>-4786.934290601812</v>
       </c>
       <c r="D79">
-        <v>1520.572773671788</v>
+        <v>1504.259709398189</v>
       </c>
       <c r="E79">
-        <v>4808.671</v>
+        <v>4889.494000000001</v>
       </c>
       <c r="F79">
-        <v>6223.371</v>
+        <v>6304.194</v>
       </c>
       <c r="G79">
         <v>13</v>
@@ -7765,37 +7765,37 @@
         <v>189.5</v>
       </c>
       <c r="M79">
-        <v>1467.4708818</v>
+        <v>1486.5289452</v>
       </c>
       <c r="N79">
-        <v>-1277.9708818</v>
+        <v>-1297.0289452</v>
       </c>
       <c r="O79">
-        <v>-281.153593996</v>
+        <v>-285.3463679440001</v>
       </c>
       <c r="P79">
-        <v>-996.8172878040001</v>
+        <v>-1011.682577256</v>
       </c>
       <c r="Q79">
-        <v>-850.1172878040002</v>
+        <v>-864.982577256</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1938909495029588</v>
+        <v>0.2006223562985478</v>
       </c>
       <c r="T79">
-        <v>3.420114307227685</v>
+        <v>3.575574048465307</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02840942230408213</v>
+        <v>0.02804519894120928</v>
       </c>
       <c r="W79">
-        <v>0.2291010582206974</v>
+        <v>0.2291869420896629</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1291337377458279</v>
+        <v>0.1274781770054968</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2229027332156175</v>
+        <v>0.2248027332156176</v>
       </c>
       <c r="C80">
-        <v>-4786.934290601812</v>
+        <v>-4883.724049301602</v>
       </c>
       <c r="D80">
-        <v>1504.259709398189</v>
+        <v>1488.292950698398</v>
       </c>
       <c r="E80">
-        <v>4889.494000000001</v>
+        <v>4970.317000000001</v>
       </c>
       <c r="F80">
-        <v>6304.194</v>
+        <v>6385.017000000001</v>
       </c>
       <c r="G80">
         <v>13</v>
@@ -7847,37 +7847,37 @@
         <v>189.5</v>
       </c>
       <c r="M80">
-        <v>1486.5289452</v>
+        <v>1505.5870086</v>
       </c>
       <c r="N80">
-        <v>-1297.0289452</v>
+        <v>-1316.0870086</v>
       </c>
       <c r="O80">
-        <v>-285.3463679440001</v>
+        <v>-289.539141892</v>
       </c>
       <c r="P80">
-        <v>-1011.682577256</v>
+        <v>-1026.547866708</v>
       </c>
       <c r="Q80">
-        <v>-864.982577256</v>
+        <v>-879.8478667080001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2006223562985478</v>
+        <v>0.2079948494556215</v>
       </c>
       <c r="T80">
-        <v>3.575574048465307</v>
+        <v>3.745839479344608</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02804519894120928</v>
+        <v>0.02769019642296613</v>
       </c>
       <c r="W80">
-        <v>0.2291869420896629</v>
+        <v>0.2292706516834646</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1274781770054968</v>
+        <v>0.1258645291953006</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2248027332156176</v>
+        <v>0.2267027332156176</v>
       </c>
       <c r="C81">
-        <v>-4883.724049301602</v>
+        <v>-4980.178414046968</v>
       </c>
       <c r="D81">
-        <v>1488.292950698398</v>
+        <v>1472.661585953032</v>
       </c>
       <c r="E81">
-        <v>4970.317000000001</v>
+        <v>5051.14</v>
       </c>
       <c r="F81">
-        <v>6385.017000000001</v>
+        <v>6465.84</v>
       </c>
       <c r="G81">
         <v>13</v>
@@ -7929,37 +7929,37 @@
         <v>189.5</v>
       </c>
       <c r="M81">
-        <v>1505.5870086</v>
+        <v>1524.645072</v>
       </c>
       <c r="N81">
-        <v>-1316.0870086</v>
+        <v>-1335.145072</v>
       </c>
       <c r="O81">
-        <v>-289.539141892</v>
+        <v>-293.73191584</v>
       </c>
       <c r="P81">
-        <v>-1026.547866708</v>
+        <v>-1041.41315616</v>
       </c>
       <c r="Q81">
-        <v>-879.8478667080001</v>
+        <v>-894.7131561599999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2079948494556215</v>
+        <v>0.2161045919284026</v>
       </c>
       <c r="T81">
-        <v>3.745839479344608</v>
+        <v>3.933131453311838</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02769019642296613</v>
+        <v>0.02734406896767905</v>
       </c>
       <c r="W81">
-        <v>0.2292706516834646</v>
+        <v>0.2293522685374213</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1258645291953006</v>
+        <v>0.1242912225803593</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2267027332156176</v>
+        <v>0.2286027332156175</v>
       </c>
       <c r="C82">
-        <v>-4980.178414046968</v>
+        <v>-5076.307842808131</v>
       </c>
       <c r="D82">
-        <v>1472.661585953032</v>
+        <v>1457.35515719187</v>
       </c>
       <c r="E82">
-        <v>5051.14</v>
+        <v>5131.963000000001</v>
       </c>
       <c r="F82">
-        <v>6465.84</v>
+        <v>6546.663</v>
       </c>
       <c r="G82">
         <v>13</v>
@@ -8011,37 +8011,37 @@
         <v>189.5</v>
       </c>
       <c r="M82">
-        <v>1524.645072</v>
+        <v>1543.7031354</v>
       </c>
       <c r="N82">
-        <v>-1335.145072</v>
+        <v>-1354.2031354</v>
       </c>
       <c r="O82">
-        <v>-293.73191584</v>
+        <v>-297.924689788</v>
       </c>
       <c r="P82">
-        <v>-1041.41315616</v>
+        <v>-1056.278445612</v>
       </c>
       <c r="Q82">
-        <v>-894.7131561599999</v>
+        <v>-909.578445612</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2161045919284026</v>
+        <v>0.2250679915035817</v>
       </c>
       <c r="T82">
-        <v>3.933131453311838</v>
+        <v>4.140138371907199</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02734406896767905</v>
+        <v>0.02700648786931265</v>
       </c>
       <c r="W82">
-        <v>0.2293522685374213</v>
+        <v>0.2294318701604161</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1242912225803593</v>
+        <v>0.1227567630423302</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2286027332156175</v>
+        <v>0.2305027332156176</v>
       </c>
       <c r="C83">
-        <v>-5076.307842808131</v>
+        <v>-5172.122363239137</v>
       </c>
       <c r="D83">
-        <v>1457.35515719187</v>
+        <v>1442.363636760864</v>
       </c>
       <c r="E83">
-        <v>5131.963000000001</v>
+        <v>5212.786000000001</v>
       </c>
       <c r="F83">
-        <v>6546.663</v>
+        <v>6627.486000000001</v>
       </c>
       <c r="G83">
         <v>13</v>
@@ -8093,37 +8093,37 @@
         <v>189.5</v>
       </c>
       <c r="M83">
-        <v>1543.7031354</v>
+        <v>1562.7611988</v>
       </c>
       <c r="N83">
-        <v>-1354.2031354</v>
+        <v>-1373.2611988</v>
       </c>
       <c r="O83">
-        <v>-297.924689788</v>
+        <v>-302.117463736</v>
       </c>
       <c r="P83">
-        <v>-1056.278445612</v>
+        <v>-1071.143735064</v>
       </c>
       <c r="Q83">
-        <v>-909.578445612</v>
+        <v>-924.4437350640003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2250679915035817</v>
+        <v>0.2350273243648918</v>
       </c>
       <c r="T83">
-        <v>4.140138371907199</v>
+        <v>4.370146059235377</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02700648786931265</v>
+        <v>0.02667714045627224</v>
       </c>
       <c r="W83">
-        <v>0.2294318701604161</v>
+        <v>0.229509530280411</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1227567630423302</v>
+        <v>0.121259729346692</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2305027332156176</v>
+        <v>0.2324027332156176</v>
       </c>
       <c r="C84">
-        <v>-5172.122363239137</v>
+        <v>-5267.631594585378</v>
       </c>
       <c r="D84">
-        <v>1442.363636760864</v>
+        <v>1427.677405414622</v>
       </c>
       <c r="E84">
-        <v>5212.786000000001</v>
+        <v>5293.609000000001</v>
       </c>
       <c r="F84">
-        <v>6627.486000000001</v>
+        <v>6708.309000000001</v>
       </c>
       <c r="G84">
         <v>13</v>
@@ -8175,37 +8175,37 @@
         <v>189.5</v>
       </c>
       <c r="M84">
-        <v>1562.7611988</v>
+        <v>1581.8192622</v>
       </c>
       <c r="N84">
-        <v>-1373.2611988</v>
+        <v>-1392.3192622</v>
       </c>
       <c r="O84">
-        <v>-302.117463736</v>
+        <v>-306.3102376840001</v>
       </c>
       <c r="P84">
-        <v>-1071.143735064</v>
+        <v>-1086.009024516</v>
       </c>
       <c r="Q84">
-        <v>-924.4437350640003</v>
+        <v>-939.3090245160004</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2350273243648918</v>
+        <v>0.2461583434451796</v>
       </c>
       <c r="T84">
-        <v>4.370146059235377</v>
+        <v>4.627213474484517</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02667714045627224</v>
+        <v>0.02635572912547378</v>
       </c>
       <c r="W84">
-        <v>0.229509530280411</v>
+        <v>0.2295853190722133</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.121259729346692</v>
+        <v>0.1197987687521536</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2324027332156176</v>
+        <v>0.2343027332156176</v>
       </c>
       <c r="C85">
-        <v>-5267.631594585378</v>
+        <v>-5362.844768266229</v>
       </c>
       <c r="D85">
-        <v>1427.677405414622</v>
+        <v>1413.287231733771</v>
       </c>
       <c r="E85">
-        <v>5293.609000000001</v>
+        <v>5374.432000000001</v>
       </c>
       <c r="F85">
-        <v>6708.309000000001</v>
+        <v>6789.132000000001</v>
       </c>
       <c r="G85">
         <v>13</v>
@@ -8257,37 +8257,37 @@
         <v>189.5</v>
       </c>
       <c r="M85">
-        <v>1581.8192622</v>
+        <v>1600.8773256</v>
       </c>
       <c r="N85">
-        <v>-1392.3192622</v>
+        <v>-1411.3773256</v>
       </c>
       <c r="O85">
-        <v>-306.3102376840001</v>
+        <v>-310.503011632</v>
       </c>
       <c r="P85">
-        <v>-1086.009024516</v>
+        <v>-1100.874313968</v>
       </c>
       <c r="Q85">
-        <v>-939.3090245160004</v>
+        <v>-954.174313968</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2461583434451796</v>
+        <v>0.2586807399105033</v>
       </c>
       <c r="T85">
-        <v>4.627213474484517</v>
+        <v>4.9164143166398</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02635572912547378</v>
+        <v>0.02604197044540862</v>
       </c>
       <c r="W85">
-        <v>0.2295853190722133</v>
+        <v>0.2296593033689727</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1197987687521536</v>
+        <v>0.1183725929336755</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2343027332156175</v>
+        <v>0.2362027332156175</v>
       </c>
       <c r="C86">
-        <v>-5362.844768266228</v>
+        <v>-5457.770747225324</v>
       </c>
       <c r="D86">
-        <v>1413.287231733771</v>
+        <v>1399.184252774676</v>
       </c>
       <c r="E86">
-        <v>5374.432</v>
+        <v>5455.255</v>
       </c>
       <c r="F86">
-        <v>6789.132</v>
+        <v>6869.955</v>
       </c>
       <c r="G86">
         <v>13</v>
@@ -8339,37 +8339,37 @@
         <v>189.5</v>
       </c>
       <c r="M86">
-        <v>1600.8773256</v>
+        <v>1619.935389</v>
       </c>
       <c r="N86">
-        <v>-1411.3773256</v>
+        <v>-1430.435389</v>
       </c>
       <c r="O86">
-        <v>-310.503011632</v>
+        <v>-314.69578558</v>
       </c>
       <c r="P86">
-        <v>-1100.874313968</v>
+        <v>-1115.73960342</v>
       </c>
       <c r="Q86">
-        <v>-954.174313968</v>
+        <v>-969.03960342</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2586807399105032</v>
+        <v>0.2728727892378701</v>
       </c>
       <c r="T86">
-        <v>4.916414316639796</v>
+        <v>5.24417527108245</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02604197044540862</v>
+        <v>0.02573559432252146</v>
       </c>
       <c r="W86">
-        <v>0.2296593033689726</v>
+        <v>0.2297315468587494</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1183725929336755</v>
+        <v>0.1169799741932794</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2362027332156175</v>
+        <v>0.2381027332156175</v>
       </c>
       <c r="C87">
-        <v>-5457.770747225324</v>
+        <v>-5552.418044133737</v>
       </c>
       <c r="D87">
-        <v>1399.184252774676</v>
+        <v>1385.359955866263</v>
       </c>
       <c r="E87">
-        <v>5455.255</v>
+        <v>5536.078</v>
       </c>
       <c r="F87">
-        <v>6869.955</v>
+        <v>6950.778</v>
       </c>
       <c r="G87">
         <v>13</v>
@@ -8421,37 +8421,37 @@
         <v>189.5</v>
       </c>
       <c r="M87">
-        <v>1619.935389</v>
+        <v>1638.9934524</v>
       </c>
       <c r="N87">
-        <v>-1430.435389</v>
+        <v>-1449.4934524</v>
       </c>
       <c r="O87">
-        <v>-314.69578558</v>
+        <v>-318.888559528</v>
       </c>
       <c r="P87">
-        <v>-1115.73960342</v>
+        <v>-1130.604892872</v>
       </c>
       <c r="Q87">
-        <v>-969.03960342</v>
+        <v>-983.9048928719999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2728727892378701</v>
+        <v>0.2890922741834322</v>
       </c>
       <c r="T87">
-        <v>5.24417527108245</v>
+        <v>5.61875921901691</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02573559432252146</v>
+        <v>0.02543634322574796</v>
       </c>
       <c r="W87">
-        <v>0.2297315468587494</v>
+        <v>0.2298021102673686</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1169799741932794</v>
+        <v>0.115619741935218</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2381027332156175</v>
+        <v>0.2400027332156175</v>
       </c>
       <c r="C88">
-        <v>-5552.418044133737</v>
+        <v>-5646.794838524589</v>
       </c>
       <c r="D88">
-        <v>1385.359955866263</v>
+        <v>1371.806161475411</v>
       </c>
       <c r="E88">
-        <v>5536.078</v>
+        <v>5616.901000000001</v>
       </c>
       <c r="F88">
-        <v>6950.778</v>
+        <v>7031.601000000001</v>
       </c>
       <c r="G88">
         <v>13</v>
@@ -8503,37 +8503,37 @@
         <v>189.5</v>
       </c>
       <c r="M88">
-        <v>1638.9934524</v>
+        <v>1658.0515158</v>
       </c>
       <c r="N88">
-        <v>-1449.4934524</v>
+        <v>-1468.5515158</v>
       </c>
       <c r="O88">
-        <v>-318.888559528</v>
+        <v>-323.0813334760001</v>
       </c>
       <c r="P88">
-        <v>-1130.604892872</v>
+        <v>-1145.470182324</v>
       </c>
       <c r="Q88">
-        <v>-983.9048928719999</v>
+        <v>-998.7701823240002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2890922741834322</v>
+        <v>0.3078070645052347</v>
       </c>
       <c r="T88">
-        <v>5.61875921901691</v>
+        <v>6.050971466633595</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02543634322574796</v>
+        <v>0.02514397146453246</v>
       </c>
       <c r="W88">
-        <v>0.2298021102673686</v>
+        <v>0.2298710515286632</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.115619741935218</v>
+        <v>0.1142907793842385</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2400027332156175</v>
+        <v>0.2419027332156175</v>
       </c>
       <c r="C89">
-        <v>-5646.794838524589</v>
+        <v>-5740.908992931587</v>
       </c>
       <c r="D89">
-        <v>1371.806161475411</v>
+        <v>1358.515007068413</v>
       </c>
       <c r="E89">
-        <v>5616.901000000001</v>
+        <v>5697.724</v>
       </c>
       <c r="F89">
-        <v>7031.601000000001</v>
+        <v>7112.424</v>
       </c>
       <c r="G89">
         <v>13</v>
@@ -8585,37 +8585,37 @@
         <v>189.5</v>
       </c>
       <c r="M89">
-        <v>1658.0515158</v>
+        <v>1677.1095792</v>
       </c>
       <c r="N89">
-        <v>-1468.5515158</v>
+        <v>-1487.6095792</v>
       </c>
       <c r="O89">
-        <v>-323.0813334760001</v>
+        <v>-327.274107424</v>
       </c>
       <c r="P89">
-        <v>-1145.470182324</v>
+        <v>-1160.335471776</v>
       </c>
       <c r="Q89">
-        <v>-998.7701823240002</v>
+        <v>-1013.635471776</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3078070645052347</v>
+        <v>0.3296409865473376</v>
       </c>
       <c r="T89">
-        <v>6.050971466633595</v>
+        <v>6.555219088853063</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02514397146453246</v>
+        <v>0.02485824451607187</v>
       </c>
       <c r="W89">
-        <v>0.2298710515286632</v>
+        <v>0.2299384259431103</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1142907793842385</v>
+        <v>0.1129920205275994</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2419027332156175</v>
+        <v>0.2438027332156175</v>
       </c>
       <c r="C90">
-        <v>-5740.908992931587</v>
+        <v>-5834.768068098384</v>
       </c>
       <c r="D90">
-        <v>1358.515007068413</v>
+        <v>1345.478931901617</v>
       </c>
       <c r="E90">
-        <v>5697.724</v>
+        <v>5778.547</v>
       </c>
       <c r="F90">
-        <v>7112.424</v>
+        <v>7193.247</v>
       </c>
       <c r="G90">
         <v>13</v>
@@ -8667,37 +8667,37 @@
         <v>189.5</v>
       </c>
       <c r="M90">
-        <v>1677.1095792</v>
+        <v>1696.1676426</v>
       </c>
       <c r="N90">
-        <v>-1487.6095792</v>
+        <v>-1506.6676426</v>
       </c>
       <c r="O90">
-        <v>-327.274107424</v>
+        <v>-331.466881372</v>
       </c>
       <c r="P90">
-        <v>-1160.335471776</v>
+        <v>-1175.200761228</v>
       </c>
       <c r="Q90">
-        <v>-1013.635471776</v>
+        <v>-1028.500761228</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3296409865473376</v>
+        <v>0.3554447125970956</v>
       </c>
       <c r="T90">
-        <v>6.555219088853063</v>
+        <v>7.151148096930615</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02485824451607187</v>
+        <v>0.02457893839791376</v>
       </c>
       <c r="W90">
-        <v>0.2299384259431103</v>
+        <v>0.2300042863257719</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1129920205275994</v>
+        <v>0.1117224472632443</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2438027332156175</v>
+        <v>0.2457027332156176</v>
       </c>
       <c r="C91">
-        <v>-5834.768068098384</v>
+        <v>-5928.379337320575</v>
       </c>
       <c r="D91">
-        <v>1345.478931901617</v>
+        <v>1332.690662679425</v>
       </c>
       <c r="E91">
-        <v>5778.547</v>
+        <v>5859.370000000001</v>
       </c>
       <c r="F91">
-        <v>7193.247</v>
+        <v>7274.070000000001</v>
       </c>
       <c r="G91">
         <v>13</v>
@@ -8749,37 +8749,37 @@
         <v>189.5</v>
       </c>
       <c r="M91">
-        <v>1696.1676426</v>
+        <v>1715.225706</v>
       </c>
       <c r="N91">
-        <v>-1506.6676426</v>
+        <v>-1525.725706</v>
       </c>
       <c r="O91">
-        <v>-331.466881372</v>
+        <v>-335.65965532</v>
       </c>
       <c r="P91">
-        <v>-1175.200761228</v>
+        <v>-1190.06605068</v>
       </c>
       <c r="Q91">
-        <v>-1028.500761228</v>
+        <v>-1043.36605068</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3554447125970956</v>
+        <v>0.3864091838568052</v>
       </c>
       <c r="T91">
-        <v>7.151148096930615</v>
+        <v>7.866262906623676</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02457893839791376</v>
+        <v>0.02430583908238138</v>
       </c>
       <c r="W91">
-        <v>0.2300042863257719</v>
+        <v>0.2300686831443745</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1117224472632443</v>
+        <v>0.1104810867380972</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2457027332156176</v>
+        <v>0.2476027332156175</v>
       </c>
       <c r="C92">
-        <v>-5928.379337320575</v>
+        <v>-6021.749799977512</v>
       </c>
       <c r="D92">
-        <v>1332.690662679425</v>
+        <v>1320.143200022488</v>
       </c>
       <c r="E92">
-        <v>5859.370000000001</v>
+        <v>5940.193</v>
       </c>
       <c r="F92">
-        <v>7274.070000000001</v>
+        <v>7354.893</v>
       </c>
       <c r="G92">
         <v>13</v>
@@ -8831,37 +8831,37 @@
         <v>189.5</v>
       </c>
       <c r="M92">
-        <v>1715.225706</v>
+        <v>1734.2837694</v>
       </c>
       <c r="N92">
-        <v>-1525.725706</v>
+        <v>-1544.7837694</v>
       </c>
       <c r="O92">
-        <v>-335.65965532</v>
+        <v>-339.852429268</v>
       </c>
       <c r="P92">
-        <v>-1190.06605068</v>
+        <v>-1204.931340132</v>
       </c>
       <c r="Q92">
-        <v>-1043.36605068</v>
+        <v>-1058.231340132</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3864091838568052</v>
+        <v>0.4242546487297836</v>
       </c>
       <c r="T92">
-        <v>7.866262906623676</v>
+        <v>8.740292118470753</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02430583908238138</v>
+        <v>0.02403874194960796</v>
       </c>
       <c r="W92">
-        <v>0.2300686831443745</v>
+        <v>0.2301316646482824</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1104810867380972</v>
+        <v>0.1092670088618544</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2476027332156175</v>
+        <v>0.2495027332156176</v>
       </c>
       <c r="C93">
-        <v>-6021.749799977512</v>
+        <v>-6114.886194306826</v>
       </c>
       <c r="D93">
-        <v>1320.143200022488</v>
+        <v>1307.829805693175</v>
       </c>
       <c r="E93">
-        <v>5940.193</v>
+        <v>6021.016000000001</v>
       </c>
       <c r="F93">
-        <v>7354.893</v>
+        <v>7435.716</v>
       </c>
       <c r="G93">
         <v>13</v>
@@ -8913,37 +8913,37 @@
         <v>189.5</v>
       </c>
       <c r="M93">
-        <v>1734.2837694</v>
+        <v>1753.3418328</v>
       </c>
       <c r="N93">
-        <v>-1544.7837694</v>
+        <v>-1563.8418328</v>
       </c>
       <c r="O93">
-        <v>-339.852429268</v>
+        <v>-344.0452032160001</v>
       </c>
       <c r="P93">
-        <v>-1204.931340132</v>
+        <v>-1219.796629584</v>
       </c>
       <c r="Q93">
-        <v>-1058.231340132</v>
+        <v>-1073.096629584</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4242546487297836</v>
+        <v>0.4715614798210066</v>
       </c>
       <c r="T93">
-        <v>8.740292118470753</v>
+        <v>9.832828633279599</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02403874194960796</v>
+        <v>0.02377745127624266</v>
       </c>
       <c r="W93">
-        <v>0.2301316646482824</v>
+        <v>0.230193276989062</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1092670088618544</v>
+        <v>0.1080793239829212</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2495027332156176</v>
+        <v>0.2514027332156175</v>
       </c>
       <c r="C94">
-        <v>-6114.886194306826</v>
+        <v>-6207.79500947063</v>
       </c>
       <c r="D94">
-        <v>1307.829805693175</v>
+        <v>1295.743990529371</v>
       </c>
       <c r="E94">
-        <v>6021.016000000001</v>
+        <v>6101.839000000001</v>
       </c>
       <c r="F94">
-        <v>7435.716</v>
+        <v>7516.539000000001</v>
       </c>
       <c r="G94">
         <v>13</v>
@@ -8995,37 +8995,37 @@
         <v>189.5</v>
       </c>
       <c r="M94">
-        <v>1753.3418328</v>
+        <v>1772.3998962</v>
       </c>
       <c r="N94">
-        <v>-1563.8418328</v>
+        <v>-1582.8998962</v>
       </c>
       <c r="O94">
-        <v>-344.0452032160001</v>
+        <v>-348.2379771640001</v>
       </c>
       <c r="P94">
-        <v>-1219.796629584</v>
+        <v>-1234.661919036</v>
       </c>
       <c r="Q94">
-        <v>-1073.096629584</v>
+        <v>-1087.961919036</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4715614798210066</v>
+        <v>0.5323845483668648</v>
       </c>
       <c r="T94">
-        <v>9.832828633279599</v>
+        <v>11.23751843803383</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02377745127624266</v>
+        <v>0.02352177975714327</v>
       </c>
       <c r="W94">
-        <v>0.230193276989062</v>
+        <v>0.2302535643332656</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1080793239829212</v>
+        <v>0.1069171807142876</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2514027332156175</v>
+        <v>0.2533027332156175</v>
       </c>
       <c r="C95">
-        <v>-6207.79500947063</v>
+        <v>-6300.482496958839</v>
       </c>
       <c r="D95">
-        <v>1295.743990529371</v>
+        <v>1283.879503041162</v>
       </c>
       <c r="E95">
-        <v>6101.839000000001</v>
+        <v>6182.662000000001</v>
       </c>
       <c r="F95">
-        <v>7516.539000000001</v>
+        <v>7597.362000000001</v>
       </c>
       <c r="G95">
         <v>13</v>
@@ -9077,37 +9077,37 @@
         <v>189.5</v>
       </c>
       <c r="M95">
-        <v>1772.3998962</v>
+        <v>1791.4579596</v>
       </c>
       <c r="N95">
-        <v>-1582.8998962</v>
+        <v>-1601.9579596</v>
       </c>
       <c r="O95">
-        <v>-348.2379771640001</v>
+        <v>-352.4307511120001</v>
       </c>
       <c r="P95">
-        <v>-1234.661919036</v>
+        <v>-1249.527208488</v>
       </c>
       <c r="Q95">
-        <v>-1087.961919036</v>
+        <v>-1102.827208488</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5323845483668648</v>
+        <v>0.6134819730946757</v>
       </c>
       <c r="T95">
-        <v>11.23751843803383</v>
+        <v>13.11043817770614</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02352177975714327</v>
+        <v>0.02327154805759919</v>
       </c>
       <c r="W95">
-        <v>0.2302535643332656</v>
+        <v>0.2303125689680181</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1069171807142876</v>
+        <v>0.1057797638981781</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2533027332156175</v>
+        <v>0.2552027332156175</v>
       </c>
       <c r="C96">
-        <v>-6300.482496958839</v>
+        <v>-6392.954681371663</v>
       </c>
       <c r="D96">
-        <v>1283.879503041162</v>
+        <v>1272.230318628337</v>
       </c>
       <c r="E96">
-        <v>6182.662000000001</v>
+        <v>6263.485000000001</v>
       </c>
       <c r="F96">
-        <v>7597.362000000001</v>
+        <v>7678.185</v>
       </c>
       <c r="G96">
         <v>13</v>
@@ -9159,37 +9159,37 @@
         <v>189.5</v>
       </c>
       <c r="M96">
-        <v>1791.4579596</v>
+        <v>1810.516023</v>
       </c>
       <c r="N96">
-        <v>-1601.9579596</v>
+        <v>-1621.016023</v>
       </c>
       <c r="O96">
-        <v>-352.4307511120001</v>
+        <v>-356.62352506</v>
       </c>
       <c r="P96">
-        <v>-1249.527208488</v>
+        <v>-1264.39249794</v>
       </c>
       <c r="Q96">
-        <v>-1102.827208488</v>
+        <v>-1117.69249794</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6134819730946757</v>
+        <v>0.7270183677136112</v>
       </c>
       <c r="T96">
-        <v>13.11043817770614</v>
+        <v>15.73252581324737</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02327154805759919</v>
+        <v>0.023026584393835</v>
       </c>
       <c r="W96">
-        <v>0.2303125689680181</v>
+        <v>0.2303703313999337</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1057797638981781</v>
+        <v>0.10466629269925</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2552027332156175</v>
+        <v>0.2571027332156176</v>
       </c>
       <c r="C97">
-        <v>-6392.954681371663</v>
+        <v>-6485.217370620393</v>
       </c>
       <c r="D97">
-        <v>1272.230318628337</v>
+        <v>1260.790629379607</v>
       </c>
       <c r="E97">
-        <v>6263.485000000001</v>
+        <v>6344.308000000001</v>
       </c>
       <c r="F97">
-        <v>7678.185</v>
+        <v>7759.008000000001</v>
       </c>
       <c r="G97">
         <v>13</v>
@@ -9241,37 +9241,37 @@
         <v>189.5</v>
       </c>
       <c r="M97">
-        <v>1810.516023</v>
+        <v>1829.5740864</v>
       </c>
       <c r="N97">
-        <v>-1621.016023</v>
+        <v>-1640.0740864</v>
       </c>
       <c r="O97">
-        <v>-356.62352506</v>
+        <v>-360.816299008</v>
       </c>
       <c r="P97">
-        <v>-1264.39249794</v>
+        <v>-1279.257787392</v>
       </c>
       <c r="Q97">
-        <v>-1117.69249794</v>
+        <v>-1132.557787392</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7270183677136112</v>
+        <v>0.8973229596420144</v>
       </c>
       <c r="T97">
-        <v>15.73252581324737</v>
+        <v>19.66565726655923</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.023026584393835</v>
+        <v>0.02278672413973255</v>
       </c>
       <c r="W97">
-        <v>0.2303703313999337</v>
+        <v>0.2304268904478511</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.10466629269925</v>
+        <v>0.1035760188169661</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2571027332156175</v>
+        <v>0.2590027332156176</v>
       </c>
       <c r="C98">
-        <v>-6485.217370620392</v>
+        <v>-6577.276165582733</v>
       </c>
       <c r="D98">
-        <v>1260.790629379607</v>
+        <v>1249.554834417267</v>
       </c>
       <c r="E98">
-        <v>6344.308</v>
+        <v>6425.131</v>
       </c>
       <c r="F98">
-        <v>7759.008</v>
+        <v>7839.831</v>
       </c>
       <c r="G98">
         <v>13</v>
@@ -9323,37 +9323,37 @@
         <v>189.5</v>
       </c>
       <c r="M98">
-        <v>1829.5740864</v>
+        <v>1848.6321498</v>
       </c>
       <c r="N98">
-        <v>-1640.0740864</v>
+        <v>-1659.1321498</v>
       </c>
       <c r="O98">
-        <v>-360.816299008</v>
+        <v>-365.0090729560001</v>
       </c>
       <c r="P98">
-        <v>-1279.257787392</v>
+        <v>-1294.123076844</v>
       </c>
       <c r="Q98">
-        <v>-1132.557787392</v>
+        <v>-1147.423076844</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8973229596420119</v>
+        <v>1.18116394618935</v>
       </c>
       <c r="T98">
-        <v>19.66565726655917</v>
+        <v>26.22087635541223</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02278672413973255</v>
+        <v>0.02255180945787963</v>
       </c>
       <c r="W98">
-        <v>0.2304268904478511</v>
+        <v>0.230482283329832</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1035760188169661</v>
+        <v>0.1025082248085438</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2590027332156176</v>
+        <v>0.2609027332156175</v>
       </c>
       <c r="C99">
-        <v>-6577.276165582733</v>
+        <v>-6669.136469246434</v>
       </c>
       <c r="D99">
-        <v>1249.554834417267</v>
+        <v>1238.517530753566</v>
       </c>
       <c r="E99">
-        <v>6425.131</v>
+        <v>6505.954000000001</v>
       </c>
       <c r="F99">
-        <v>7839.831</v>
+        <v>7920.654</v>
       </c>
       <c r="G99">
         <v>13</v>
@@ -9405,37 +9405,37 @@
         <v>189.5</v>
       </c>
       <c r="M99">
-        <v>1848.6321498</v>
+        <v>1867.6902132</v>
       </c>
       <c r="N99">
-        <v>-1659.1321498</v>
+        <v>-1678.1902132</v>
       </c>
       <c r="O99">
-        <v>-365.0090729560001</v>
+        <v>-369.201846904</v>
       </c>
       <c r="P99">
-        <v>-1294.123076844</v>
+        <v>-1308.988366296</v>
       </c>
       <c r="Q99">
-        <v>-1147.423076844</v>
+        <v>-1162.288366296</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.18116394618935</v>
+        <v>1.748845919284024</v>
       </c>
       <c r="T99">
-        <v>26.22087635541223</v>
+        <v>39.33131453311834</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02255180945787963</v>
+        <v>0.02232168895320739</v>
       </c>
       <c r="W99">
-        <v>0.230482283329832</v>
+        <v>0.2305365457448337</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1025082248085438</v>
+        <v>0.101462222514579</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2609027332156175</v>
+        <v>0.2628027332156175</v>
       </c>
       <c r="C100">
-        <v>-6669.136469246434</v>
+        <v>-6760.803495372564</v>
       </c>
       <c r="D100">
-        <v>1238.517530753566</v>
+        <v>1227.673504627436</v>
       </c>
       <c r="E100">
-        <v>6505.954000000001</v>
+        <v>6586.777</v>
       </c>
       <c r="F100">
-        <v>7920.654</v>
+        <v>8001.477</v>
       </c>
       <c r="G100">
         <v>13</v>
@@ -9487,37 +9487,37 @@
         <v>189.5</v>
       </c>
       <c r="M100">
-        <v>1867.6902132</v>
+        <v>1886.7482766</v>
       </c>
       <c r="N100">
-        <v>-1678.1902132</v>
+        <v>-1697.2482766</v>
       </c>
       <c r="O100">
-        <v>-369.201846904</v>
+        <v>-373.394620852</v>
       </c>
       <c r="P100">
-        <v>-1308.988366296</v>
+        <v>-1323.853655748</v>
       </c>
       <c r="Q100">
-        <v>-1162.288366296</v>
+        <v>-1177.153655748</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.748845919284024</v>
+        <v>3.451891838568048</v>
       </c>
       <c r="T100">
-        <v>39.33131453311834</v>
+        <v>78.66262906623668</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02232168895320739</v>
+        <v>0.02209621734761944</v>
       </c>
       <c r="W100">
-        <v>0.2305365457448337</v>
+        <v>0.2305897119494313</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.101462222514579</v>
+        <v>0.1004373515800884</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2628027332156175</v>
-      </c>
-      <c r="C101">
-        <v>-6760.803495372564</v>
-      </c>
-      <c r="D101">
-        <v>1227.673504627436</v>
-      </c>
-      <c r="E101">
-        <v>6586.777</v>
-      </c>
-      <c r="F101">
-        <v>8001.477</v>
-      </c>
-      <c r="G101">
-        <v>13</v>
-      </c>
-      <c r="H101">
-        <v>6667.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>336.2</v>
-      </c>
-      <c r="K101">
-        <v>146.7</v>
-      </c>
-      <c r="L101">
-        <v>189.5</v>
-      </c>
-      <c r="M101">
-        <v>1886.7482766</v>
-      </c>
-      <c r="N101">
-        <v>-1697.2482766</v>
-      </c>
-      <c r="O101">
-        <v>-373.394620852</v>
-      </c>
-      <c r="P101">
-        <v>-1323.853655748</v>
-      </c>
-      <c r="Q101">
-        <v>-1177.153655748</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.451891838568048</v>
-      </c>
-      <c r="T101">
-        <v>78.66262906623668</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02209621734761944</v>
-      </c>
-      <c r="W101">
-        <v>0.2305897119494313</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1004373515800884</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
